--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -86,26 +86,26 @@
     <sheet name="North Park" sheetId="77" r:id="rId77"/>
     <sheet name="Chinatown" sheetId="78" r:id="rId78"/>
     <sheet name="Beverly" sheetId="79" r:id="rId79"/>
-    <sheet name="Sauganash,Forest Glen" sheetId="80" r:id="rId80"/>
-    <sheet name="Garfield Ridge" sheetId="81" r:id="rId81"/>
+    <sheet name="West Lawn" sheetId="80" r:id="rId80"/>
+    <sheet name="East Side" sheetId="81" r:id="rId81"/>
     <sheet name="Rush &amp; Division" sheetId="82" r:id="rId82"/>
-    <sheet name="West Lawn" sheetId="83" r:id="rId83"/>
-    <sheet name="East Side" sheetId="84" r:id="rId84"/>
-    <sheet name="Pullman" sheetId="85" r:id="rId85"/>
-    <sheet name="Streeterville" sheetId="86" r:id="rId86"/>
-    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
-    <sheet name="Jackson Park" sheetId="88" r:id="rId88"/>
-    <sheet name="Millenium Park" sheetId="89" r:id="rId89"/>
-    <sheet name="Museum Campus" sheetId="90" r:id="rId90"/>
-    <sheet name="Printers Row" sheetId="91" r:id="rId91"/>
-    <sheet name="Gold Coast" sheetId="92" r:id="rId92"/>
-    <sheet name="Burnside" sheetId="93" r:id="rId93"/>
-    <sheet name="Bridgeport" sheetId="94" r:id="rId94"/>
-    <sheet name="Armour Square" sheetId="95" r:id="rId95"/>
-    <sheet name="Wrigleyville" sheetId="96" r:id="rId96"/>
-    <sheet name="Mount Greenwood" sheetId="97" r:id="rId97"/>
-    <sheet name="Edison Park" sheetId="98" r:id="rId98"/>
-    <sheet name="Andersonville" sheetId="99" r:id="rId99"/>
+    <sheet name="Pullman" sheetId="83" r:id="rId83"/>
+    <sheet name="Streeterville" sheetId="84" r:id="rId84"/>
+    <sheet name="Riverdale" sheetId="85" r:id="rId85"/>
+    <sheet name="Jackson Park" sheetId="86" r:id="rId86"/>
+    <sheet name="Millenium Park" sheetId="87" r:id="rId87"/>
+    <sheet name="Museum Campus" sheetId="88" r:id="rId88"/>
+    <sheet name="Printers Row" sheetId="89" r:id="rId89"/>
+    <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
+    <sheet name="Burnside" sheetId="91" r:id="rId91"/>
+    <sheet name="Bridgeport" sheetId="92" r:id="rId92"/>
+    <sheet name="Mount Greenwood" sheetId="93" r:id="rId93"/>
+    <sheet name="Garfield Ridge" sheetId="94" r:id="rId94"/>
+    <sheet name="Wrigleyville" sheetId="95" r:id="rId95"/>
+    <sheet name="Armour Square" sheetId="96" r:id="rId96"/>
+    <sheet name="Edison Park" sheetId="97" r:id="rId97"/>
+    <sheet name="Andersonville" sheetId="98" r:id="rId98"/>
+    <sheet name="Sauganash,Forest Glen" sheetId="99" r:id="rId99"/>
     <sheet name="Grant Park" sheetId="100" r:id="rId100"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41048,40 +41048,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41089,53 +41089,77 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
       <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -41144,40 +41168,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>64</v>
+      </c>
+      <c r="J5">
+        <v>92</v>
+      </c>
+      <c r="K5">
+        <v>66</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
         <v>36</v>
-      </c>
-      <c r="I5">
-        <v>40</v>
-      </c>
-      <c r="J5">
-        <v>39</v>
-      </c>
-      <c r="K5">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>25</v>
-      </c>
-      <c r="M5">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41185,39 +41209,72 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
       <c r="J7">
         <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41225,40 +41282,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>271</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41266,37 +41323,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="M9">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41304,40 +41364,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>119</v>
+        <v>641</v>
       </c>
       <c r="C10">
-        <v>146</v>
+        <v>540</v>
       </c>
       <c r="D10">
-        <v>152</v>
+        <v>482</v>
       </c>
       <c r="E10">
-        <v>152</v>
+        <v>485</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>443</v>
       </c>
       <c r="G10">
-        <v>103</v>
+        <v>310</v>
       </c>
       <c r="H10">
-        <v>88</v>
+        <v>248</v>
       </c>
       <c r="I10">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="J10">
-        <v>151</v>
+        <v>360</v>
       </c>
       <c r="K10">
-        <v>146</v>
+        <v>479</v>
       </c>
       <c r="L10">
-        <v>117</v>
+        <v>486</v>
       </c>
       <c r="M10">
-        <v>55</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41345,40 +41405,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>194</v>
+        <v>1023</v>
       </c>
       <c r="C11">
-        <v>271</v>
+        <v>1021</v>
       </c>
       <c r="D11">
-        <v>245</v>
+        <v>860</v>
       </c>
       <c r="E11">
-        <v>246</v>
+        <v>846</v>
       </c>
       <c r="F11">
-        <v>186</v>
+        <v>718</v>
       </c>
       <c r="G11">
-        <v>183</v>
+        <v>519</v>
       </c>
       <c r="H11">
-        <v>156</v>
+        <v>501</v>
       </c>
       <c r="I11">
-        <v>222</v>
+        <v>727</v>
       </c>
       <c r="J11">
-        <v>256</v>
+        <v>845</v>
       </c>
       <c r="K11">
-        <v>243</v>
+        <v>936</v>
       </c>
       <c r="L11">
-        <v>187</v>
+        <v>803</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -41452,40 +41512,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L2">
         <v>42</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41493,40 +41553,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C3">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
         <v>28</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>33</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>36</v>
-      </c>
-      <c r="K3">
-        <v>41</v>
-      </c>
-      <c r="L3">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41534,39 +41594,36 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
       <c r="L4">
-        <v>6</v>
-      </c>
-      <c r="M4">
         <v>2</v>
       </c>
     </row>
@@ -41575,40 +41632,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="E5">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="K5">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L5">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41616,37 +41673,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -41657,37 +41714,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="D7">
+      <c r="J7">
         <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41695,40 +41755,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F8">
+        <v>39</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8">
         <v>52</v>
       </c>
-      <c r="G8">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>70</v>
-      </c>
       <c r="I8">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="J8">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="K8">
-        <v>339</v>
+        <v>174</v>
       </c>
       <c r="L8">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="M8">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41736,40 +41796,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
         <v>39</v>
       </c>
-      <c r="H9">
-        <v>52</v>
-      </c>
-      <c r="I9">
-        <v>24</v>
-      </c>
       <c r="J9">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K9">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41777,40 +41837,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>395</v>
+        <v>180</v>
       </c>
       <c r="C10">
-        <v>492</v>
+        <v>215</v>
       </c>
       <c r="D10">
-        <v>381</v>
+        <v>184</v>
       </c>
       <c r="E10">
-        <v>489</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>489</v>
+        <v>137</v>
       </c>
       <c r="G10">
-        <v>276</v>
+        <v>126</v>
       </c>
       <c r="H10">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="I10">
-        <v>445</v>
+        <v>192</v>
       </c>
       <c r="J10">
-        <v>502</v>
+        <v>269</v>
       </c>
       <c r="K10">
-        <v>411</v>
+        <v>193</v>
       </c>
       <c r="L10">
-        <v>386</v>
+        <v>218</v>
       </c>
       <c r="M10">
-        <v>231</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41818,40 +41878,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>654</v>
+        <v>385</v>
       </c>
       <c r="C11">
-        <v>876</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>743</v>
+        <v>397</v>
       </c>
       <c r="E11">
-        <v>789</v>
+        <v>354</v>
       </c>
       <c r="F11">
-        <v>728</v>
+        <v>298</v>
       </c>
       <c r="G11">
-        <v>491</v>
+        <v>290</v>
       </c>
       <c r="H11">
-        <v>565</v>
+        <v>326</v>
       </c>
       <c r="I11">
-        <v>767</v>
+        <v>434</v>
       </c>
       <c r="J11">
-        <v>949</v>
+        <v>592</v>
       </c>
       <c r="K11">
-        <v>973</v>
+        <v>554</v>
       </c>
       <c r="L11">
-        <v>703</v>
+        <v>580</v>
       </c>
       <c r="M11">
-        <v>456</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -42347,40 +42407,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K2">
         <v>35</v>
       </c>
       <c r="L2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42388,40 +42448,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>31</v>
+      </c>
+      <c r="F3">
         <v>29</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>36</v>
+      </c>
+      <c r="H3">
+        <v>31</v>
+      </c>
+      <c r="I3">
+        <v>24</v>
+      </c>
+      <c r="J3">
         <v>28</v>
       </c>
-      <c r="F3">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <v>33</v>
-      </c>
-      <c r="H3">
-        <v>34</v>
-      </c>
-      <c r="I3">
-        <v>37</v>
-      </c>
-      <c r="J3">
-        <v>37</v>
-      </c>
       <c r="K3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42429,13 +42489,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -42446,20 +42503,17 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -42467,40 +42521,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="J5">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="K5">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42508,40 +42562,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
       <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
       <c r="J6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -42549,31 +42603,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -42581,40 +42635,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G8">
+        <v>44</v>
+      </c>
+      <c r="H8">
         <v>48</v>
       </c>
-      <c r="H8">
-        <v>63</v>
-      </c>
       <c r="I8">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="J8">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="K8">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="L8">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="M8">
-        <v>129</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42622,40 +42676,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -42663,40 +42717,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>641</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>540</v>
+        <v>250</v>
       </c>
       <c r="D10">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="E10">
-        <v>485</v>
+        <v>297</v>
       </c>
       <c r="F10">
-        <v>443</v>
+        <v>226</v>
       </c>
       <c r="G10">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="H10">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="I10">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="J10">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="K10">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="L10">
-        <v>486</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>278</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42704,40 +42758,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1023</v>
+        <v>359</v>
       </c>
       <c r="C11">
-        <v>1021</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>860</v>
+        <v>427</v>
       </c>
       <c r="E11">
-        <v>846</v>
+        <v>450</v>
       </c>
       <c r="F11">
-        <v>718</v>
+        <v>388</v>
       </c>
       <c r="G11">
-        <v>519</v>
+        <v>284</v>
       </c>
       <c r="H11">
-        <v>501</v>
+        <v>324</v>
       </c>
       <c r="I11">
-        <v>727</v>
+        <v>346</v>
       </c>
       <c r="J11">
-        <v>845</v>
+        <v>418</v>
       </c>
       <c r="K11">
-        <v>936</v>
+        <v>490</v>
       </c>
       <c r="L11">
-        <v>803</v>
+        <v>427</v>
       </c>
       <c r="M11">
-        <v>523</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -42811,40 +42865,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42852,77 +42906,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -42931,40 +42967,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K5">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42972,81 +43008,60 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43054,40 +43069,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="I8">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="J8">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="K8">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="L8">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="M8">
-        <v>102</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43095,40 +43110,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9">
         <v>29</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43136,40 +43151,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>180</v>
+        <v>632</v>
       </c>
       <c r="C10">
-        <v>215</v>
+        <v>762</v>
       </c>
       <c r="D10">
-        <v>184</v>
+        <v>938</v>
       </c>
       <c r="E10">
-        <v>140</v>
+        <v>859</v>
       </c>
       <c r="F10">
-        <v>137</v>
+        <v>913</v>
       </c>
       <c r="G10">
-        <v>126</v>
+        <v>398</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>413</v>
       </c>
       <c r="I10">
-        <v>192</v>
+        <v>716</v>
       </c>
       <c r="J10">
-        <v>269</v>
+        <v>690</v>
       </c>
       <c r="K10">
-        <v>193</v>
+        <v>724</v>
       </c>
       <c r="L10">
-        <v>218</v>
+        <v>660</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43177,40 +43192,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>385</v>
+        <v>721</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>927</v>
       </c>
       <c r="D11">
-        <v>397</v>
+        <v>1129</v>
       </c>
       <c r="E11">
-        <v>354</v>
+        <v>1075</v>
       </c>
       <c r="F11">
-        <v>298</v>
+        <v>1141</v>
       </c>
       <c r="G11">
-        <v>290</v>
+        <v>616</v>
       </c>
       <c r="H11">
-        <v>326</v>
+        <v>689</v>
       </c>
       <c r="I11">
-        <v>434</v>
+        <v>1063</v>
       </c>
       <c r="J11">
-        <v>592</v>
+        <v>997</v>
       </c>
       <c r="K11">
-        <v>554</v>
+        <v>1009</v>
       </c>
       <c r="L11">
-        <v>580</v>
+        <v>902</v>
       </c>
       <c r="M11">
-        <v>356</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -43284,40 +43299,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="K2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43325,40 +43340,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="L3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43366,31 +43381,40 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -43398,40 +43422,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>71</v>
+      </c>
+      <c r="D5">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>38</v>
+      </c>
+      <c r="J5">
         <v>30</v>
       </c>
-      <c r="C5">
-        <v>44</v>
-      </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-      <c r="E5">
-        <v>35</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
-      <c r="H5">
-        <v>31</v>
-      </c>
-      <c r="I5">
-        <v>19</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
       <c r="K5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L5">
+        <v>13</v>
+      </c>
+      <c r="M5">
         <v>18</v>
-      </c>
-      <c r="M5">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43442,69 +43466,78 @@
         <v>3</v>
       </c>
       <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
         <v>6</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
       </c>
       <c r="I6">
         <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>3</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43512,40 +43545,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>52</v>
+      </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
         <v>42</v>
       </c>
-      <c r="D8">
-        <v>47</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>37</v>
-      </c>
-      <c r="G8">
-        <v>44</v>
-      </c>
       <c r="H8">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I8">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="J8">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L8">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43553,40 +43586,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E9">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
         <v>21</v>
       </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
       <c r="I9">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J9">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K9">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43594,40 +43627,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>270</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>297</v>
+        <v>169</v>
       </c>
       <c r="F10">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="G10">
+        <v>112</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10">
+        <v>131</v>
+      </c>
+      <c r="J10">
+        <v>154</v>
+      </c>
+      <c r="K10">
+        <v>148</v>
+      </c>
+      <c r="L10">
         <v>133</v>
       </c>
-      <c r="H10">
-        <v>143</v>
-      </c>
-      <c r="I10">
-        <v>149</v>
-      </c>
-      <c r="J10">
-        <v>195</v>
-      </c>
-      <c r="K10">
-        <v>275</v>
-      </c>
-      <c r="L10">
-        <v>265</v>
-      </c>
       <c r="M10">
-        <v>180</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43635,40 +43668,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="D11">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="E11">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="F11">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G11">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="H11">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="I11">
-        <v>346</v>
+        <v>466</v>
       </c>
       <c r="J11">
-        <v>418</v>
+        <v>528</v>
       </c>
       <c r="K11">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="L11">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="M11">
-        <v>313</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -43678,7 +43711,7 @@
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -43745,37 +43778,37 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>16</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43783,326 +43816,309 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="E4">
+        <v>6</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>19</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>23</v>
-      </c>
-      <c r="G5">
-        <v>56</v>
-      </c>
-      <c r="H5">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
       <c r="J5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>39</v>
-      </c>
-      <c r="G6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="J8">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="K8">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="L8">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>632</v>
+        <v>106</v>
       </c>
       <c r="C10">
-        <v>762</v>
+        <v>79</v>
       </c>
       <c r="D10">
-        <v>938</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>859</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>913</v>
+        <v>86</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>94</v>
       </c>
       <c r="H10">
-        <v>413</v>
+        <v>141</v>
       </c>
       <c r="I10">
-        <v>716</v>
+        <v>182</v>
       </c>
       <c r="J10">
-        <v>690</v>
+        <v>155</v>
       </c>
       <c r="K10">
-        <v>724</v>
+        <v>170</v>
       </c>
       <c r="L10">
-        <v>660</v>
+        <v>141</v>
       </c>
       <c r="M10">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>721</v>
-      </c>
-      <c r="C11">
-        <v>927</v>
-      </c>
-      <c r="D11">
-        <v>1129</v>
-      </c>
-      <c r="E11">
-        <v>1075</v>
-      </c>
-      <c r="F11">
-        <v>1141</v>
-      </c>
-      <c r="G11">
-        <v>616</v>
-      </c>
-      <c r="H11">
-        <v>689</v>
-      </c>
-      <c r="I11">
-        <v>1063</v>
-      </c>
-      <c r="J11">
-        <v>997</v>
-      </c>
-      <c r="K11">
-        <v>1009</v>
-      </c>
-      <c r="L11">
-        <v>902</v>
-      </c>
-      <c r="M11">
-        <v>683</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -44176,81 +44192,69 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39</v>
-      </c>
-      <c r="C2">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>47</v>
-      </c>
-      <c r="G2">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>53</v>
-      </c>
       <c r="C3">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -44258,40 +44262,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -44299,40 +44270,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44340,81 +44302,45 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
       <c r="E6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
       <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -44422,40 +44348,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44463,40 +44386,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44504,40 +44427,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="D10">
-        <v>149</v>
+        <v>445</v>
       </c>
       <c r="E10">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="F10">
-        <v>157</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>127</v>
+        <v>321</v>
       </c>
       <c r="I10">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="J10">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K10">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="L10">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M10">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44545,40 +44468,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>368</v>
+        <v>220</v>
       </c>
       <c r="C11">
-        <v>412</v>
+        <v>364</v>
       </c>
       <c r="D11">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="E11">
-        <v>414</v>
+        <v>328</v>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>340</v>
       </c>
       <c r="G11">
-        <v>330</v>
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="I11">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="J11">
-        <v>528</v>
+        <v>203</v>
       </c>
       <c r="K11">
-        <v>448</v>
+        <v>201</v>
       </c>
       <c r="L11">
-        <v>374</v>
+        <v>143</v>
       </c>
       <c r="M11">
-        <v>289</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -44588,7 +44511,7 @@
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -44652,40 +44575,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>16</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -44693,115 +44616,70 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
       <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -44810,192 +44688,188 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
+      <c r="J6">
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>34</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="M9">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>110</v>
+      </c>
+      <c r="C10">
+        <v>87</v>
+      </c>
+      <c r="D10">
+        <v>69</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>39</v>
+      </c>
+      <c r="J10">
+        <v>56</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>36</v>
+      </c>
+      <c r="M10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>106</v>
-      </c>
-      <c r="C10">
-        <v>79</v>
-      </c>
-      <c r="D10">
-        <v>73</v>
-      </c>
-      <c r="E10">
-        <v>117</v>
-      </c>
-      <c r="F10">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>94</v>
-      </c>
-      <c r="H10">
-        <v>141</v>
-      </c>
-      <c r="I10">
-        <v>182</v>
-      </c>
-      <c r="J10">
-        <v>155</v>
-      </c>
-      <c r="K10">
-        <v>170</v>
-      </c>
-      <c r="L10">
-        <v>141</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
+      <c r="B11">
+        <v>123</v>
+      </c>
+      <c r="C11">
+        <v>97</v>
+      </c>
+      <c r="D11">
+        <v>89</v>
+      </c>
+      <c r="E11">
+        <v>44</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
+      </c>
+      <c r="G11">
+        <v>23</v>
+      </c>
+      <c r="H11">
+        <v>27</v>
+      </c>
+      <c r="I11">
+        <v>56</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+      <c r="K11">
+        <v>76</v>
+      </c>
+      <c r="L11">
+        <v>61</v>
+      </c>
+      <c r="M11">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -45069,76 +44943,97 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
         <v>4</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -45147,31 +45042,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
         <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45179,19 +45083,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -45200,12 +45104,12 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -45213,10 +45117,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="I7">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -45225,37 +45126,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45263,40 +45167,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
         <v>7</v>
       </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
       <c r="M9">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45304,40 +45208,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="D10">
-        <v>445</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>307</v>
+        <v>188</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="I10">
-        <v>367</v>
+        <v>226</v>
       </c>
       <c r="J10">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="K10">
-        <v>167</v>
+        <v>295</v>
       </c>
       <c r="L10">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="M10">
-        <v>94</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45345,40 +45249,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C11">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="D11">
-        <v>474</v>
+        <v>270</v>
       </c>
       <c r="E11">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="F11">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="G11">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>338</v>
+        <v>198</v>
       </c>
       <c r="I11">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="J11">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>143</v>
+        <v>309</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -45931,37 +45835,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
         <v>4</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45969,44 +45870,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -46015,61 +45919,94 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
       </c>
       <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
       <c r="C6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -46078,31 +46015,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46110,37 +46056,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
+        <v>23</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
         <v>3</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46148,40 +46097,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>256</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>262</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="I10">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="J10">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="K10">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="L10">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46189,40 +46138,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="C11">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="D11">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>342</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="G11">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="H11">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="I11">
-        <v>56</v>
+        <v>236</v>
       </c>
       <c r="J11">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="K11">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="L11">
-        <v>61</v>
+        <v>323</v>
       </c>
       <c r="M11">
-        <v>50</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -46296,40 +46245,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>11</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46337,54 +46286,63 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -46395,40 +46353,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>32</v>
+      </c>
+      <c r="J5">
         <v>9</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
-      </c>
       <c r="K5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>8</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46436,42 +46394,60 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="D6">
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46479,40 +46455,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46520,40 +46496,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>15</v>
+      </c>
+      <c r="L9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>15</v>
-      </c>
-      <c r="K9">
-        <v>16</v>
-      </c>
-      <c r="L9">
-        <v>7</v>
-      </c>
       <c r="M9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46561,40 +46537,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>213</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>188</v>
+        <v>67</v>
       </c>
       <c r="F10">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="K10">
-        <v>295</v>
+        <v>37</v>
       </c>
       <c r="L10">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="M10">
-        <v>172</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46602,40 +46578,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>164</v>
       </c>
       <c r="D11">
-        <v>270</v>
+        <v>145</v>
       </c>
       <c r="E11">
-        <v>237</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="G11">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="H11">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="I11">
-        <v>308</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="K11">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="L11">
-        <v>309</v>
+        <v>128</v>
       </c>
       <c r="M11">
-        <v>202</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -46709,37 +46685,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>41</v>
+      </c>
+      <c r="L2">
+        <v>44</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46747,48 +46726,78 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -46796,40 +46805,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46837,54 +46846,72 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
       <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46892,40 +46919,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46933,40 +46960,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F9">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>59</v>
+      </c>
+      <c r="I9">
+        <v>50</v>
+      </c>
+      <c r="J9">
+        <v>61</v>
+      </c>
+      <c r="K9">
+        <v>47</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
         <v>16</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>23</v>
-      </c>
-      <c r="K9">
-        <v>23</v>
-      </c>
-      <c r="L9">
-        <v>12</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46974,40 +47001,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="C10">
-        <v>260</v>
+        <v>394</v>
       </c>
       <c r="D10">
-        <v>256</v>
+        <v>372</v>
       </c>
       <c r="E10">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="F10">
-        <v>211</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="H10">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I10">
-        <v>175</v>
+        <v>372</v>
       </c>
       <c r="J10">
-        <v>199</v>
+        <v>319</v>
       </c>
       <c r="K10">
-        <v>256</v>
+        <v>369</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>427</v>
       </c>
       <c r="M10">
-        <v>148</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47015,40 +47042,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>255</v>
+        <v>713</v>
       </c>
       <c r="C11">
-        <v>323</v>
+        <v>714</v>
       </c>
       <c r="D11">
-        <v>311</v>
+        <v>697</v>
       </c>
       <c r="E11">
-        <v>342</v>
+        <v>616</v>
       </c>
       <c r="F11">
-        <v>261</v>
+        <v>568</v>
       </c>
       <c r="G11">
-        <v>197</v>
+        <v>492</v>
       </c>
       <c r="H11">
-        <v>233</v>
+        <v>474</v>
       </c>
       <c r="I11">
-        <v>236</v>
+        <v>722</v>
       </c>
       <c r="J11">
-        <v>268</v>
+        <v>739</v>
       </c>
       <c r="K11">
-        <v>337</v>
+        <v>720</v>
       </c>
       <c r="L11">
-        <v>323</v>
+        <v>728</v>
       </c>
       <c r="M11">
-        <v>190</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -47122,40 +47149,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
         <v>12</v>
       </c>
-      <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2">
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
         <v>17</v>
       </c>
-      <c r="G2">
-        <v>9</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
       <c r="K2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47163,40 +47190,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47210,18 +47237,9 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -47230,37 +47248,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>18</v>
       </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>32</v>
-      </c>
       <c r="J5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
         <v>15</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -47271,60 +47289,42 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47332,40 +47332,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L8">
         <v>26</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47373,40 +47373,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
       <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
         <v>6</v>
       </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9">
-        <v>15</v>
-      </c>
-      <c r="L9">
-        <v>9</v>
-      </c>
       <c r="M9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47414,40 +47414,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="J10">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47455,40 +47455,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="D11">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="E11">
+        <v>186</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11">
+        <v>112</v>
+      </c>
+      <c r="H11">
+        <v>125</v>
+      </c>
+      <c r="I11">
         <v>160</v>
       </c>
-      <c r="F11">
-        <v>142</v>
-      </c>
-      <c r="G11">
-        <v>126</v>
-      </c>
-      <c r="H11">
-        <v>130</v>
-      </c>
-      <c r="I11">
-        <v>175</v>
-      </c>
       <c r="J11">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="K11">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="L11">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="M11">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -47562,40 +47562,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="L2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47603,40 +47603,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C3">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3">
+        <v>33</v>
+      </c>
+      <c r="J3">
+        <v>36</v>
+      </c>
+      <c r="K3">
         <v>41</v>
       </c>
-      <c r="D3">
+      <c r="L3">
         <v>32</v>
       </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>44</v>
-      </c>
-      <c r="G3">
-        <v>35</v>
-      </c>
-      <c r="H3">
-        <v>31</v>
-      </c>
-      <c r="I3">
-        <v>36</v>
-      </c>
-      <c r="J3">
-        <v>30</v>
-      </c>
-      <c r="K3">
-        <v>31</v>
-      </c>
-      <c r="L3">
-        <v>22</v>
-      </c>
       <c r="M3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47644,34 +47644,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -47682,40 +47685,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="D5">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H5">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="M5">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -47723,40 +47726,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
+      <c r="M6">
         <v>5</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -47764,31 +47767,37 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47796,40 +47805,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D8">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="F8">
+        <v>52</v>
+      </c>
+      <c r="G8">
         <v>35</v>
       </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
       <c r="H8">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="I8">
+        <v>140</v>
+      </c>
+      <c r="J8">
+        <v>242</v>
+      </c>
+      <c r="K8">
+        <v>339</v>
+      </c>
+      <c r="L8">
+        <v>141</v>
+      </c>
+      <c r="M8">
         <v>110</v>
-      </c>
-      <c r="J8">
-        <v>171</v>
-      </c>
-      <c r="K8">
-        <v>143</v>
-      </c>
-      <c r="L8">
-        <v>122</v>
-      </c>
-      <c r="M8">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47837,40 +47846,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47878,40 +47887,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C10">
-        <v>394</v>
+        <v>492</v>
       </c>
       <c r="D10">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E10">
-        <v>305</v>
+        <v>489</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>489</v>
       </c>
       <c r="G10">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H10">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="I10">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="J10">
-        <v>319</v>
+        <v>502</v>
       </c>
       <c r="K10">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="L10">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="M10">
-        <v>327</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47919,40 +47928,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>713</v>
+        <v>654</v>
       </c>
       <c r="C11">
-        <v>714</v>
+        <v>876</v>
       </c>
       <c r="D11">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="E11">
-        <v>616</v>
+        <v>789</v>
       </c>
       <c r="F11">
-        <v>568</v>
+        <v>728</v>
       </c>
       <c r="G11">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H11">
-        <v>474</v>
+        <v>565</v>
       </c>
       <c r="I11">
-        <v>722</v>
+        <v>767</v>
       </c>
       <c r="J11">
-        <v>739</v>
+        <v>949</v>
       </c>
       <c r="K11">
-        <v>720</v>
+        <v>973</v>
       </c>
       <c r="L11">
-        <v>728</v>
+        <v>703</v>
       </c>
       <c r="M11">
-        <v>525</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -48026,40 +48035,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>19</v>
-      </c>
       <c r="I2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48067,59 +48073,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48128,34 +48131,34 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>26</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48168,72 +48171,48 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48242,40 +48221,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>18</v>
       </c>
-      <c r="E8">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>88</v>
-      </c>
-      <c r="K8">
-        <v>46</v>
-      </c>
-      <c r="L8">
-        <v>50</v>
-      </c>
       <c r="M8">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48283,40 +48262,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="H9">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>38</v>
-      </c>
       <c r="L9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48324,40 +48303,40 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <v>192</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>142</v>
+      </c>
+      <c r="E10">
+        <v>135</v>
+      </c>
+      <c r="F10">
+        <v>184</v>
+      </c>
+      <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
         <v>112</v>
       </c>
-      <c r="C10">
-        <v>108</v>
-      </c>
-      <c r="D10">
-        <v>119</v>
-      </c>
-      <c r="E10">
-        <v>133</v>
-      </c>
-      <c r="F10">
-        <v>146</v>
-      </c>
-      <c r="G10">
-        <v>68</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
       <c r="I10">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="K10">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="L10">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="M10">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48365,40 +48344,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="C11">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="E11">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F11">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H11">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="I11">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J11">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="K11">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="L11">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M11">
-        <v>205</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -48472,37 +48451,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48510,56 +48492,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48568,34 +48553,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
       <c r="H5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
         <v>13</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48608,48 +48593,72 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48658,40 +48667,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J8">
+        <v>88</v>
+      </c>
+      <c r="K8">
+        <v>46</v>
+      </c>
+      <c r="L8">
+        <v>50</v>
+      </c>
+      <c r="M8">
         <v>38</v>
-      </c>
-      <c r="K8">
-        <v>42</v>
-      </c>
-      <c r="L8">
-        <v>18</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48699,40 +48708,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
       <c r="G9">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48740,40 +48749,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="C10">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="D10">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="J10">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="L10">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="M10">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48781,40 +48790,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="C11">
+        <v>227</v>
+      </c>
+      <c r="D11">
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>248</v>
+      </c>
+      <c r="F11">
+        <v>249</v>
+      </c>
+      <c r="G11">
+        <v>169</v>
+      </c>
+      <c r="H11">
+        <v>193</v>
+      </c>
+      <c r="I11">
+        <v>251</v>
+      </c>
+      <c r="J11">
         <v>291</v>
       </c>
-      <c r="D11">
-        <v>212</v>
-      </c>
-      <c r="E11">
-        <v>216</v>
-      </c>
-      <c r="F11">
-        <v>247</v>
-      </c>
-      <c r="G11">
-        <v>155</v>
-      </c>
-      <c r="H11">
-        <v>179</v>
-      </c>
-      <c r="I11">
-        <v>238</v>
-      </c>
-      <c r="J11">
-        <v>318</v>
-      </c>
       <c r="K11">
-        <v>347</v>
+        <v>251</v>
       </c>
       <c r="L11">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="M11">
-        <v>176</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -48888,40 +48897,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>17</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
       <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48929,37 +48935,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -48969,16 +48975,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -48990,37 +48996,37 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
       <c r="M5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49028,41 +49034,38 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -49071,40 +49074,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
       <c r="I8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49112,37 +49115,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <v>4</v>
       </c>
-      <c r="H9">
-        <v>15</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
       <c r="K9">
-        <v>4</v>
-      </c>
-      <c r="L9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -49153,40 +49153,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="M10">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49194,40 +49194,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="J11">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="K11">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="L11">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -49301,37 +49301,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49339,56 +49342,44 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -49397,40 +49388,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>16</v>
       </c>
-      <c r="C5">
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
       <c r="K5">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49438,16 +49429,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -49458,10 +49446,10 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -49469,7 +49457,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -49478,40 +49466,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8">
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>37</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>23</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>8</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49519,37 +49507,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49557,40 +49548,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="G10">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="H10">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="K10">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="L10">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="M10">
-        <v>20</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49598,40 +49589,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="C11">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="D11">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="F11">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="H11">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="I11">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="J11">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="L11">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="M11">
-        <v>29</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -49705,40 +49696,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49746,45 +49737,54 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
         <v>5</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="M3">
         <v>5</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -49792,40 +49792,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49833,35 +49833,38 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>1</v>
+      <c r="L6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -49870,40 +49873,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>14</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J8">
         <v>37</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49911,39 +49914,36 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
       <c r="E9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
         <v>7</v>
       </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
       <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
         <v>3</v>
       </c>
     </row>
@@ -49952,40 +49952,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="E10">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F10">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G10">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="J10">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="K10">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="L10">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="M10">
-        <v>88</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49993,40 +49993,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="C11">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D11">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="F11">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G11">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="I11">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="J11">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="K11">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="L11">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="M11">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -86,26 +86,26 @@
     <sheet name="North Park" sheetId="77" r:id="rId77"/>
     <sheet name="Chinatown" sheetId="78" r:id="rId78"/>
     <sheet name="Beverly" sheetId="79" r:id="rId79"/>
-    <sheet name="Sauganash,Forest Glen" sheetId="80" r:id="rId80"/>
-    <sheet name="Garfield Ridge" sheetId="81" r:id="rId81"/>
+    <sheet name="West Lawn" sheetId="80" r:id="rId80"/>
+    <sheet name="East Side" sheetId="81" r:id="rId81"/>
     <sheet name="Rush &amp; Division" sheetId="82" r:id="rId82"/>
-    <sheet name="West Lawn" sheetId="83" r:id="rId83"/>
-    <sheet name="East Side" sheetId="84" r:id="rId84"/>
-    <sheet name="Pullman" sheetId="85" r:id="rId85"/>
-    <sheet name="Streeterville" sheetId="86" r:id="rId86"/>
-    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
-    <sheet name="Jackson Park" sheetId="88" r:id="rId88"/>
-    <sheet name="Millenium Park" sheetId="89" r:id="rId89"/>
-    <sheet name="Museum Campus" sheetId="90" r:id="rId90"/>
-    <sheet name="Printers Row" sheetId="91" r:id="rId91"/>
-    <sheet name="Gold Coast" sheetId="92" r:id="rId92"/>
-    <sheet name="Burnside" sheetId="93" r:id="rId93"/>
-    <sheet name="Bridgeport" sheetId="94" r:id="rId94"/>
-    <sheet name="Armour Square" sheetId="95" r:id="rId95"/>
-    <sheet name="Wrigleyville" sheetId="96" r:id="rId96"/>
-    <sheet name="Mount Greenwood" sheetId="97" r:id="rId97"/>
-    <sheet name="Edison Park" sheetId="98" r:id="rId98"/>
-    <sheet name="Andersonville" sheetId="99" r:id="rId99"/>
+    <sheet name="Pullman" sheetId="83" r:id="rId83"/>
+    <sheet name="Streeterville" sheetId="84" r:id="rId84"/>
+    <sheet name="Riverdale" sheetId="85" r:id="rId85"/>
+    <sheet name="Jackson Park" sheetId="86" r:id="rId86"/>
+    <sheet name="Millenium Park" sheetId="87" r:id="rId87"/>
+    <sheet name="Museum Campus" sheetId="88" r:id="rId88"/>
+    <sheet name="Printers Row" sheetId="89" r:id="rId89"/>
+    <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
+    <sheet name="Burnside" sheetId="91" r:id="rId91"/>
+    <sheet name="Bridgeport" sheetId="92" r:id="rId92"/>
+    <sheet name="Mount Greenwood" sheetId="93" r:id="rId93"/>
+    <sheet name="Garfield Ridge" sheetId="94" r:id="rId94"/>
+    <sheet name="Wrigleyville" sheetId="95" r:id="rId95"/>
+    <sheet name="Armour Square" sheetId="96" r:id="rId96"/>
+    <sheet name="Edison Park" sheetId="97" r:id="rId97"/>
+    <sheet name="Andersonville" sheetId="98" r:id="rId98"/>
+    <sheet name="Sauganash,Forest Glen" sheetId="99" r:id="rId99"/>
     <sheet name="Grant Park" sheetId="100" r:id="rId100"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41048,40 +41048,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41089,53 +41089,77 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
       <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -41144,40 +41168,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>64</v>
+      </c>
+      <c r="J5">
+        <v>92</v>
+      </c>
+      <c r="K5">
+        <v>66</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
         <v>36</v>
-      </c>
-      <c r="I5">
-        <v>40</v>
-      </c>
-      <c r="J5">
-        <v>39</v>
-      </c>
-      <c r="K5">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>25</v>
-      </c>
-      <c r="M5">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41185,39 +41209,72 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
       <c r="J7">
         <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41225,40 +41282,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>271</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41266,37 +41323,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="M9">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41304,40 +41364,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>119</v>
+        <v>641</v>
       </c>
       <c r="C10">
-        <v>146</v>
+        <v>540</v>
       </c>
       <c r="D10">
-        <v>152</v>
+        <v>482</v>
       </c>
       <c r="E10">
-        <v>152</v>
+        <v>485</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>443</v>
       </c>
       <c r="G10">
-        <v>103</v>
+        <v>310</v>
       </c>
       <c r="H10">
-        <v>88</v>
+        <v>248</v>
       </c>
       <c r="I10">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="J10">
-        <v>151</v>
+        <v>360</v>
       </c>
       <c r="K10">
-        <v>146</v>
+        <v>479</v>
       </c>
       <c r="L10">
-        <v>117</v>
+        <v>486</v>
       </c>
       <c r="M10">
-        <v>56</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41345,40 +41405,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>194</v>
+        <v>1023</v>
       </c>
       <c r="C11">
-        <v>271</v>
+        <v>1021</v>
       </c>
       <c r="D11">
-        <v>245</v>
+        <v>860</v>
       </c>
       <c r="E11">
-        <v>246</v>
+        <v>846</v>
       </c>
       <c r="F11">
-        <v>186</v>
+        <v>718</v>
       </c>
       <c r="G11">
-        <v>183</v>
+        <v>519</v>
       </c>
       <c r="H11">
-        <v>156</v>
+        <v>501</v>
       </c>
       <c r="I11">
-        <v>222</v>
+        <v>727</v>
       </c>
       <c r="J11">
-        <v>256</v>
+        <v>845</v>
       </c>
       <c r="K11">
-        <v>243</v>
+        <v>936</v>
       </c>
       <c r="L11">
-        <v>187</v>
+        <v>803</v>
       </c>
       <c r="M11">
-        <v>97</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -41452,40 +41512,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L2">
         <v>42</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41493,40 +41553,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C3">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
         <v>28</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>33</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>36</v>
-      </c>
-      <c r="K3">
-        <v>41</v>
-      </c>
-      <c r="L3">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41534,39 +41594,36 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
       <c r="L4">
-        <v>6</v>
-      </c>
-      <c r="M4">
         <v>2</v>
       </c>
     </row>
@@ -41575,40 +41632,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="E5">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="K5">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L5">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41616,37 +41673,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -41657,37 +41714,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="D7">
+      <c r="J7">
         <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41695,40 +41755,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F8">
+        <v>39</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8">
         <v>52</v>
       </c>
-      <c r="G8">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>70</v>
-      </c>
       <c r="I8">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="J8">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="K8">
-        <v>339</v>
+        <v>174</v>
       </c>
       <c r="L8">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="M8">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41736,40 +41796,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
         <v>39</v>
       </c>
-      <c r="H9">
-        <v>52</v>
-      </c>
-      <c r="I9">
-        <v>24</v>
-      </c>
       <c r="J9">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K9">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41777,40 +41837,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>395</v>
+        <v>180</v>
       </c>
       <c r="C10">
-        <v>492</v>
+        <v>215</v>
       </c>
       <c r="D10">
-        <v>381</v>
+        <v>184</v>
       </c>
       <c r="E10">
-        <v>489</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>489</v>
+        <v>137</v>
       </c>
       <c r="G10">
-        <v>276</v>
+        <v>126</v>
       </c>
       <c r="H10">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="I10">
-        <v>445</v>
+        <v>192</v>
       </c>
       <c r="J10">
-        <v>502</v>
+        <v>269</v>
       </c>
       <c r="K10">
-        <v>411</v>
+        <v>193</v>
       </c>
       <c r="L10">
-        <v>386</v>
+        <v>218</v>
       </c>
       <c r="M10">
-        <v>233</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41818,40 +41878,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>654</v>
+        <v>385</v>
       </c>
       <c r="C11">
-        <v>876</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>743</v>
+        <v>397</v>
       </c>
       <c r="E11">
-        <v>789</v>
+        <v>354</v>
       </c>
       <c r="F11">
-        <v>728</v>
+        <v>298</v>
       </c>
       <c r="G11">
-        <v>491</v>
+        <v>290</v>
       </c>
       <c r="H11">
-        <v>565</v>
+        <v>326</v>
       </c>
       <c r="I11">
-        <v>767</v>
+        <v>434</v>
       </c>
       <c r="J11">
-        <v>949</v>
+        <v>592</v>
       </c>
       <c r="K11">
-        <v>973</v>
+        <v>554</v>
       </c>
       <c r="L11">
-        <v>703</v>
+        <v>580</v>
       </c>
       <c r="M11">
-        <v>460</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -42347,40 +42407,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K2">
         <v>35</v>
       </c>
       <c r="L2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42388,40 +42448,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>31</v>
+      </c>
+      <c r="F3">
         <v>29</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>36</v>
+      </c>
+      <c r="H3">
+        <v>31</v>
+      </c>
+      <c r="I3">
+        <v>24</v>
+      </c>
+      <c r="J3">
         <v>28</v>
       </c>
-      <c r="F3">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <v>33</v>
-      </c>
-      <c r="H3">
-        <v>34</v>
-      </c>
-      <c r="I3">
-        <v>37</v>
-      </c>
-      <c r="J3">
-        <v>37</v>
-      </c>
       <c r="K3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42429,13 +42489,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -42446,20 +42503,17 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -42467,40 +42521,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="J5">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="K5">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42508,40 +42562,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
       <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
       <c r="J6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -42549,31 +42603,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -42581,40 +42635,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G8">
+        <v>44</v>
+      </c>
+      <c r="H8">
         <v>48</v>
       </c>
-      <c r="H8">
-        <v>63</v>
-      </c>
       <c r="I8">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="J8">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="K8">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="L8">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="M8">
-        <v>129</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42622,40 +42676,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -42663,40 +42717,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>641</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>540</v>
+        <v>250</v>
       </c>
       <c r="D10">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="E10">
-        <v>485</v>
+        <v>297</v>
       </c>
       <c r="F10">
-        <v>443</v>
+        <v>226</v>
       </c>
       <c r="G10">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="H10">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="I10">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="J10">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="K10">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="L10">
-        <v>486</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>279</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42704,40 +42758,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1023</v>
+        <v>359</v>
       </c>
       <c r="C11">
-        <v>1021</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>860</v>
+        <v>427</v>
       </c>
       <c r="E11">
-        <v>846</v>
+        <v>450</v>
       </c>
       <c r="F11">
-        <v>718</v>
+        <v>388</v>
       </c>
       <c r="G11">
-        <v>519</v>
+        <v>284</v>
       </c>
       <c r="H11">
-        <v>501</v>
+        <v>324</v>
       </c>
       <c r="I11">
-        <v>727</v>
+        <v>346</v>
       </c>
       <c r="J11">
-        <v>845</v>
+        <v>418</v>
       </c>
       <c r="K11">
-        <v>936</v>
+        <v>490</v>
       </c>
       <c r="L11">
-        <v>803</v>
+        <v>427</v>
       </c>
       <c r="M11">
-        <v>524</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -42811,40 +42865,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42852,77 +42906,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -42931,40 +42967,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K5">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42972,81 +43008,60 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43054,40 +43069,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="I8">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="J8">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="K8">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="L8">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43095,40 +43110,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9">
         <v>29</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43136,40 +43151,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>180</v>
+        <v>632</v>
       </c>
       <c r="C10">
-        <v>215</v>
+        <v>762</v>
       </c>
       <c r="D10">
-        <v>184</v>
+        <v>938</v>
       </c>
       <c r="E10">
-        <v>140</v>
+        <v>859</v>
       </c>
       <c r="F10">
-        <v>137</v>
+        <v>913</v>
       </c>
       <c r="G10">
-        <v>126</v>
+        <v>398</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>413</v>
       </c>
       <c r="I10">
-        <v>192</v>
+        <v>716</v>
       </c>
       <c r="J10">
-        <v>269</v>
+        <v>690</v>
       </c>
       <c r="K10">
-        <v>193</v>
+        <v>724</v>
       </c>
       <c r="L10">
-        <v>218</v>
+        <v>660</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43177,40 +43192,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>385</v>
+        <v>721</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>927</v>
       </c>
       <c r="D11">
-        <v>397</v>
+        <v>1129</v>
       </c>
       <c r="E11">
-        <v>354</v>
+        <v>1075</v>
       </c>
       <c r="F11">
-        <v>298</v>
+        <v>1141</v>
       </c>
       <c r="G11">
-        <v>290</v>
+        <v>616</v>
       </c>
       <c r="H11">
-        <v>326</v>
+        <v>689</v>
       </c>
       <c r="I11">
-        <v>434</v>
+        <v>1063</v>
       </c>
       <c r="J11">
-        <v>592</v>
+        <v>997</v>
       </c>
       <c r="K11">
-        <v>554</v>
+        <v>1009</v>
       </c>
       <c r="L11">
-        <v>580</v>
+        <v>902</v>
       </c>
       <c r="M11">
-        <v>357</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -43284,40 +43299,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="K2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43325,40 +43340,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="L3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43366,31 +43381,40 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -43398,40 +43422,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>71</v>
+      </c>
+      <c r="D5">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>38</v>
+      </c>
+      <c r="J5">
         <v>30</v>
       </c>
-      <c r="C5">
-        <v>44</v>
-      </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-      <c r="E5">
-        <v>35</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
-      <c r="H5">
-        <v>31</v>
-      </c>
-      <c r="I5">
-        <v>19</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
       <c r="K5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L5">
+        <v>13</v>
+      </c>
+      <c r="M5">
         <v>18</v>
-      </c>
-      <c r="M5">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43442,69 +43466,78 @@
         <v>3</v>
       </c>
       <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
         <v>6</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
       </c>
       <c r="I6">
         <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>3</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43512,40 +43545,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>52</v>
+      </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
         <v>42</v>
       </c>
-      <c r="D8">
-        <v>47</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>37</v>
-      </c>
-      <c r="G8">
-        <v>44</v>
-      </c>
       <c r="H8">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I8">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="J8">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L8">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43553,40 +43586,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E9">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
         <v>21</v>
       </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
       <c r="I9">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J9">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K9">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43594,40 +43627,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>270</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>297</v>
+        <v>169</v>
       </c>
       <c r="F10">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="G10">
+        <v>112</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10">
+        <v>131</v>
+      </c>
+      <c r="J10">
+        <v>154</v>
+      </c>
+      <c r="K10">
+        <v>148</v>
+      </c>
+      <c r="L10">
         <v>133</v>
       </c>
-      <c r="H10">
-        <v>143</v>
-      </c>
-      <c r="I10">
-        <v>149</v>
-      </c>
-      <c r="J10">
-        <v>195</v>
-      </c>
-      <c r="K10">
-        <v>275</v>
-      </c>
-      <c r="L10">
-        <v>265</v>
-      </c>
       <c r="M10">
-        <v>180</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43635,40 +43668,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="D11">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="E11">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="F11">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G11">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="H11">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="I11">
-        <v>346</v>
+        <v>466</v>
       </c>
       <c r="J11">
-        <v>418</v>
+        <v>528</v>
       </c>
       <c r="K11">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="L11">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="M11">
-        <v>314</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -43678,7 +43711,7 @@
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -43745,37 +43778,37 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>16</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43783,326 +43816,309 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="E4">
+        <v>6</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>19</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>23</v>
-      </c>
-      <c r="G5">
-        <v>56</v>
-      </c>
-      <c r="H5">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
       <c r="J5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>39</v>
-      </c>
-      <c r="G6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="J8">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="K8">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="L8">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>632</v>
+        <v>106</v>
       </c>
       <c r="C10">
-        <v>762</v>
+        <v>79</v>
       </c>
       <c r="D10">
-        <v>938</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>859</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>913</v>
+        <v>86</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>94</v>
       </c>
       <c r="H10">
-        <v>413</v>
+        <v>141</v>
       </c>
       <c r="I10">
-        <v>716</v>
+        <v>182</v>
       </c>
       <c r="J10">
-        <v>690</v>
+        <v>155</v>
       </c>
       <c r="K10">
-        <v>724</v>
+        <v>170</v>
       </c>
       <c r="L10">
-        <v>660</v>
+        <v>141</v>
       </c>
       <c r="M10">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>721</v>
-      </c>
-      <c r="C11">
-        <v>927</v>
-      </c>
-      <c r="D11">
-        <v>1129</v>
-      </c>
-      <c r="E11">
-        <v>1075</v>
-      </c>
-      <c r="F11">
-        <v>1141</v>
-      </c>
-      <c r="G11">
-        <v>616</v>
-      </c>
-      <c r="H11">
-        <v>689</v>
-      </c>
-      <c r="I11">
-        <v>1063</v>
-      </c>
-      <c r="J11">
-        <v>997</v>
-      </c>
-      <c r="K11">
-        <v>1009</v>
-      </c>
-      <c r="L11">
-        <v>902</v>
-      </c>
-      <c r="M11">
-        <v>687</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -44176,81 +44192,69 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39</v>
-      </c>
-      <c r="C2">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>47</v>
-      </c>
-      <c r="G2">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>53</v>
-      </c>
       <c r="C3">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -44258,40 +44262,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -44299,40 +44270,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44340,81 +44302,45 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
       <c r="E6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
       <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -44422,40 +44348,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44463,40 +44386,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44504,40 +44427,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="D10">
-        <v>149</v>
+        <v>445</v>
       </c>
       <c r="E10">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="F10">
-        <v>157</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>127</v>
+        <v>321</v>
       </c>
       <c r="I10">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="J10">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K10">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="L10">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M10">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44545,40 +44468,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>368</v>
+        <v>220</v>
       </c>
       <c r="C11">
-        <v>412</v>
+        <v>364</v>
       </c>
       <c r="D11">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="E11">
-        <v>414</v>
+        <v>328</v>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>340</v>
       </c>
       <c r="G11">
-        <v>330</v>
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="I11">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="J11">
-        <v>528</v>
+        <v>203</v>
       </c>
       <c r="K11">
-        <v>448</v>
+        <v>201</v>
       </c>
       <c r="L11">
-        <v>374</v>
+        <v>143</v>
       </c>
       <c r="M11">
-        <v>290</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -44588,7 +44511,7 @@
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -44652,40 +44575,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>16</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -44693,115 +44616,70 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
       <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -44810,192 +44688,188 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
+      <c r="J6">
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>34</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="M9">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>110</v>
+      </c>
+      <c r="C10">
+        <v>87</v>
+      </c>
+      <c r="D10">
+        <v>69</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>39</v>
+      </c>
+      <c r="J10">
+        <v>56</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>36</v>
+      </c>
+      <c r="M10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>106</v>
-      </c>
-      <c r="C10">
-        <v>79</v>
-      </c>
-      <c r="D10">
-        <v>73</v>
-      </c>
-      <c r="E10">
-        <v>117</v>
-      </c>
-      <c r="F10">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>94</v>
-      </c>
-      <c r="H10">
-        <v>141</v>
-      </c>
-      <c r="I10">
-        <v>182</v>
-      </c>
-      <c r="J10">
-        <v>155</v>
-      </c>
-      <c r="K10">
-        <v>170</v>
-      </c>
-      <c r="L10">
-        <v>141</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
+      <c r="B11">
+        <v>123</v>
+      </c>
+      <c r="C11">
+        <v>97</v>
+      </c>
+      <c r="D11">
+        <v>89</v>
+      </c>
+      <c r="E11">
+        <v>44</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
+      </c>
+      <c r="G11">
+        <v>23</v>
+      </c>
+      <c r="H11">
+        <v>27</v>
+      </c>
+      <c r="I11">
+        <v>56</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+      <c r="K11">
+        <v>76</v>
+      </c>
+      <c r="L11">
+        <v>61</v>
+      </c>
+      <c r="M11">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -45069,76 +44943,97 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
         <v>4</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -45147,31 +45042,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
         <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45179,19 +45083,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -45200,12 +45104,12 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -45213,10 +45117,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="I7">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -45225,37 +45126,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45263,40 +45167,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
         <v>7</v>
       </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
       <c r="M9">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45304,40 +45208,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="D10">
-        <v>445</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>307</v>
+        <v>188</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="I10">
-        <v>367</v>
+        <v>226</v>
       </c>
       <c r="J10">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="K10">
-        <v>167</v>
+        <v>295</v>
       </c>
       <c r="L10">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="M10">
-        <v>94</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45345,40 +45249,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C11">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="D11">
-        <v>474</v>
+        <v>270</v>
       </c>
       <c r="E11">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="F11">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="G11">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>338</v>
+        <v>198</v>
       </c>
       <c r="I11">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="J11">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>143</v>
+        <v>309</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -45931,37 +45835,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
         <v>4</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45969,44 +45870,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -46015,61 +45919,94 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
       </c>
       <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
       <c r="C6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -46078,31 +46015,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46110,37 +46056,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
+        <v>23</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
         <v>3</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46148,40 +46097,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>256</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>262</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="I10">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="J10">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="K10">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="L10">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46189,40 +46138,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="C11">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="D11">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>342</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="G11">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="H11">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="I11">
-        <v>56</v>
+        <v>236</v>
       </c>
       <c r="J11">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="K11">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="L11">
-        <v>61</v>
+        <v>323</v>
       </c>
       <c r="M11">
-        <v>53</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -46296,40 +46245,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>11</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46337,54 +46286,63 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
         <v>10</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -46395,40 +46353,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>32</v>
+      </c>
+      <c r="J5">
         <v>9</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
-      </c>
       <c r="K5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>8</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46436,42 +46394,60 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="D6">
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46479,40 +46455,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46520,40 +46496,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>15</v>
+      </c>
+      <c r="L9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>15</v>
-      </c>
-      <c r="K9">
-        <v>16</v>
-      </c>
-      <c r="L9">
-        <v>7</v>
-      </c>
       <c r="M9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46561,40 +46537,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>213</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>188</v>
+        <v>67</v>
       </c>
       <c r="F10">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="K10">
-        <v>295</v>
+        <v>37</v>
       </c>
       <c r="L10">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="M10">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46602,40 +46578,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>164</v>
       </c>
       <c r="D11">
-        <v>270</v>
+        <v>145</v>
       </c>
       <c r="E11">
-        <v>237</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="G11">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="H11">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="I11">
-        <v>308</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="K11">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="L11">
-        <v>309</v>
+        <v>128</v>
       </c>
       <c r="M11">
-        <v>204</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -46709,37 +46685,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>41</v>
+      </c>
+      <c r="L2">
+        <v>44</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46747,48 +46726,78 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -46796,40 +46805,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46837,54 +46846,72 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
       <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46892,40 +46919,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46933,40 +46960,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F9">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>59</v>
+      </c>
+      <c r="I9">
+        <v>50</v>
+      </c>
+      <c r="J9">
+        <v>61</v>
+      </c>
+      <c r="K9">
+        <v>47</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
         <v>16</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>23</v>
-      </c>
-      <c r="K9">
-        <v>23</v>
-      </c>
-      <c r="L9">
-        <v>12</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46974,40 +47001,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="C10">
-        <v>260</v>
+        <v>394</v>
       </c>
       <c r="D10">
-        <v>256</v>
+        <v>372</v>
       </c>
       <c r="E10">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="F10">
-        <v>211</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="H10">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I10">
-        <v>175</v>
+        <v>372</v>
       </c>
       <c r="J10">
-        <v>199</v>
+        <v>319</v>
       </c>
       <c r="K10">
-        <v>256</v>
+        <v>369</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>427</v>
       </c>
       <c r="M10">
-        <v>148</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47015,40 +47042,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>255</v>
+        <v>713</v>
       </c>
       <c r="C11">
-        <v>323</v>
+        <v>714</v>
       </c>
       <c r="D11">
-        <v>311</v>
+        <v>697</v>
       </c>
       <c r="E11">
-        <v>342</v>
+        <v>616</v>
       </c>
       <c r="F11">
-        <v>261</v>
+        <v>568</v>
       </c>
       <c r="G11">
-        <v>197</v>
+        <v>492</v>
       </c>
       <c r="H11">
-        <v>233</v>
+        <v>474</v>
       </c>
       <c r="I11">
-        <v>236</v>
+        <v>722</v>
       </c>
       <c r="J11">
-        <v>268</v>
+        <v>739</v>
       </c>
       <c r="K11">
-        <v>337</v>
+        <v>720</v>
       </c>
       <c r="L11">
-        <v>323</v>
+        <v>728</v>
       </c>
       <c r="M11">
-        <v>190</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -47122,40 +47149,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
         <v>12</v>
       </c>
-      <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2">
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
         <v>17</v>
       </c>
-      <c r="G2">
-        <v>9</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
       <c r="K2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47163,40 +47190,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47210,18 +47237,9 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -47230,37 +47248,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>18</v>
       </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>32</v>
-      </c>
       <c r="J5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
         <v>15</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -47271,60 +47289,42 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47332,40 +47332,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L8">
         <v>26</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47373,40 +47373,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
       <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
         <v>6</v>
       </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9">
-        <v>15</v>
-      </c>
-      <c r="L9">
-        <v>9</v>
-      </c>
       <c r="M9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47414,40 +47414,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="J10">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47455,40 +47455,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="D11">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="E11">
+        <v>186</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11">
+        <v>112</v>
+      </c>
+      <c r="H11">
+        <v>125</v>
+      </c>
+      <c r="I11">
         <v>160</v>
       </c>
-      <c r="F11">
-        <v>142</v>
-      </c>
-      <c r="G11">
-        <v>126</v>
-      </c>
-      <c r="H11">
-        <v>130</v>
-      </c>
-      <c r="I11">
-        <v>175</v>
-      </c>
       <c r="J11">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="K11">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="L11">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="M11">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -47562,40 +47562,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="L2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47603,40 +47603,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C3">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3">
+        <v>33</v>
+      </c>
+      <c r="J3">
+        <v>36</v>
+      </c>
+      <c r="K3">
         <v>41</v>
       </c>
-      <c r="D3">
+      <c r="L3">
         <v>32</v>
       </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>44</v>
-      </c>
-      <c r="G3">
-        <v>35</v>
-      </c>
-      <c r="H3">
-        <v>31</v>
-      </c>
-      <c r="I3">
-        <v>36</v>
-      </c>
-      <c r="J3">
-        <v>30</v>
-      </c>
-      <c r="K3">
-        <v>31</v>
-      </c>
-      <c r="L3">
-        <v>22</v>
-      </c>
       <c r="M3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47644,34 +47644,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -47682,40 +47685,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="D5">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H5">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -47723,40 +47726,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
+      <c r="M6">
         <v>5</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -47764,31 +47767,37 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47796,40 +47805,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D8">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="F8">
+        <v>52</v>
+      </c>
+      <c r="G8">
         <v>35</v>
       </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
       <c r="H8">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="J8">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="K8">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="L8">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="M8">
-        <v>79</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47837,40 +47846,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47878,40 +47887,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C10">
-        <v>394</v>
+        <v>492</v>
       </c>
       <c r="D10">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E10">
-        <v>305</v>
+        <v>489</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>489</v>
       </c>
       <c r="G10">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H10">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="I10">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="J10">
-        <v>319</v>
+        <v>502</v>
       </c>
       <c r="K10">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="L10">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="M10">
-        <v>328</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47919,40 +47928,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>713</v>
+        <v>654</v>
       </c>
       <c r="C11">
-        <v>714</v>
+        <v>876</v>
       </c>
       <c r="D11">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="E11">
-        <v>616</v>
+        <v>789</v>
       </c>
       <c r="F11">
-        <v>568</v>
+        <v>728</v>
       </c>
       <c r="G11">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H11">
-        <v>474</v>
+        <v>565</v>
       </c>
       <c r="I11">
-        <v>722</v>
+        <v>767</v>
       </c>
       <c r="J11">
-        <v>739</v>
+        <v>949</v>
       </c>
       <c r="K11">
-        <v>720</v>
+        <v>973</v>
       </c>
       <c r="L11">
-        <v>728</v>
+        <v>703</v>
       </c>
       <c r="M11">
-        <v>528</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -48026,40 +48035,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>19</v>
-      </c>
       <c r="I2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48067,59 +48073,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48128,34 +48131,34 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>26</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48168,72 +48171,48 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48242,40 +48221,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>18</v>
       </c>
-      <c r="E8">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>88</v>
-      </c>
-      <c r="K8">
-        <v>46</v>
-      </c>
-      <c r="L8">
-        <v>50</v>
-      </c>
       <c r="M8">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48283,40 +48262,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="H9">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>38</v>
-      </c>
       <c r="L9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48324,40 +48303,40 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <v>192</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>142</v>
+      </c>
+      <c r="E10">
+        <v>135</v>
+      </c>
+      <c r="F10">
+        <v>184</v>
+      </c>
+      <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
         <v>112</v>
       </c>
-      <c r="C10">
-        <v>108</v>
-      </c>
-      <c r="D10">
-        <v>119</v>
-      </c>
-      <c r="E10">
-        <v>133</v>
-      </c>
-      <c r="F10">
-        <v>146</v>
-      </c>
-      <c r="G10">
-        <v>68</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
       <c r="I10">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="K10">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="L10">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48365,40 +48344,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="C11">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="E11">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F11">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H11">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="I11">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J11">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="K11">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="L11">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M11">
-        <v>207</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -48472,37 +48451,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48510,56 +48492,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48568,34 +48553,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
       <c r="H5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
         <v>13</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48608,48 +48593,72 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48658,40 +48667,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="K8">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48699,40 +48708,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
       <c r="G9">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48740,40 +48749,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="C10">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="D10">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="J10">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="L10">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="M10">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48781,40 +48790,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="C11">
+        <v>227</v>
+      </c>
+      <c r="D11">
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>248</v>
+      </c>
+      <c r="F11">
+        <v>249</v>
+      </c>
+      <c r="G11">
+        <v>169</v>
+      </c>
+      <c r="H11">
+        <v>193</v>
+      </c>
+      <c r="I11">
+        <v>251</v>
+      </c>
+      <c r="J11">
         <v>291</v>
       </c>
-      <c r="D11">
-        <v>212</v>
-      </c>
-      <c r="E11">
-        <v>216</v>
-      </c>
-      <c r="F11">
-        <v>247</v>
-      </c>
-      <c r="G11">
-        <v>155</v>
-      </c>
-      <c r="H11">
-        <v>179</v>
-      </c>
-      <c r="I11">
-        <v>238</v>
-      </c>
-      <c r="J11">
-        <v>318</v>
-      </c>
       <c r="K11">
-        <v>347</v>
+        <v>251</v>
       </c>
       <c r="L11">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="M11">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -48888,40 +48897,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>17</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
       <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48929,37 +48935,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -48969,16 +48975,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -48990,37 +48996,37 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
       <c r="M5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49028,41 +49034,38 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -49071,40 +49074,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
       <c r="I8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49112,37 +49115,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <v>4</v>
       </c>
-      <c r="H9">
-        <v>15</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
       <c r="K9">
-        <v>4</v>
-      </c>
-      <c r="L9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -49153,40 +49153,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="M10">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49194,40 +49194,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="J11">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="K11">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="L11">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -49301,37 +49301,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49339,56 +49342,44 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -49397,40 +49388,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>16</v>
       </c>
-      <c r="C5">
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
       <c r="K5">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49438,16 +49429,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -49458,10 +49446,10 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -49469,7 +49457,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -49478,40 +49466,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8">
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>37</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>23</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>8</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49519,37 +49507,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49557,40 +49548,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="G10">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="H10">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="K10">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="L10">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="M10">
-        <v>20</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49598,40 +49589,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="C11">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="D11">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="F11">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="H11">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="I11">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="J11">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="L11">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="M11">
-        <v>29</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -49705,40 +49696,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49746,45 +49737,54 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
         <v>5</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="M3">
         <v>5</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -49792,40 +49792,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49833,35 +49833,38 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>1</v>
+      <c r="L6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -49870,40 +49873,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>14</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J8">
         <v>37</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49911,39 +49914,36 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
       <c r="E9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
         <v>7</v>
       </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
       <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
         <v>3</v>
       </c>
     </row>
@@ -49952,40 +49952,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="E10">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F10">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G10">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="J10">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="K10">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="L10">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="M10">
-        <v>89</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49993,40 +49993,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="C11">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D11">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="F11">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G11">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="I11">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="J11">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="K11">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="L11">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="M11">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -86,26 +86,26 @@
     <sheet name="North Park" sheetId="77" r:id="rId77"/>
     <sheet name="Chinatown" sheetId="78" r:id="rId78"/>
     <sheet name="Beverly" sheetId="79" r:id="rId79"/>
-    <sheet name="West Lawn" sheetId="80" r:id="rId80"/>
-    <sheet name="East Side" sheetId="81" r:id="rId81"/>
+    <sheet name="Sauganash,Forest Glen" sheetId="80" r:id="rId80"/>
+    <sheet name="Garfield Ridge" sheetId="81" r:id="rId81"/>
     <sheet name="Rush &amp; Division" sheetId="82" r:id="rId82"/>
-    <sheet name="Pullman" sheetId="83" r:id="rId83"/>
-    <sheet name="Streeterville" sheetId="84" r:id="rId84"/>
-    <sheet name="Riverdale" sheetId="85" r:id="rId85"/>
-    <sheet name="Jackson Park" sheetId="86" r:id="rId86"/>
-    <sheet name="Millenium Park" sheetId="87" r:id="rId87"/>
-    <sheet name="Museum Campus" sheetId="88" r:id="rId88"/>
-    <sheet name="Printers Row" sheetId="89" r:id="rId89"/>
-    <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
-    <sheet name="Burnside" sheetId="91" r:id="rId91"/>
-    <sheet name="Bridgeport" sheetId="92" r:id="rId92"/>
-    <sheet name="Mount Greenwood" sheetId="93" r:id="rId93"/>
-    <sheet name="Garfield Ridge" sheetId="94" r:id="rId94"/>
-    <sheet name="Wrigleyville" sheetId="95" r:id="rId95"/>
-    <sheet name="Armour Square" sheetId="96" r:id="rId96"/>
-    <sheet name="Edison Park" sheetId="97" r:id="rId97"/>
-    <sheet name="Andersonville" sheetId="98" r:id="rId98"/>
-    <sheet name="Sauganash,Forest Glen" sheetId="99" r:id="rId99"/>
+    <sheet name="West Lawn" sheetId="83" r:id="rId83"/>
+    <sheet name="East Side" sheetId="84" r:id="rId84"/>
+    <sheet name="Pullman" sheetId="85" r:id="rId85"/>
+    <sheet name="Streeterville" sheetId="86" r:id="rId86"/>
+    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
+    <sheet name="Jackson Park" sheetId="88" r:id="rId88"/>
+    <sheet name="Millenium Park" sheetId="89" r:id="rId89"/>
+    <sheet name="Museum Campus" sheetId="90" r:id="rId90"/>
+    <sheet name="Printers Row" sheetId="91" r:id="rId91"/>
+    <sheet name="Gold Coast" sheetId="92" r:id="rId92"/>
+    <sheet name="Burnside" sheetId="93" r:id="rId93"/>
+    <sheet name="Bridgeport" sheetId="94" r:id="rId94"/>
+    <sheet name="Armour Square" sheetId="95" r:id="rId95"/>
+    <sheet name="Wrigleyville" sheetId="96" r:id="rId96"/>
+    <sheet name="Mount Greenwood" sheetId="97" r:id="rId97"/>
+    <sheet name="Edison Park" sheetId="98" r:id="rId98"/>
+    <sheet name="Andersonville" sheetId="99" r:id="rId99"/>
     <sheet name="Grant Park" sheetId="100" r:id="rId100"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41048,40 +41048,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41089,77 +41089,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
       <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -41168,40 +41144,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41209,72 +41185,39 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>6</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
         <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41282,40 +41225,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H8">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="K8">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="M8">
-        <v>129</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41323,40 +41266,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>32</v>
-      </c>
-      <c r="M9">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41364,40 +41304,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>641</v>
+        <v>119</v>
       </c>
       <c r="C10">
-        <v>540</v>
+        <v>146</v>
       </c>
       <c r="D10">
-        <v>482</v>
+        <v>152</v>
       </c>
       <c r="E10">
-        <v>485</v>
+        <v>152</v>
       </c>
       <c r="F10">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="G10">
-        <v>310</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>248</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>383</v>
+        <v>137</v>
       </c>
       <c r="J10">
-        <v>360</v>
+        <v>151</v>
       </c>
       <c r="K10">
-        <v>479</v>
+        <v>146</v>
       </c>
       <c r="L10">
-        <v>486</v>
+        <v>117</v>
       </c>
       <c r="M10">
-        <v>279</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41405,40 +41345,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1023</v>
+        <v>194</v>
       </c>
       <c r="C11">
-        <v>1021</v>
+        <v>271</v>
       </c>
       <c r="D11">
-        <v>860</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>846</v>
+        <v>246</v>
       </c>
       <c r="F11">
-        <v>718</v>
+        <v>186</v>
       </c>
       <c r="G11">
-        <v>519</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>501</v>
+        <v>156</v>
       </c>
       <c r="I11">
-        <v>727</v>
+        <v>222</v>
       </c>
       <c r="J11">
-        <v>845</v>
+        <v>256</v>
       </c>
       <c r="K11">
-        <v>936</v>
+        <v>243</v>
       </c>
       <c r="L11">
-        <v>803</v>
+        <v>187</v>
       </c>
       <c r="M11">
-        <v>524</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -41512,40 +41452,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="L2">
         <v>42</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41553,40 +41493,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>33</v>
       </c>
-      <c r="G3">
-        <v>38</v>
-      </c>
-      <c r="H3">
-        <v>45</v>
-      </c>
       <c r="I3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41594,36 +41534,39 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
     </row>
@@ -41632,40 +41575,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>119</v>
+      </c>
+      <c r="E5">
+        <v>112</v>
+      </c>
+      <c r="F5">
+        <v>99</v>
+      </c>
+      <c r="G5">
+        <v>66</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <v>66</v>
+      </c>
+      <c r="J5">
         <v>65</v>
       </c>
-      <c r="D5">
-        <v>54</v>
-      </c>
-      <c r="E5">
-        <v>46</v>
-      </c>
-      <c r="F5">
-        <v>31</v>
-      </c>
-      <c r="G5">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>30</v>
-      </c>
-      <c r="I5">
-        <v>35</v>
-      </c>
-      <c r="J5">
-        <v>33</v>
-      </c>
       <c r="K5">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41673,37 +41616,37 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>7</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>9</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -41714,40 +41657,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41755,40 +41695,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="I8">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="J8">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="K8">
-        <v>174</v>
+        <v>339</v>
       </c>
       <c r="L8">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41796,40 +41736,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="I9">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41837,40 +41777,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>180</v>
+        <v>395</v>
       </c>
       <c r="C10">
-        <v>215</v>
+        <v>492</v>
       </c>
       <c r="D10">
-        <v>184</v>
+        <v>381</v>
       </c>
       <c r="E10">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="F10">
-        <v>137</v>
+        <v>489</v>
       </c>
       <c r="G10">
-        <v>126</v>
+        <v>276</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="I10">
-        <v>192</v>
+        <v>445</v>
       </c>
       <c r="J10">
-        <v>269</v>
+        <v>502</v>
       </c>
       <c r="K10">
-        <v>193</v>
+        <v>411</v>
       </c>
       <c r="L10">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41878,40 +41818,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>385</v>
+        <v>654</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>876</v>
       </c>
       <c r="D11">
-        <v>397</v>
+        <v>743</v>
       </c>
       <c r="E11">
-        <v>354</v>
+        <v>789</v>
       </c>
       <c r="F11">
-        <v>298</v>
+        <v>728</v>
       </c>
       <c r="G11">
-        <v>290</v>
+        <v>491</v>
       </c>
       <c r="H11">
-        <v>326</v>
+        <v>565</v>
       </c>
       <c r="I11">
-        <v>434</v>
+        <v>767</v>
       </c>
       <c r="J11">
-        <v>592</v>
+        <v>949</v>
       </c>
       <c r="K11">
-        <v>554</v>
+        <v>973</v>
       </c>
       <c r="L11">
-        <v>580</v>
+        <v>703</v>
       </c>
       <c r="M11">
-        <v>357</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -42407,40 +42347,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H2">
+        <v>48</v>
+      </c>
+      <c r="I2">
+        <v>41</v>
+      </c>
+      <c r="J2">
         <v>36</v>
-      </c>
-      <c r="I2">
-        <v>26</v>
-      </c>
-      <c r="J2">
-        <v>35</v>
       </c>
       <c r="K2">
         <v>35</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42448,40 +42388,40 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>43</v>
+      </c>
+      <c r="D3">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>28</v>
+      </c>
+      <c r="F3">
         <v>24</v>
       </c>
-      <c r="C3">
-        <v>26</v>
-      </c>
-      <c r="D3">
-        <v>16</v>
-      </c>
-      <c r="E3">
+      <c r="G3">
+        <v>33</v>
+      </c>
+      <c r="H3">
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>37</v>
+      </c>
+      <c r="J3">
+        <v>37</v>
+      </c>
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3">
         <v>31</v>
       </c>
-      <c r="F3">
-        <v>29</v>
-      </c>
-      <c r="G3">
-        <v>36</v>
-      </c>
-      <c r="H3">
-        <v>31</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>28</v>
-      </c>
-      <c r="K3">
-        <v>31</v>
-      </c>
-      <c r="L3">
-        <v>28</v>
-      </c>
       <c r="M3">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42489,31 +42429,37 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -42521,40 +42467,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C5">
+        <v>175</v>
+      </c>
+      <c r="D5">
+        <v>120</v>
+      </c>
+      <c r="E5">
+        <v>152</v>
+      </c>
+      <c r="F5">
+        <v>91</v>
+      </c>
+      <c r="G5">
         <v>44</v>
       </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-      <c r="E5">
-        <v>35</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
       <c r="H5">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="K5">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="L5">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42562,40 +42508,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>13</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
+      <c r="M6">
         <v>7</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -42603,31 +42549,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>3</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -42635,40 +42581,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="D8">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H8">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="I8">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="J8">
-        <v>124</v>
+        <v>268</v>
       </c>
       <c r="K8">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="L8">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42676,40 +42622,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C9">
+        <v>101</v>
+      </c>
+      <c r="D9">
+        <v>84</v>
+      </c>
+      <c r="E9">
+        <v>49</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>42</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>62</v>
+      </c>
+      <c r="J9">
         <v>36</v>
       </c>
-      <c r="D9">
-        <v>26</v>
-      </c>
-      <c r="E9">
-        <v>21</v>
-      </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>21</v>
-      </c>
-      <c r="J9">
-        <v>17</v>
-      </c>
       <c r="K9">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -42717,40 +42663,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>641</v>
       </c>
       <c r="C10">
-        <v>250</v>
+        <v>540</v>
       </c>
       <c r="D10">
-        <v>270</v>
+        <v>482</v>
       </c>
       <c r="E10">
-        <v>297</v>
+        <v>485</v>
       </c>
       <c r="F10">
-        <v>226</v>
+        <v>443</v>
       </c>
       <c r="G10">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="H10">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="I10">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="J10">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="K10">
-        <v>275</v>
+        <v>479</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>486</v>
       </c>
       <c r="M10">
-        <v>180</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42758,40 +42704,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>359</v>
+        <v>1023</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>1021</v>
       </c>
       <c r="D11">
-        <v>427</v>
+        <v>860</v>
       </c>
       <c r="E11">
-        <v>450</v>
+        <v>846</v>
       </c>
       <c r="F11">
-        <v>388</v>
+        <v>718</v>
       </c>
       <c r="G11">
-        <v>284</v>
+        <v>519</v>
       </c>
       <c r="H11">
-        <v>324</v>
+        <v>501</v>
       </c>
       <c r="I11">
-        <v>346</v>
+        <v>727</v>
       </c>
       <c r="J11">
-        <v>418</v>
+        <v>845</v>
       </c>
       <c r="K11">
-        <v>490</v>
+        <v>936</v>
       </c>
       <c r="L11">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="M11">
-        <v>314</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -42865,40 +42811,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I2">
+        <v>50</v>
+      </c>
+      <c r="J2">
+        <v>66</v>
+      </c>
+      <c r="K2">
+        <v>50</v>
+      </c>
+      <c r="L2">
+        <v>42</v>
+      </c>
+      <c r="M2">
         <v>31</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42906,59 +42852,77 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
         <v>33</v>
       </c>
-      <c r="F3">
+      <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
         <v>28</v>
-      </c>
-      <c r="G3">
-        <v>19</v>
-      </c>
-      <c r="H3">
-        <v>19</v>
-      </c>
-      <c r="I3">
-        <v>15</v>
-      </c>
-      <c r="J3">
-        <v>29</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -42967,40 +42931,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K5">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43008,60 +42972,81 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
       <c r="D7">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43069,40 +43054,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H8">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="I8">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="J8">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="K8">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="L8">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="M8">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43110,40 +43095,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
         <v>19</v>
       </c>
-      <c r="C9">
-        <v>32</v>
-      </c>
-      <c r="D9">
-        <v>51</v>
-      </c>
-      <c r="E9">
-        <v>29</v>
-      </c>
-      <c r="F9">
-        <v>47</v>
-      </c>
       <c r="G9">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9">
         <v>29</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43151,40 +43136,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>632</v>
+        <v>180</v>
       </c>
       <c r="C10">
-        <v>762</v>
+        <v>215</v>
       </c>
       <c r="D10">
-        <v>938</v>
+        <v>184</v>
       </c>
       <c r="E10">
-        <v>859</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>913</v>
+        <v>137</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="H10">
-        <v>413</v>
+        <v>120</v>
       </c>
       <c r="I10">
-        <v>716</v>
+        <v>192</v>
       </c>
       <c r="J10">
-        <v>690</v>
+        <v>269</v>
       </c>
       <c r="K10">
-        <v>724</v>
+        <v>193</v>
       </c>
       <c r="L10">
-        <v>660</v>
+        <v>218</v>
       </c>
       <c r="M10">
-        <v>525</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43192,40 +43177,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>721</v>
+        <v>385</v>
       </c>
       <c r="C11">
-        <v>927</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>1129</v>
+        <v>397</v>
       </c>
       <c r="E11">
-        <v>1075</v>
+        <v>354</v>
       </c>
       <c r="F11">
-        <v>1141</v>
+        <v>298</v>
       </c>
       <c r="G11">
-        <v>616</v>
+        <v>290</v>
       </c>
       <c r="H11">
-        <v>689</v>
+        <v>326</v>
       </c>
       <c r="I11">
-        <v>1063</v>
+        <v>434</v>
       </c>
       <c r="J11">
-        <v>997</v>
+        <v>592</v>
       </c>
       <c r="K11">
-        <v>1009</v>
+        <v>554</v>
       </c>
       <c r="L11">
-        <v>902</v>
+        <v>580</v>
       </c>
       <c r="M11">
-        <v>687</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -43299,40 +43284,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="J2">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="K2">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43340,40 +43325,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43381,40 +43366,31 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -43422,40 +43398,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K5">
+        <v>22</v>
+      </c>
+      <c r="L5">
         <v>18</v>
       </c>
-      <c r="L5">
-        <v>13</v>
-      </c>
       <c r="M5">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43466,78 +43442,69 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>7</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43545,40 +43512,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>37</v>
+      </c>
+      <c r="G8">
+        <v>44</v>
+      </c>
+      <c r="H8">
+        <v>48</v>
+      </c>
+      <c r="I8">
+        <v>94</v>
+      </c>
+      <c r="J8">
+        <v>124</v>
+      </c>
+      <c r="K8">
+        <v>101</v>
+      </c>
+      <c r="L8">
+        <v>64</v>
+      </c>
+      <c r="M8">
         <v>52</v>
-      </c>
-      <c r="E8">
-        <v>48</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>57</v>
-      </c>
-      <c r="I8">
-        <v>134</v>
-      </c>
-      <c r="J8">
-        <v>136</v>
-      </c>
-      <c r="K8">
-        <v>97</v>
-      </c>
-      <c r="L8">
-        <v>80</v>
-      </c>
-      <c r="M8">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43586,40 +43553,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
         <v>21</v>
       </c>
-      <c r="I9">
-        <v>40</v>
-      </c>
       <c r="J9">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43627,40 +43594,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D10">
+        <v>270</v>
+      </c>
+      <c r="E10">
+        <v>297</v>
+      </c>
+      <c r="F10">
+        <v>226</v>
+      </c>
+      <c r="G10">
+        <v>133</v>
+      </c>
+      <c r="H10">
+        <v>143</v>
+      </c>
+      <c r="I10">
         <v>149</v>
       </c>
-      <c r="E10">
-        <v>169</v>
-      </c>
-      <c r="F10">
-        <v>157</v>
-      </c>
-      <c r="G10">
-        <v>112</v>
-      </c>
-      <c r="H10">
-        <v>127</v>
-      </c>
-      <c r="I10">
-        <v>131</v>
-      </c>
       <c r="J10">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="K10">
-        <v>148</v>
+        <v>275</v>
       </c>
       <c r="L10">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43668,40 +43635,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C11">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="E11">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G11">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="H11">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I11">
-        <v>466</v>
+        <v>346</v>
       </c>
       <c r="J11">
-        <v>528</v>
+        <v>418</v>
       </c>
       <c r="K11">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="L11">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="M11">
-        <v>290</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -43711,7 +43678,7 @@
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -43778,37 +43745,37 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>16</v>
       </c>
       <c r="I2">
+        <v>31</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>29</v>
+      </c>
+      <c r="L2">
         <v>19</v>
       </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
-      <c r="K2">
+      <c r="M2">
         <v>11</v>
-      </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43816,309 +43783,326 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G3">
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <v>19</v>
+      </c>
+      <c r="I3">
         <v>15</v>
       </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
       <c r="J3">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>39</v>
+      </c>
+      <c r="G6">
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <v>95</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="L8">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>47</v>
+      </c>
+      <c r="G9">
         <v>37</v>
       </c>
-      <c r="D9">
+      <c r="H9">
+        <v>46</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>29</v>
+      </c>
+      <c r="K9">
         <v>39</v>
       </c>
-      <c r="E9">
-        <v>67</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>33</v>
-      </c>
-      <c r="H9">
-        <v>80</v>
-      </c>
-      <c r="I9">
-        <v>94</v>
-      </c>
-      <c r="J9">
-        <v>70</v>
-      </c>
-      <c r="K9">
-        <v>102</v>
-      </c>
       <c r="L9">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="M9">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>632</v>
+      </c>
+      <c r="C10">
+        <v>762</v>
+      </c>
+      <c r="D10">
+        <v>938</v>
+      </c>
+      <c r="E10">
+        <v>859</v>
+      </c>
+      <c r="F10">
+        <v>913</v>
+      </c>
+      <c r="G10">
+        <v>398</v>
+      </c>
+      <c r="H10">
+        <v>413</v>
+      </c>
+      <c r="I10">
+        <v>716</v>
+      </c>
+      <c r="J10">
+        <v>690</v>
+      </c>
+      <c r="K10">
+        <v>724</v>
+      </c>
+      <c r="L10">
+        <v>660</v>
+      </c>
+      <c r="M10">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>106</v>
-      </c>
-      <c r="C10">
-        <v>79</v>
-      </c>
-      <c r="D10">
-        <v>73</v>
-      </c>
-      <c r="E10">
-        <v>117</v>
-      </c>
-      <c r="F10">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>94</v>
-      </c>
-      <c r="H10">
-        <v>141</v>
-      </c>
-      <c r="I10">
-        <v>182</v>
-      </c>
-      <c r="J10">
-        <v>155</v>
-      </c>
-      <c r="K10">
-        <v>170</v>
-      </c>
-      <c r="L10">
-        <v>141</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
+      <c r="B11">
+        <v>721</v>
+      </c>
+      <c r="C11">
+        <v>927</v>
+      </c>
+      <c r="D11">
+        <v>1129</v>
+      </c>
+      <c r="E11">
+        <v>1075</v>
+      </c>
+      <c r="F11">
+        <v>1141</v>
+      </c>
+      <c r="G11">
+        <v>616</v>
+      </c>
+      <c r="H11">
+        <v>689</v>
+      </c>
+      <c r="I11">
+        <v>1063</v>
+      </c>
+      <c r="J11">
+        <v>997</v>
+      </c>
+      <c r="K11">
+        <v>1009</v>
+      </c>
+      <c r="L11">
+        <v>902</v>
+      </c>
+      <c r="M11">
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -44192,69 +44176,81 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="C2">
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>47</v>
+      </c>
+      <c r="G2">
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>53</v>
+      </c>
       <c r="C3">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -44262,7 +44258,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -44270,31 +44299,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>38</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>13</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44302,45 +44340,81 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
       <c r="C7">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -44348,37 +44422,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>42</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44386,40 +44463,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>39</v>
+      </c>
+      <c r="K9">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>32</v>
+      </c>
+      <c r="M9">
         <v>10</v>
-      </c>
-      <c r="E9">
-        <v>12</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
-      <c r="M9">
-        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44427,40 +44504,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>209</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>344</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>445</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>307</v>
+        <v>169</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>157</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="H10">
-        <v>321</v>
+        <v>127</v>
       </c>
       <c r="I10">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="J10">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="K10">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="L10">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="M10">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44468,40 +44545,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="C11">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="D11">
-        <v>474</v>
+        <v>395</v>
       </c>
       <c r="E11">
-        <v>328</v>
+        <v>414</v>
       </c>
       <c r="F11">
-        <v>340</v>
+        <v>387</v>
       </c>
       <c r="G11">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="H11">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="I11">
-        <v>391</v>
+        <v>466</v>
       </c>
       <c r="J11">
-        <v>203</v>
+        <v>528</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>448</v>
       </c>
       <c r="L11">
-        <v>143</v>
+        <v>374</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -44511,7 +44588,7 @@
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -44575,40 +44652,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+      <c r="M2">
         <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -44616,70 +44693,115 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
       <c r="L4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -44688,188 +44810,192 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>2</v>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
       </c>
       <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>16</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>9</v>
+      </c>
+      <c r="M8">
         <v>6</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>9</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="I10">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="J10">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="K10">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="L10">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="M10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>123</v>
-      </c>
-      <c r="C11">
-        <v>97</v>
-      </c>
-      <c r="D11">
-        <v>89</v>
-      </c>
-      <c r="E11">
-        <v>44</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11">
-        <v>23</v>
-      </c>
-      <c r="H11">
-        <v>27</v>
-      </c>
-      <c r="I11">
-        <v>56</v>
-      </c>
-      <c r="J11">
-        <v>82</v>
-      </c>
-      <c r="K11">
-        <v>76</v>
-      </c>
-      <c r="L11">
-        <v>61</v>
-      </c>
-      <c r="M11">
-        <v>53</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -44943,97 +45069,76 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <v>4</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
         <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>3</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
+      <c r="J3">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
       <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -45042,40 +45147,31 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45083,19 +45179,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -45104,12 +45200,12 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -45117,7 +45213,10 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -45126,40 +45225,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="G8">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>16</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>40</v>
-      </c>
       <c r="K8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45167,40 +45263,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>15</v>
-      </c>
       <c r="K9">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45208,40 +45304,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C10">
-        <v>213</v>
+        <v>344</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>445</v>
       </c>
       <c r="E10">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="F10">
-        <v>229</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>158</v>
+        <v>321</v>
       </c>
       <c r="I10">
-        <v>226</v>
+        <v>367</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="K10">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="L10">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="M10">
-        <v>174</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45249,40 +45345,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>364</v>
       </c>
       <c r="D11">
-        <v>270</v>
+        <v>474</v>
       </c>
       <c r="E11">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="F11">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="G11">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>198</v>
+        <v>338</v>
       </c>
       <c r="I11">
-        <v>308</v>
+        <v>391</v>
       </c>
       <c r="J11">
-        <v>314</v>
+        <v>203</v>
       </c>
       <c r="K11">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="L11">
-        <v>309</v>
+        <v>143</v>
       </c>
       <c r="M11">
-        <v>204</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -45835,34 +45931,37 @@
         <v>1</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>8</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45870,47 +45969,44 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
       <c r="J3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -45919,94 +46015,61 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
         <v>3</v>
       </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
       <c r="K5">
-        <v>13</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="K7">
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -46015,40 +46078,31 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
         <v>12</v>
       </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
         <v>11</v>
       </c>
-      <c r="E8">
-        <v>23</v>
-      </c>
-      <c r="F8">
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>24</v>
-      </c>
-      <c r="J8">
-        <v>27</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46056,40 +46110,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46097,40 +46148,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="C10">
-        <v>260</v>
+        <v>87</v>
       </c>
       <c r="D10">
-        <v>256</v>
+        <v>69</v>
       </c>
       <c r="E10">
-        <v>262</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="H10">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="I10">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="J10">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="K10">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>36</v>
       </c>
       <c r="M10">
-        <v>148</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46138,40 +46189,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="C11">
-        <v>323</v>
+        <v>97</v>
       </c>
       <c r="D11">
-        <v>311</v>
+        <v>89</v>
       </c>
       <c r="E11">
-        <v>342</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="G11">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="H11">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="I11">
-        <v>236</v>
+        <v>56</v>
       </c>
       <c r="J11">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="K11">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="L11">
-        <v>323</v>
+        <v>61</v>
       </c>
       <c r="M11">
-        <v>190</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -46245,40 +46296,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>11</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46286,63 +46337,54 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="I4">
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -46353,40 +46395,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>8</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46394,60 +46436,42 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46455,40 +46479,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>31</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
         <v>13</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>21</v>
-      </c>
-      <c r="I8">
-        <v>39</v>
-      </c>
-      <c r="J8">
-        <v>50</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46496,40 +46520,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>31</v>
+      </c>
+      <c r="E9">
         <v>17</v>
       </c>
-      <c r="D9">
-        <v>13</v>
-      </c>
-      <c r="E9">
-        <v>26</v>
-      </c>
       <c r="F9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
         <v>11</v>
       </c>
-      <c r="H9">
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
         <v>15</v>
       </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
       <c r="K9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46537,40 +46561,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="I10">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="J10">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="K10">
-        <v>37</v>
+        <v>295</v>
       </c>
       <c r="L10">
-        <v>56</v>
+        <v>264</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46578,40 +46602,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="D11">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="E11">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="F11">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="G11">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="I11">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="J11">
-        <v>146</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>128</v>
+        <v>309</v>
       </c>
       <c r="M11">
-        <v>74</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -46685,40 +46709,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>41</v>
-      </c>
-      <c r="L2">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46726,78 +46747,48 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
       <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -46805,40 +46796,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="L5">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46846,72 +46837,54 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>3</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
       <c r="G7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
       <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46919,40 +46892,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46960,40 +46933,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
         <v>17</v>
       </c>
-      <c r="G9">
-        <v>40</v>
-      </c>
-      <c r="H9">
-        <v>59</v>
-      </c>
       <c r="I9">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J9">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47001,40 +46974,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>369</v>
+        <v>197</v>
       </c>
       <c r="C10">
-        <v>394</v>
+        <v>260</v>
       </c>
       <c r="D10">
-        <v>372</v>
+        <v>256</v>
       </c>
       <c r="E10">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>211</v>
       </c>
       <c r="G10">
-        <v>266</v>
+        <v>122</v>
       </c>
       <c r="H10">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="I10">
-        <v>372</v>
+        <v>175</v>
       </c>
       <c r="J10">
-        <v>319</v>
+        <v>199</v>
       </c>
       <c r="K10">
-        <v>369</v>
+        <v>256</v>
       </c>
       <c r="L10">
-        <v>427</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>328</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47042,40 +47015,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>713</v>
+        <v>255</v>
       </c>
       <c r="C11">
-        <v>714</v>
+        <v>323</v>
       </c>
       <c r="D11">
-        <v>697</v>
+        <v>311</v>
       </c>
       <c r="E11">
-        <v>616</v>
+        <v>342</v>
       </c>
       <c r="F11">
-        <v>568</v>
+        <v>261</v>
       </c>
       <c r="G11">
-        <v>492</v>
+        <v>197</v>
       </c>
       <c r="H11">
-        <v>474</v>
+        <v>233</v>
       </c>
       <c r="I11">
-        <v>722</v>
+        <v>236</v>
       </c>
       <c r="J11">
-        <v>739</v>
+        <v>268</v>
       </c>
       <c r="K11">
-        <v>720</v>
+        <v>337</v>
       </c>
       <c r="L11">
-        <v>728</v>
+        <v>323</v>
       </c>
       <c r="M11">
-        <v>528</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -47149,40 +47122,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I2">
+        <v>11</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>21</v>
+      </c>
+      <c r="L2">
+        <v>9</v>
+      </c>
+      <c r="M2">
         <v>8</v>
-      </c>
-      <c r="J2">
-        <v>17</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47190,40 +47163,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47237,9 +47210,18 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -47248,37 +47230,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <v>30</v>
       </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
       <c r="G5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J5">
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
         <v>8</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -47289,42 +47271,60 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47332,40 +47332,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L8">
         <v>26</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47373,40 +47373,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47414,40 +47414,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="G10">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="M10">
-        <v>69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47455,40 +47455,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="D11">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="E11">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G11">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H11">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I11">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="K11">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="L11">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -47562,40 +47562,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47603,40 +47603,40 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>44</v>
+      </c>
+      <c r="G3">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>31</v>
+      </c>
+      <c r="I3">
+        <v>36</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>31</v>
+      </c>
+      <c r="L3">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>18</v>
-      </c>
-      <c r="C3">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>33</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>36</v>
-      </c>
-      <c r="K3">
-        <v>41</v>
-      </c>
-      <c r="L3">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47644,37 +47644,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -47685,40 +47682,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E5">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -47726,40 +47723,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -47767,37 +47764,31 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>3</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47805,40 +47796,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>96</v>
+      </c>
+      <c r="C8">
         <v>59</v>
       </c>
-      <c r="C8">
-        <v>104</v>
-      </c>
       <c r="D8">
+        <v>59</v>
+      </c>
+      <c r="E8">
+        <v>63</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>110</v>
+      </c>
+      <c r="J8">
+        <v>171</v>
+      </c>
+      <c r="K8">
+        <v>143</v>
+      </c>
+      <c r="L8">
         <v>122</v>
       </c>
-      <c r="E8">
-        <v>89</v>
-      </c>
-      <c r="F8">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>70</v>
-      </c>
-      <c r="I8">
-        <v>140</v>
-      </c>
-      <c r="J8">
-        <v>242</v>
-      </c>
-      <c r="K8">
-        <v>339</v>
-      </c>
-      <c r="L8">
-        <v>141</v>
-      </c>
       <c r="M8">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47846,40 +47837,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I9">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J9">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K9">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47887,40 +47878,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="C10">
-        <v>492</v>
+        <v>394</v>
       </c>
       <c r="D10">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E10">
-        <v>489</v>
+        <v>305</v>
       </c>
       <c r="F10">
-        <v>489</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="H10">
-        <v>330</v>
+        <v>224</v>
       </c>
       <c r="I10">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="J10">
-        <v>502</v>
+        <v>319</v>
       </c>
       <c r="K10">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="L10">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="M10">
-        <v>233</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47928,40 +47919,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>654</v>
+        <v>713</v>
       </c>
       <c r="C11">
-        <v>876</v>
+        <v>714</v>
       </c>
       <c r="D11">
-        <v>743</v>
+        <v>697</v>
       </c>
       <c r="E11">
-        <v>789</v>
+        <v>616</v>
       </c>
       <c r="F11">
+        <v>568</v>
+      </c>
+      <c r="G11">
+        <v>492</v>
+      </c>
+      <c r="H11">
+        <v>474</v>
+      </c>
+      <c r="I11">
+        <v>722</v>
+      </c>
+      <c r="J11">
+        <v>739</v>
+      </c>
+      <c r="K11">
+        <v>720</v>
+      </c>
+      <c r="L11">
         <v>728</v>
       </c>
-      <c r="G11">
-        <v>491</v>
-      </c>
-      <c r="H11">
-        <v>565</v>
-      </c>
-      <c r="I11">
-        <v>767</v>
-      </c>
-      <c r="J11">
-        <v>949</v>
-      </c>
-      <c r="K11">
-        <v>973</v>
-      </c>
-      <c r="L11">
-        <v>703</v>
-      </c>
       <c r="M11">
-        <v>460</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -48035,37 +48026,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48073,56 +48067,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48131,34 +48128,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
       <c r="H5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
         <v>13</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48171,48 +48168,72 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48221,40 +48242,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="K8">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48262,40 +48283,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
       <c r="G9">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48303,40 +48324,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="C10">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="D10">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="J10">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="L10">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="M10">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48344,40 +48365,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="C11">
+        <v>227</v>
+      </c>
+      <c r="D11">
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>248</v>
+      </c>
+      <c r="F11">
+        <v>249</v>
+      </c>
+      <c r="G11">
+        <v>169</v>
+      </c>
+      <c r="H11">
+        <v>193</v>
+      </c>
+      <c r="I11">
+        <v>251</v>
+      </c>
+      <c r="J11">
         <v>291</v>
       </c>
-      <c r="D11">
-        <v>212</v>
-      </c>
-      <c r="E11">
-        <v>216</v>
-      </c>
-      <c r="F11">
-        <v>247</v>
-      </c>
-      <c r="G11">
-        <v>155</v>
-      </c>
-      <c r="H11">
-        <v>179</v>
-      </c>
-      <c r="I11">
-        <v>238</v>
-      </c>
-      <c r="J11">
-        <v>318</v>
-      </c>
       <c r="K11">
-        <v>347</v>
+        <v>251</v>
       </c>
       <c r="L11">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="M11">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -48451,40 +48472,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>19</v>
-      </c>
       <c r="I2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48492,59 +48510,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48553,34 +48568,34 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>26</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48593,72 +48608,48 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48667,40 +48658,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>18</v>
       </c>
-      <c r="E8">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>88</v>
-      </c>
-      <c r="K8">
-        <v>46</v>
-      </c>
-      <c r="L8">
-        <v>50</v>
-      </c>
       <c r="M8">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48708,40 +48699,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="H9">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>38</v>
-      </c>
       <c r="L9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48749,40 +48740,40 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <v>192</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>142</v>
+      </c>
+      <c r="E10">
+        <v>135</v>
+      </c>
+      <c r="F10">
+        <v>184</v>
+      </c>
+      <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
         <v>112</v>
       </c>
-      <c r="C10">
-        <v>108</v>
-      </c>
-      <c r="D10">
-        <v>119</v>
-      </c>
-      <c r="E10">
-        <v>133</v>
-      </c>
-      <c r="F10">
-        <v>146</v>
-      </c>
-      <c r="G10">
-        <v>68</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
       <c r="I10">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="K10">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="L10">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48790,40 +48781,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="C11">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="E11">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F11">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H11">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="I11">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J11">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="K11">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="L11">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M11">
-        <v>207</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -48897,37 +48888,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
         <v>5</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48935,37 +48929,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
         <v>7</v>
       </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -48975,16 +48969,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -48996,37 +48990,37 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F5">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
         <v>6</v>
       </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
+      <c r="L5">
+        <v>15</v>
+      </c>
+      <c r="M5">
         <v>8</v>
-      </c>
-      <c r="I5">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>12</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49034,38 +49028,41 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -49074,40 +49071,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
         <v>11</v>
-      </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>8</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49115,34 +49112,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
         <v>5</v>
       </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
+      <c r="K9">
         <v>4</v>
       </c>
-      <c r="K9">
-        <v>3</v>
+      <c r="L9">
+        <v>6</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -49153,40 +49153,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="D10">
+        <v>150</v>
+      </c>
+      <c r="E10">
+        <v>134</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
         <v>62</v>
       </c>
-      <c r="E10">
-        <v>45</v>
-      </c>
-      <c r="F10">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>52</v>
-      </c>
       <c r="H10">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49194,40 +49194,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="C11">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="D11">
-        <v>87</v>
+        <v>204</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="F11">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="H11">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="I11">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="J11">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="L11">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="M11">
-        <v>29</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -49301,40 +49301,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>9</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
         <v>3</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49342,44 +49339,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -49388,40 +49397,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>27</v>
-      </c>
-      <c r="E5">
-        <v>32</v>
-      </c>
       <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>32</v>
-      </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49429,13 +49438,16 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+      <c r="F6">
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -49446,10 +49458,10 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -49457,7 +49469,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -49466,40 +49478,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>37</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
       <c r="L8">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49507,40 +49519,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49548,40 +49557,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="J10">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="K10">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="M10">
-        <v>89</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49589,40 +49598,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="F11">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="J11">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="K11">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="L11">
-        <v>239</v>
+        <v>87</v>
       </c>
       <c r="M11">
-        <v>109</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -49696,40 +49705,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49737,54 +49746,45 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="E3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
         <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -49792,40 +49792,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49833,38 +49833,35 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="D6">
         <v>3</v>
       </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
-        <v>2</v>
+      <c r="M6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -49873,40 +49870,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
         <v>15</v>
       </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
       <c r="D8">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>14</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J8">
         <v>37</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49914,36 +49911,39 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>7</v>
-      </c>
-      <c r="L9">
+      <c r="M9">
         <v>3</v>
       </c>
     </row>
@@ -49952,40 +49952,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C10">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="D10">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G10">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H10">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I10">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="J10">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="K10">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="L10">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="M10">
-        <v>56</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49993,40 +49993,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="C11">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="D11">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="E11">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="F11">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="G11">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="H11">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="I11">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="J11">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="K11">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="L11">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="M11">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -86,26 +86,26 @@
     <sheet name="North Park" sheetId="77" r:id="rId77"/>
     <sheet name="Chinatown" sheetId="78" r:id="rId78"/>
     <sheet name="Beverly" sheetId="79" r:id="rId79"/>
-    <sheet name="Sauganash,Forest Glen" sheetId="80" r:id="rId80"/>
-    <sheet name="Garfield Ridge" sheetId="81" r:id="rId81"/>
+    <sheet name="West Lawn" sheetId="80" r:id="rId80"/>
+    <sheet name="East Side" sheetId="81" r:id="rId81"/>
     <sheet name="Rush &amp; Division" sheetId="82" r:id="rId82"/>
-    <sheet name="West Lawn" sheetId="83" r:id="rId83"/>
-    <sheet name="East Side" sheetId="84" r:id="rId84"/>
-    <sheet name="Pullman" sheetId="85" r:id="rId85"/>
-    <sheet name="Streeterville" sheetId="86" r:id="rId86"/>
-    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
-    <sheet name="Jackson Park" sheetId="88" r:id="rId88"/>
-    <sheet name="Millenium Park" sheetId="89" r:id="rId89"/>
-    <sheet name="Museum Campus" sheetId="90" r:id="rId90"/>
-    <sheet name="Printers Row" sheetId="91" r:id="rId91"/>
-    <sheet name="Gold Coast" sheetId="92" r:id="rId92"/>
-    <sheet name="Burnside" sheetId="93" r:id="rId93"/>
-    <sheet name="Bridgeport" sheetId="94" r:id="rId94"/>
-    <sheet name="Armour Square" sheetId="95" r:id="rId95"/>
-    <sheet name="Wrigleyville" sheetId="96" r:id="rId96"/>
-    <sheet name="Mount Greenwood" sheetId="97" r:id="rId97"/>
-    <sheet name="Edison Park" sheetId="98" r:id="rId98"/>
-    <sheet name="Andersonville" sheetId="99" r:id="rId99"/>
+    <sheet name="Pullman" sheetId="83" r:id="rId83"/>
+    <sheet name="Streeterville" sheetId="84" r:id="rId84"/>
+    <sheet name="Riverdale" sheetId="85" r:id="rId85"/>
+    <sheet name="Jackson Park" sheetId="86" r:id="rId86"/>
+    <sheet name="Millenium Park" sheetId="87" r:id="rId87"/>
+    <sheet name="Museum Campus" sheetId="88" r:id="rId88"/>
+    <sheet name="Printers Row" sheetId="89" r:id="rId89"/>
+    <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
+    <sheet name="Burnside" sheetId="91" r:id="rId91"/>
+    <sheet name="Bridgeport" sheetId="92" r:id="rId92"/>
+    <sheet name="Mount Greenwood" sheetId="93" r:id="rId93"/>
+    <sheet name="Garfield Ridge" sheetId="94" r:id="rId94"/>
+    <sheet name="Wrigleyville" sheetId="95" r:id="rId95"/>
+    <sheet name="Armour Square" sheetId="96" r:id="rId96"/>
+    <sheet name="Edison Park" sheetId="97" r:id="rId97"/>
+    <sheet name="Andersonville" sheetId="98" r:id="rId98"/>
+    <sheet name="Sauganash,Forest Glen" sheetId="99" r:id="rId99"/>
     <sheet name="Grant Park" sheetId="100" r:id="rId100"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41048,40 +41048,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41089,53 +41089,77 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
       <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -41144,40 +41168,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>64</v>
+      </c>
+      <c r="J5">
+        <v>92</v>
+      </c>
+      <c r="K5">
+        <v>66</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
         <v>36</v>
-      </c>
-      <c r="I5">
-        <v>40</v>
-      </c>
-      <c r="J5">
-        <v>39</v>
-      </c>
-      <c r="K5">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>25</v>
-      </c>
-      <c r="M5">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41185,39 +41209,72 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
       <c r="J7">
         <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41225,40 +41282,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>271</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41266,37 +41323,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="M9">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41304,40 +41364,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>119</v>
+        <v>641</v>
       </c>
       <c r="C10">
-        <v>146</v>
+        <v>540</v>
       </c>
       <c r="D10">
-        <v>152</v>
+        <v>482</v>
       </c>
       <c r="E10">
-        <v>152</v>
+        <v>485</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>443</v>
       </c>
       <c r="G10">
-        <v>103</v>
+        <v>310</v>
       </c>
       <c r="H10">
-        <v>88</v>
+        <v>248</v>
       </c>
       <c r="I10">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="J10">
-        <v>151</v>
+        <v>360</v>
       </c>
       <c r="K10">
-        <v>146</v>
+        <v>479</v>
       </c>
       <c r="L10">
-        <v>117</v>
+        <v>486</v>
       </c>
       <c r="M10">
-        <v>56</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41345,40 +41405,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>194</v>
+        <v>1023</v>
       </c>
       <c r="C11">
-        <v>271</v>
+        <v>1021</v>
       </c>
       <c r="D11">
-        <v>245</v>
+        <v>860</v>
       </c>
       <c r="E11">
-        <v>246</v>
+        <v>846</v>
       </c>
       <c r="F11">
-        <v>186</v>
+        <v>718</v>
       </c>
       <c r="G11">
-        <v>183</v>
+        <v>519</v>
       </c>
       <c r="H11">
-        <v>156</v>
+        <v>501</v>
       </c>
       <c r="I11">
-        <v>222</v>
+        <v>727</v>
       </c>
       <c r="J11">
-        <v>256</v>
+        <v>845</v>
       </c>
       <c r="K11">
-        <v>243</v>
+        <v>936</v>
       </c>
       <c r="L11">
-        <v>187</v>
+        <v>803</v>
       </c>
       <c r="M11">
-        <v>97</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -41452,40 +41512,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L2">
         <v>42</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41493,40 +41553,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C3">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
         <v>28</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>33</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>36</v>
-      </c>
-      <c r="K3">
-        <v>41</v>
-      </c>
-      <c r="L3">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41534,39 +41594,36 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
       <c r="L4">
-        <v>6</v>
-      </c>
-      <c r="M4">
         <v>2</v>
       </c>
     </row>
@@ -41575,40 +41632,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="E5">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="K5">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L5">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41616,37 +41673,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -41657,37 +41714,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="D7">
+      <c r="J7">
         <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41695,40 +41755,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F8">
+        <v>39</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8">
         <v>52</v>
       </c>
-      <c r="G8">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>70</v>
-      </c>
       <c r="I8">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="J8">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="K8">
-        <v>339</v>
+        <v>174</v>
       </c>
       <c r="L8">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="M8">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41736,40 +41796,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
         <v>39</v>
       </c>
-      <c r="H9">
-        <v>52</v>
-      </c>
-      <c r="I9">
-        <v>24</v>
-      </c>
       <c r="J9">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K9">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41777,40 +41837,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>395</v>
+        <v>180</v>
       </c>
       <c r="C10">
-        <v>492</v>
+        <v>215</v>
       </c>
       <c r="D10">
-        <v>381</v>
+        <v>184</v>
       </c>
       <c r="E10">
-        <v>489</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>489</v>
+        <v>137</v>
       </c>
       <c r="G10">
-        <v>276</v>
+        <v>126</v>
       </c>
       <c r="H10">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="I10">
-        <v>445</v>
+        <v>192</v>
       </c>
       <c r="J10">
-        <v>502</v>
+        <v>269</v>
       </c>
       <c r="K10">
-        <v>411</v>
+        <v>193</v>
       </c>
       <c r="L10">
-        <v>386</v>
+        <v>218</v>
       </c>
       <c r="M10">
-        <v>233</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41818,40 +41878,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>654</v>
+        <v>385</v>
       </c>
       <c r="C11">
-        <v>876</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>743</v>
+        <v>397</v>
       </c>
       <c r="E11">
-        <v>789</v>
+        <v>354</v>
       </c>
       <c r="F11">
-        <v>728</v>
+        <v>298</v>
       </c>
       <c r="G11">
-        <v>491</v>
+        <v>290</v>
       </c>
       <c r="H11">
-        <v>565</v>
+        <v>326</v>
       </c>
       <c r="I11">
-        <v>767</v>
+        <v>434</v>
       </c>
       <c r="J11">
-        <v>949</v>
+        <v>592</v>
       </c>
       <c r="K11">
-        <v>973</v>
+        <v>554</v>
       </c>
       <c r="L11">
-        <v>703</v>
+        <v>580</v>
       </c>
       <c r="M11">
-        <v>461</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -42347,40 +42407,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K2">
         <v>35</v>
       </c>
       <c r="L2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42388,40 +42448,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>31</v>
+      </c>
+      <c r="F3">
         <v>29</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>36</v>
+      </c>
+      <c r="H3">
+        <v>31</v>
+      </c>
+      <c r="I3">
+        <v>24</v>
+      </c>
+      <c r="J3">
         <v>28</v>
       </c>
-      <c r="F3">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <v>33</v>
-      </c>
-      <c r="H3">
-        <v>34</v>
-      </c>
-      <c r="I3">
-        <v>37</v>
-      </c>
-      <c r="J3">
-        <v>37</v>
-      </c>
       <c r="K3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42429,13 +42489,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -42446,20 +42503,17 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -42467,40 +42521,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="J5">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="K5">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42508,40 +42562,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
       <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
       <c r="J6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -42549,31 +42603,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -42581,40 +42635,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G8">
+        <v>44</v>
+      </c>
+      <c r="H8">
         <v>48</v>
       </c>
-      <c r="H8">
-        <v>63</v>
-      </c>
       <c r="I8">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="J8">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="K8">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="L8">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="M8">
-        <v>131</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42622,40 +42676,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -42663,40 +42717,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>641</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>540</v>
+        <v>250</v>
       </c>
       <c r="D10">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="E10">
-        <v>485</v>
+        <v>297</v>
       </c>
       <c r="F10">
-        <v>443</v>
+        <v>226</v>
       </c>
       <c r="G10">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="H10">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="I10">
-        <v>383</v>
+        <v>149</v>
       </c>
       <c r="J10">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="K10">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="L10">
-        <v>486</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>282</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42704,40 +42758,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1023</v>
+        <v>359</v>
       </c>
       <c r="C11">
-        <v>1021</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>860</v>
+        <v>427</v>
       </c>
       <c r="E11">
-        <v>846</v>
+        <v>450</v>
       </c>
       <c r="F11">
-        <v>718</v>
+        <v>388</v>
       </c>
       <c r="G11">
-        <v>519</v>
+        <v>284</v>
       </c>
       <c r="H11">
-        <v>501</v>
+        <v>324</v>
       </c>
       <c r="I11">
-        <v>727</v>
+        <v>346</v>
       </c>
       <c r="J11">
-        <v>845</v>
+        <v>418</v>
       </c>
       <c r="K11">
-        <v>936</v>
+        <v>490</v>
       </c>
       <c r="L11">
-        <v>803</v>
+        <v>427</v>
       </c>
       <c r="M11">
-        <v>530</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -42811,40 +42865,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42852,77 +42906,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I3">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -42931,40 +42967,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K5">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42972,81 +43008,60 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43054,40 +43069,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="I8">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="J8">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="K8">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="L8">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43095,40 +43110,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9">
         <v>29</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43136,40 +43151,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>180</v>
+        <v>632</v>
       </c>
       <c r="C10">
-        <v>215</v>
+        <v>762</v>
       </c>
       <c r="D10">
-        <v>184</v>
+        <v>938</v>
       </c>
       <c r="E10">
-        <v>140</v>
+        <v>859</v>
       </c>
       <c r="F10">
-        <v>137</v>
+        <v>913</v>
       </c>
       <c r="G10">
-        <v>126</v>
+        <v>398</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>413</v>
       </c>
       <c r="I10">
-        <v>192</v>
+        <v>716</v>
       </c>
       <c r="J10">
-        <v>269</v>
+        <v>690</v>
       </c>
       <c r="K10">
-        <v>193</v>
+        <v>724</v>
       </c>
       <c r="L10">
-        <v>218</v>
+        <v>660</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43177,40 +43192,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>385</v>
+        <v>721</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>927</v>
       </c>
       <c r="D11">
-        <v>397</v>
+        <v>1129</v>
       </c>
       <c r="E11">
-        <v>354</v>
+        <v>1075</v>
       </c>
       <c r="F11">
-        <v>298</v>
+        <v>1141</v>
       </c>
       <c r="G11">
-        <v>290</v>
+        <v>616</v>
       </c>
       <c r="H11">
-        <v>326</v>
+        <v>689</v>
       </c>
       <c r="I11">
-        <v>434</v>
+        <v>1063</v>
       </c>
       <c r="J11">
-        <v>592</v>
+        <v>997</v>
       </c>
       <c r="K11">
-        <v>554</v>
+        <v>1009</v>
       </c>
       <c r="L11">
-        <v>580</v>
+        <v>902</v>
       </c>
       <c r="M11">
-        <v>358</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -43284,40 +43299,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="K2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43325,40 +43340,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="L3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43366,31 +43381,40 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -43398,40 +43422,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>71</v>
+      </c>
+      <c r="D5">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>38</v>
+      </c>
+      <c r="J5">
         <v>30</v>
       </c>
-      <c r="C5">
-        <v>44</v>
-      </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-      <c r="E5">
-        <v>35</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
-      <c r="H5">
-        <v>31</v>
-      </c>
-      <c r="I5">
-        <v>19</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
       <c r="K5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L5">
+        <v>13</v>
+      </c>
+      <c r="M5">
         <v>18</v>
-      </c>
-      <c r="M5">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43442,69 +43466,78 @@
         <v>3</v>
       </c>
       <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
         <v>6</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
       </c>
       <c r="I6">
         <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>3</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43512,40 +43545,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>52</v>
+      </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>44</v>
+      </c>
+      <c r="G8">
         <v>42</v>
       </c>
-      <c r="D8">
-        <v>47</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>37</v>
-      </c>
-      <c r="G8">
-        <v>44</v>
-      </c>
       <c r="H8">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I8">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="J8">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L8">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43553,40 +43586,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E9">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
         <v>21</v>
       </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
       <c r="I9">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J9">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K9">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43594,40 +43627,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>270</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>297</v>
+        <v>169</v>
       </c>
       <c r="F10">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="G10">
+        <v>112</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10">
+        <v>131</v>
+      </c>
+      <c r="J10">
+        <v>154</v>
+      </c>
+      <c r="K10">
+        <v>148</v>
+      </c>
+      <c r="L10">
         <v>133</v>
       </c>
-      <c r="H10">
-        <v>143</v>
-      </c>
-      <c r="I10">
-        <v>149</v>
-      </c>
-      <c r="J10">
-        <v>195</v>
-      </c>
-      <c r="K10">
-        <v>275</v>
-      </c>
-      <c r="L10">
-        <v>265</v>
-      </c>
       <c r="M10">
-        <v>181</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43635,40 +43668,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="D11">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="E11">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="F11">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G11">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="H11">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="I11">
-        <v>346</v>
+        <v>466</v>
       </c>
       <c r="J11">
-        <v>418</v>
+        <v>528</v>
       </c>
       <c r="K11">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="L11">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="M11">
-        <v>315</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -43678,7 +43711,7 @@
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -43745,37 +43778,37 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>16</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43783,326 +43816,309 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="E4">
+        <v>6</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>19</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>23</v>
-      </c>
-      <c r="G5">
-        <v>56</v>
-      </c>
-      <c r="H5">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
       <c r="J5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>39</v>
-      </c>
-      <c r="G6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="J8">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="K8">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="L8">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>632</v>
+        <v>106</v>
       </c>
       <c r="C10">
-        <v>762</v>
+        <v>79</v>
       </c>
       <c r="D10">
-        <v>938</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>859</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>913</v>
+        <v>86</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>94</v>
       </c>
       <c r="H10">
-        <v>413</v>
+        <v>141</v>
       </c>
       <c r="I10">
-        <v>716</v>
+        <v>182</v>
       </c>
       <c r="J10">
-        <v>690</v>
+        <v>155</v>
       </c>
       <c r="K10">
-        <v>724</v>
+        <v>170</v>
       </c>
       <c r="L10">
-        <v>660</v>
+        <v>141</v>
       </c>
       <c r="M10">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>721</v>
-      </c>
-      <c r="C11">
-        <v>927</v>
-      </c>
-      <c r="D11">
-        <v>1129</v>
-      </c>
-      <c r="E11">
-        <v>1075</v>
-      </c>
-      <c r="F11">
-        <v>1141</v>
-      </c>
-      <c r="G11">
-        <v>616</v>
-      </c>
-      <c r="H11">
-        <v>689</v>
-      </c>
-      <c r="I11">
-        <v>1063</v>
-      </c>
-      <c r="J11">
-        <v>997</v>
-      </c>
-      <c r="K11">
-        <v>1009</v>
-      </c>
-      <c r="L11">
-        <v>902</v>
-      </c>
-      <c r="M11">
-        <v>689</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -44176,81 +44192,69 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39</v>
-      </c>
-      <c r="C2">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>47</v>
-      </c>
-      <c r="G2">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>53</v>
-      </c>
       <c r="C3">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -44258,40 +44262,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -44299,40 +44270,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44340,81 +44302,45 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
       <c r="E6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
       <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -44422,40 +44348,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44463,40 +44386,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44504,40 +44427,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="D10">
-        <v>149</v>
+        <v>445</v>
       </c>
       <c r="E10">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="F10">
-        <v>157</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>127</v>
+        <v>321</v>
       </c>
       <c r="I10">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="J10">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K10">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="L10">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M10">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44545,40 +44468,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>368</v>
+        <v>220</v>
       </c>
       <c r="C11">
-        <v>412</v>
+        <v>364</v>
       </c>
       <c r="D11">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="E11">
-        <v>414</v>
+        <v>328</v>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>340</v>
       </c>
       <c r="G11">
-        <v>330</v>
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="I11">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="J11">
-        <v>528</v>
+        <v>203</v>
       </c>
       <c r="K11">
-        <v>448</v>
+        <v>201</v>
       </c>
       <c r="L11">
-        <v>374</v>
+        <v>143</v>
       </c>
       <c r="M11">
-        <v>290</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -44588,7 +44511,7 @@
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -44652,40 +44575,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>16</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
-      <c r="K2">
-        <v>11</v>
-      </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -44693,115 +44616,70 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
       <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -44810,192 +44688,188 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
+      <c r="J6">
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>34</v>
-      </c>
-      <c r="K7">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="M9">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>110</v>
+      </c>
+      <c r="C10">
+        <v>87</v>
+      </c>
+      <c r="D10">
+        <v>69</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>39</v>
+      </c>
+      <c r="J10">
+        <v>56</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>36</v>
+      </c>
+      <c r="M10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>106</v>
-      </c>
-      <c r="C10">
-        <v>79</v>
-      </c>
-      <c r="D10">
-        <v>73</v>
-      </c>
-      <c r="E10">
-        <v>117</v>
-      </c>
-      <c r="F10">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>94</v>
-      </c>
-      <c r="H10">
-        <v>141</v>
-      </c>
-      <c r="I10">
-        <v>182</v>
-      </c>
-      <c r="J10">
-        <v>155</v>
-      </c>
-      <c r="K10">
-        <v>170</v>
-      </c>
-      <c r="L10">
-        <v>141</v>
-      </c>
-      <c r="M10">
-        <v>101</v>
+      <c r="B11">
+        <v>123</v>
+      </c>
+      <c r="C11">
+        <v>97</v>
+      </c>
+      <c r="D11">
+        <v>89</v>
+      </c>
+      <c r="E11">
+        <v>44</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
+      </c>
+      <c r="G11">
+        <v>23</v>
+      </c>
+      <c r="H11">
+        <v>27</v>
+      </c>
+      <c r="I11">
+        <v>56</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+      <c r="K11">
+        <v>76</v>
+      </c>
+      <c r="L11">
+        <v>61</v>
+      </c>
+      <c r="M11">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -45069,76 +44943,97 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
         <v>4</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -45147,31 +45042,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
         <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45179,19 +45083,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -45200,12 +45104,12 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -45213,10 +45117,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="I7">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -45225,37 +45126,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45263,40 +45167,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
         <v>7</v>
       </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
       <c r="M9">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45304,40 +45208,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="D10">
-        <v>445</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>307</v>
+        <v>188</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="I10">
-        <v>367</v>
+        <v>226</v>
       </c>
       <c r="J10">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="K10">
-        <v>167</v>
+        <v>295</v>
       </c>
       <c r="L10">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="M10">
-        <v>94</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45345,40 +45249,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C11">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="D11">
-        <v>474</v>
+        <v>270</v>
       </c>
       <c r="E11">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="F11">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="G11">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>338</v>
+        <v>198</v>
       </c>
       <c r="I11">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="J11">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>143</v>
+        <v>309</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -45931,37 +45835,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
         <v>4</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45969,44 +45870,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -46015,61 +45919,94 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
       </c>
       <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
       <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
       <c r="C6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -46078,31 +46015,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46110,37 +46056,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
+        <v>23</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
         <v>3</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46148,40 +46097,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>256</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>262</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="I10">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="J10">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="K10">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="L10">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46189,40 +46138,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="C11">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="D11">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>342</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="G11">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="H11">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="I11">
-        <v>56</v>
+        <v>236</v>
       </c>
       <c r="J11">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="K11">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="L11">
-        <v>61</v>
+        <v>323</v>
       </c>
       <c r="M11">
-        <v>53</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -46296,40 +46245,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>11</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46337,54 +46286,63 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
         <v>10</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -46395,40 +46353,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>32</v>
+      </c>
+      <c r="J5">
         <v>9</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
-      </c>
       <c r="K5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>8</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46436,42 +46394,60 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="D6">
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46479,40 +46455,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46520,40 +46496,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>15</v>
+      </c>
+      <c r="L9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>15</v>
-      </c>
-      <c r="K9">
-        <v>16</v>
-      </c>
-      <c r="L9">
-        <v>7</v>
-      </c>
       <c r="M9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46561,40 +46537,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>213</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>188</v>
+        <v>67</v>
       </c>
       <c r="F10">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="K10">
-        <v>295</v>
+        <v>37</v>
       </c>
       <c r="L10">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="M10">
-        <v>176</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46602,40 +46578,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>164</v>
       </c>
       <c r="D11">
-        <v>270</v>
+        <v>145</v>
       </c>
       <c r="E11">
-        <v>237</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="G11">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="H11">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="I11">
-        <v>308</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="K11">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="L11">
-        <v>309</v>
+        <v>128</v>
       </c>
       <c r="M11">
-        <v>207</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -46709,37 +46685,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>41</v>
+      </c>
+      <c r="L2">
+        <v>44</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46747,48 +46726,78 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -46796,40 +46805,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46837,54 +46846,72 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
       <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46892,40 +46919,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46933,40 +46960,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H9">
+        <v>59</v>
+      </c>
+      <c r="I9">
+        <v>50</v>
+      </c>
+      <c r="J9">
+        <v>61</v>
+      </c>
+      <c r="K9">
+        <v>47</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
         <v>17</v>
-      </c>
-      <c r="I9">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>23</v>
-      </c>
-      <c r="K9">
-        <v>23</v>
-      </c>
-      <c r="L9">
-        <v>12</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46974,40 +47001,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="C10">
-        <v>260</v>
+        <v>394</v>
       </c>
       <c r="D10">
-        <v>256</v>
+        <v>372</v>
       </c>
       <c r="E10">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="F10">
-        <v>211</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="H10">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I10">
-        <v>175</v>
+        <v>372</v>
       </c>
       <c r="J10">
-        <v>199</v>
+        <v>319</v>
       </c>
       <c r="K10">
-        <v>256</v>
+        <v>369</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>427</v>
       </c>
       <c r="M10">
-        <v>149</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47015,40 +47042,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>255</v>
+        <v>713</v>
       </c>
       <c r="C11">
-        <v>323</v>
+        <v>714</v>
       </c>
       <c r="D11">
-        <v>311</v>
+        <v>697</v>
       </c>
       <c r="E11">
-        <v>342</v>
+        <v>616</v>
       </c>
       <c r="F11">
-        <v>261</v>
+        <v>568</v>
       </c>
       <c r="G11">
-        <v>197</v>
+        <v>492</v>
       </c>
       <c r="H11">
-        <v>233</v>
+        <v>474</v>
       </c>
       <c r="I11">
-        <v>236</v>
+        <v>722</v>
       </c>
       <c r="J11">
-        <v>268</v>
+        <v>739</v>
       </c>
       <c r="K11">
-        <v>337</v>
+        <v>720</v>
       </c>
       <c r="L11">
-        <v>323</v>
+        <v>728</v>
       </c>
       <c r="M11">
-        <v>191</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -47122,40 +47149,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
         <v>12</v>
       </c>
-      <c r="E2">
-        <v>13</v>
-      </c>
-      <c r="F2">
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
         <v>17</v>
       </c>
-      <c r="G2">
-        <v>9</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
       <c r="K2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47163,40 +47190,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47210,18 +47237,9 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -47230,37 +47248,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>18</v>
       </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>32</v>
-      </c>
       <c r="J5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
         <v>15</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -47271,60 +47289,42 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47332,40 +47332,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I8">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L8">
         <v>26</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47373,40 +47373,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
       <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
         <v>6</v>
       </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9">
-        <v>15</v>
-      </c>
-      <c r="L9">
-        <v>9</v>
-      </c>
       <c r="M9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47414,40 +47414,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="J10">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47455,40 +47455,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="D11">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="E11">
+        <v>186</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11">
+        <v>112</v>
+      </c>
+      <c r="H11">
+        <v>125</v>
+      </c>
+      <c r="I11">
         <v>160</v>
       </c>
-      <c r="F11">
-        <v>142</v>
-      </c>
-      <c r="G11">
-        <v>126</v>
-      </c>
-      <c r="H11">
-        <v>130</v>
-      </c>
-      <c r="I11">
-        <v>175</v>
-      </c>
       <c r="J11">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="K11">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="L11">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="M11">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -47562,40 +47562,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="L2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47603,40 +47603,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C3">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3">
+        <v>33</v>
+      </c>
+      <c r="J3">
+        <v>36</v>
+      </c>
+      <c r="K3">
         <v>41</v>
       </c>
-      <c r="D3">
+      <c r="L3">
         <v>32</v>
       </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>44</v>
-      </c>
-      <c r="G3">
-        <v>35</v>
-      </c>
-      <c r="H3">
-        <v>31</v>
-      </c>
-      <c r="I3">
-        <v>36</v>
-      </c>
-      <c r="J3">
-        <v>30</v>
-      </c>
-      <c r="K3">
-        <v>31</v>
-      </c>
-      <c r="L3">
-        <v>22</v>
-      </c>
       <c r="M3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47644,34 +47644,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -47682,40 +47685,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="D5">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H5">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -47723,40 +47726,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
-      </c>
-      <c r="K6">
+      <c r="M6">
         <v>5</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -47764,31 +47767,37 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47796,40 +47805,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D8">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="F8">
+        <v>52</v>
+      </c>
+      <c r="G8">
         <v>35</v>
       </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
       <c r="H8">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="J8">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="K8">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="L8">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="M8">
-        <v>80</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47837,40 +47846,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47878,40 +47887,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C10">
-        <v>394</v>
+        <v>492</v>
       </c>
       <c r="D10">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E10">
-        <v>305</v>
+        <v>489</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>489</v>
       </c>
       <c r="G10">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H10">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="I10">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="J10">
-        <v>319</v>
+        <v>502</v>
       </c>
       <c r="K10">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="L10">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="M10">
-        <v>329</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47919,40 +47928,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>713</v>
+        <v>654</v>
       </c>
       <c r="C11">
-        <v>714</v>
+        <v>876</v>
       </c>
       <c r="D11">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="E11">
-        <v>616</v>
+        <v>789</v>
       </c>
       <c r="F11">
-        <v>568</v>
+        <v>728</v>
       </c>
       <c r="G11">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H11">
-        <v>474</v>
+        <v>565</v>
       </c>
       <c r="I11">
-        <v>722</v>
+        <v>767</v>
       </c>
       <c r="J11">
-        <v>739</v>
+        <v>949</v>
       </c>
       <c r="K11">
-        <v>720</v>
+        <v>973</v>
       </c>
       <c r="L11">
-        <v>728</v>
+        <v>703</v>
       </c>
       <c r="M11">
-        <v>531</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -48026,40 +48035,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>19</v>
-      </c>
       <c r="I2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48067,59 +48073,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48128,34 +48131,34 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>26</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48168,72 +48171,48 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48242,40 +48221,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>18</v>
       </c>
-      <c r="E8">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>88</v>
-      </c>
-      <c r="K8">
-        <v>46</v>
-      </c>
-      <c r="L8">
-        <v>50</v>
-      </c>
       <c r="M8">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48283,40 +48262,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="H9">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>38</v>
-      </c>
       <c r="L9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48324,40 +48303,40 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <v>192</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>142</v>
+      </c>
+      <c r="E10">
+        <v>135</v>
+      </c>
+      <c r="F10">
+        <v>184</v>
+      </c>
+      <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
         <v>112</v>
       </c>
-      <c r="C10">
-        <v>108</v>
-      </c>
-      <c r="D10">
-        <v>119</v>
-      </c>
-      <c r="E10">
-        <v>133</v>
-      </c>
-      <c r="F10">
-        <v>146</v>
-      </c>
-      <c r="G10">
-        <v>68</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
       <c r="I10">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="K10">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="L10">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48365,40 +48344,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="C11">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="E11">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F11">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H11">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="I11">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J11">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="K11">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="L11">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M11">
-        <v>207</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -48472,37 +48451,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48510,56 +48492,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48568,34 +48553,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
       <c r="H5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
         <v>13</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48608,48 +48593,72 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48658,40 +48667,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="K8">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48699,40 +48708,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
       <c r="G9">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48740,40 +48749,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="C10">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="D10">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="J10">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="L10">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="M10">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48781,40 +48790,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="C11">
+        <v>227</v>
+      </c>
+      <c r="D11">
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>248</v>
+      </c>
+      <c r="F11">
+        <v>249</v>
+      </c>
+      <c r="G11">
+        <v>169</v>
+      </c>
+      <c r="H11">
+        <v>193</v>
+      </c>
+      <c r="I11">
+        <v>251</v>
+      </c>
+      <c r="J11">
         <v>291</v>
       </c>
-      <c r="D11">
-        <v>212</v>
-      </c>
-      <c r="E11">
-        <v>216</v>
-      </c>
-      <c r="F11">
-        <v>247</v>
-      </c>
-      <c r="G11">
-        <v>155</v>
-      </c>
-      <c r="H11">
-        <v>179</v>
-      </c>
-      <c r="I11">
-        <v>238</v>
-      </c>
-      <c r="J11">
-        <v>318</v>
-      </c>
       <c r="K11">
-        <v>347</v>
+        <v>251</v>
       </c>
       <c r="L11">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="M11">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -48888,40 +48897,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>17</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
       <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48929,37 +48935,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -48969,16 +48975,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -48990,37 +48996,37 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
       <c r="M5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49028,41 +49034,38 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -49071,40 +49074,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
       <c r="I8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49112,37 +49115,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <v>4</v>
       </c>
-      <c r="H9">
-        <v>15</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
       <c r="K9">
-        <v>4</v>
-      </c>
-      <c r="L9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -49153,40 +49153,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="M10">
-        <v>69</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49194,40 +49194,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="J11">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="K11">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="L11">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -49301,37 +49301,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49339,56 +49342,44 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -49397,40 +49388,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>16</v>
       </c>
-      <c r="C5">
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
       <c r="K5">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49438,16 +49429,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -49458,10 +49446,10 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -49469,7 +49457,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -49478,40 +49466,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8">
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>37</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>23</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>8</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49519,37 +49507,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49557,40 +49548,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="G10">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="H10">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="K10">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="L10">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="M10">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49598,40 +49589,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="C11">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="D11">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="F11">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="H11">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="I11">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="J11">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="L11">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="M11">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -49705,40 +49696,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49746,45 +49737,54 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
         <v>5</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="M3">
         <v>5</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -49792,40 +49792,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49833,35 +49833,38 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>1</v>
+      <c r="L6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -49870,40 +49873,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>14</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J8">
         <v>37</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49911,39 +49914,36 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
       <c r="E9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
         <v>7</v>
       </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
       <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
         <v>3</v>
       </c>
     </row>
@@ -49952,40 +49952,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="E10">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="F10">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G10">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="J10">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="K10">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="L10">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="M10">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49993,40 +49993,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="C11">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D11">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="F11">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G11">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="I11">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="J11">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="K11">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="L11">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="M11">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4379</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7125</v>
       </c>
       <c r="M3">
-        <v>4925</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6212</v>
       </c>
       <c r="M5">
-        <v>3800</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1953</v>
       </c>
       <c r="M6">
-        <v>1308</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>434</v>
       </c>
       <c r="M7">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17256</v>
       </c>
       <c r="M8">
-        <v>12462</v>
+        <v>12527</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5817</v>
       </c>
       <c r="M9">
-        <v>3225</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1238,10 +1238,10 @@
         <v>61332</v>
       </c>
       <c r="L10">
-        <v>58723</v>
+        <v>58724</v>
       </c>
       <c r="M10">
-        <v>39759</v>
+        <v>39885</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1279,10 +1279,10 @@
         <v>118950</v>
       </c>
       <c r="L11">
-        <v>104482</v>
+        <v>104483</v>
       </c>
       <c r="M11">
-        <v>70409</v>
+        <v>70711</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1512,7 +1512,7 @@
         <v>304</v>
       </c>
       <c r="M5">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3396</v>
       </c>
       <c r="M11">
-        <v>2393</v>
+        <v>2400</v>
       </c>
     </row>
   </sheetData>
@@ -2263,7 +2263,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2467,6 +2467,9 @@
       <c r="L7">
         <v>1</v>
       </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
@@ -2588,7 +2591,7 @@
         <v>1203</v>
       </c>
       <c r="M10">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2629,7 +2632,7 @@
         <v>1756</v>
       </c>
       <c r="M11">
-        <v>1269</v>
+        <v>1273</v>
       </c>
     </row>
   </sheetData>
@@ -2979,7 +2982,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3061,7 +3064,7 @@
         <v>824</v>
       </c>
       <c r="M10">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3102,7 +3105,7 @@
         <v>1155</v>
       </c>
       <c r="M11">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
   </sheetData>
@@ -3449,7 +3452,7 @@
         <v>227</v>
       </c>
       <c r="M8">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3572,7 +3575,7 @@
         <v>782</v>
       </c>
       <c r="M11">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -3925,7 +3928,7 @@
         <v>138</v>
       </c>
       <c r="M8">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4007,7 +4010,7 @@
         <v>606</v>
       </c>
       <c r="M10">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4048,7 +4051,7 @@
         <v>1015</v>
       </c>
       <c r="M11">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
   </sheetData>
@@ -4155,7 +4158,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4196,7 +4199,7 @@
         <v>504</v>
       </c>
       <c r="M3">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4278,7 +4281,7 @@
         <v>216</v>
       </c>
       <c r="M5">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4360,7 +4363,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4401,7 +4404,7 @@
         <v>777</v>
       </c>
       <c r="M8">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4442,7 +4445,7 @@
         <v>342</v>
       </c>
       <c r="M9">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4483,7 +4486,7 @@
         <v>1969</v>
       </c>
       <c r="M10">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4524,7 +4527,7 @@
         <v>4423</v>
       </c>
       <c r="M11">
-        <v>3005</v>
+        <v>3018</v>
       </c>
     </row>
   </sheetData>
@@ -4713,7 +4716,7 @@
         <v>14</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4795,7 +4798,7 @@
         <v>43</v>
       </c>
       <c r="M6">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4877,7 +4880,7 @@
         <v>572</v>
       </c>
       <c r="M8">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4959,7 +4962,7 @@
         <v>939</v>
       </c>
       <c r="M10">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5000,7 +5003,7 @@
         <v>2412</v>
       </c>
       <c r="M11">
-        <v>1550</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -5353,7 +5356,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5476,7 +5479,7 @@
         <v>1505</v>
       </c>
       <c r="M11">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -5624,7 +5627,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5747,7 +5750,7 @@
         <v>22</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5826,7 +5829,7 @@
         <v>437</v>
       </c>
       <c r="M8">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5949,7 +5952,7 @@
         <v>1425</v>
       </c>
       <c r="M11">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -6097,7 +6100,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6214,7 +6217,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6296,7 +6299,7 @@
         <v>208</v>
       </c>
       <c r="M8">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6337,7 +6340,7 @@
         <v>161</v>
       </c>
       <c r="M9">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6378,7 +6381,7 @@
         <v>2713</v>
       </c>
       <c r="M10">
-        <v>1683</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6419,7 +6422,7 @@
         <v>3356</v>
       </c>
       <c r="M11">
-        <v>2124</v>
+        <v>2141</v>
       </c>
     </row>
   </sheetData>
@@ -6567,7 +6570,7 @@
         <v>239</v>
       </c>
       <c r="M3">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6608,7 +6611,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6649,7 +6652,7 @@
         <v>266</v>
       </c>
       <c r="M5">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6690,7 +6693,7 @@
         <v>782</v>
       </c>
       <c r="M6">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6731,7 +6734,7 @@
         <v>2412</v>
       </c>
       <c r="M7">
-        <v>1550</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6772,7 +6775,7 @@
         <v>4423</v>
       </c>
       <c r="M8">
-        <v>3005</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6813,7 +6816,7 @@
         <v>442</v>
       </c>
       <c r="M9">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6854,7 +6857,7 @@
         <v>1155</v>
       </c>
       <c r="M10">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6895,7 +6898,7 @@
         <v>1779</v>
       </c>
       <c r="M11">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6936,7 +6939,7 @@
         <v>414</v>
       </c>
       <c r="M12">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -7018,7 +7021,7 @@
         <v>728</v>
       </c>
       <c r="M14">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7059,7 +7062,7 @@
         <v>812</v>
       </c>
       <c r="M15">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7100,7 +7103,7 @@
         <v>746</v>
       </c>
       <c r="M16">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7182,7 +7185,7 @@
         <v>642</v>
       </c>
       <c r="M18">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7223,7 +7226,7 @@
         <v>2333</v>
       </c>
       <c r="M19">
-        <v>1435</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7264,7 +7267,7 @@
         <v>1697</v>
       </c>
       <c r="M20">
-        <v>1152</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7305,7 +7308,7 @@
         <v>277</v>
       </c>
       <c r="M21">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7387,7 +7390,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7428,7 +7431,7 @@
         <v>533</v>
       </c>
       <c r="M24">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7469,7 +7472,7 @@
         <v>580</v>
       </c>
       <c r="M25">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7551,7 +7554,7 @@
         <v>1242</v>
       </c>
       <c r="M27">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7633,7 +7636,7 @@
         <v>3363</v>
       </c>
       <c r="M29">
-        <v>2268</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7674,7 +7677,7 @@
         <v>276</v>
       </c>
       <c r="M30">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7715,7 +7718,7 @@
         <v>1015</v>
       </c>
       <c r="M31">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7756,7 +7759,7 @@
         <v>180</v>
       </c>
       <c r="M32">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -7797,7 +7800,7 @@
         <v>2445</v>
       </c>
       <c r="M33">
-        <v>1780</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7879,7 +7882,7 @@
         <v>323</v>
       </c>
       <c r="M35">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7920,7 +7923,7 @@
         <v>1425</v>
       </c>
       <c r="M36">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7961,7 +7964,7 @@
         <v>2337</v>
       </c>
       <c r="M37">
-        <v>1580</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8043,7 +8046,7 @@
         <v>181</v>
       </c>
       <c r="M39">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -8084,7 +8087,7 @@
         <v>329</v>
       </c>
       <c r="M40">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -8125,7 +8128,7 @@
         <v>361</v>
       </c>
       <c r="M41">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8166,7 +8169,7 @@
         <v>2494</v>
       </c>
       <c r="M42">
-        <v>2142</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8207,7 +8210,7 @@
         <v>1462</v>
       </c>
       <c r="M43">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8289,7 +8292,7 @@
         <v>141</v>
       </c>
       <c r="M45">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -8371,7 +8374,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8412,7 +8415,7 @@
         <v>2767</v>
       </c>
       <c r="M48">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8453,7 +8456,7 @@
         <v>1779</v>
       </c>
       <c r="M49">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8494,7 +8497,7 @@
         <v>1020</v>
       </c>
       <c r="M50">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8535,7 +8538,7 @@
         <v>1445</v>
       </c>
       <c r="M51">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8576,7 +8579,7 @@
         <v>1413</v>
       </c>
       <c r="M52">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8617,7 +8620,7 @@
         <v>1756</v>
       </c>
       <c r="M53">
-        <v>1269</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8658,7 +8661,7 @@
         <v>3832</v>
       </c>
       <c r="M54">
-        <v>2495</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8699,7 +8702,7 @@
         <v>1080</v>
       </c>
       <c r="M55">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8740,7 +8743,7 @@
         <v>621</v>
       </c>
       <c r="M56">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8781,7 +8784,7 @@
         <v>467</v>
       </c>
       <c r="M57">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8822,7 +8825,7 @@
         <v>143</v>
       </c>
       <c r="M58">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8863,7 +8866,7 @@
         <v>298</v>
       </c>
       <c r="M59">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8904,7 +8907,7 @@
         <v>739</v>
       </c>
       <c r="M60">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -9024,10 +9027,10 @@
         <v>1076</v>
       </c>
       <c r="L63">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="M63">
-        <v>351</v>
+        <v>376</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9068,7 +9071,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9109,7 +9112,7 @@
         <v>1385</v>
       </c>
       <c r="M65">
-        <v>961</v>
+        <v>967</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9191,7 +9194,7 @@
         <v>1920</v>
       </c>
       <c r="M67">
-        <v>1350</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9396,7 +9399,7 @@
         <v>663</v>
       </c>
       <c r="M72">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9437,7 +9440,7 @@
         <v>1349</v>
       </c>
       <c r="M73">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9478,7 +9481,7 @@
         <v>309</v>
       </c>
       <c r="M74">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9560,7 +9563,7 @@
         <v>3356</v>
       </c>
       <c r="M76">
-        <v>2124</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9601,7 +9604,7 @@
         <v>374</v>
       </c>
       <c r="M77">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9642,7 +9645,7 @@
         <v>1582</v>
       </c>
       <c r="M78">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9683,7 +9686,7 @@
         <v>2091</v>
       </c>
       <c r="M79">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9724,7 +9727,7 @@
         <v>470</v>
       </c>
       <c r="M80">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9847,7 +9850,7 @@
         <v>1487</v>
       </c>
       <c r="M83">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9888,7 +9891,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9929,7 +9932,7 @@
         <v>3396</v>
       </c>
       <c r="M85">
-        <v>2393</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9970,7 +9973,7 @@
         <v>902</v>
       </c>
       <c r="M86">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -10011,7 +10014,7 @@
         <v>437</v>
       </c>
       <c r="M87">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10052,7 +10055,7 @@
         <v>874</v>
       </c>
       <c r="M88">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10093,7 +10096,7 @@
         <v>2036</v>
       </c>
       <c r="M89">
-        <v>1451</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10134,7 +10137,7 @@
         <v>1090</v>
       </c>
       <c r="M90">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10175,7 +10178,7 @@
         <v>968</v>
       </c>
       <c r="M91">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10216,7 +10219,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10257,7 +10260,7 @@
         <v>803</v>
       </c>
       <c r="M93">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10298,7 +10301,7 @@
         <v>2671</v>
       </c>
       <c r="M94">
-        <v>1917</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10339,7 +10342,7 @@
         <v>1241</v>
       </c>
       <c r="M95">
-        <v>852</v>
+        <v>858</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10380,7 +10383,7 @@
         <v>1359</v>
       </c>
       <c r="M96">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10421,7 +10424,7 @@
         <v>1719</v>
       </c>
       <c r="M97">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10462,7 +10465,7 @@
         <v>1128</v>
       </c>
       <c r="M98">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10503,7 +10506,7 @@
         <v>1505</v>
       </c>
       <c r="M99">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10582,10 +10585,10 @@
         <v>118950</v>
       </c>
       <c r="L101">
-        <v>104482</v>
+        <v>104483</v>
       </c>
       <c r="M101">
-        <v>70409</v>
+        <v>70711</v>
       </c>
     </row>
   </sheetData>
@@ -11104,7 +11107,7 @@
         <v>1379</v>
       </c>
       <c r="M10">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11145,7 +11148,7 @@
         <v>1779</v>
       </c>
       <c r="M11">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
   </sheetData>
@@ -11556,7 +11559,7 @@
         <v>169</v>
       </c>
       <c r="M10">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11597,7 +11600,7 @@
         <v>298</v>
       </c>
       <c r="M11">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -12023,7 +12026,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12064,7 +12067,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
   </sheetData>
@@ -12171,7 +12174,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12449,7 +12452,7 @@
         <v>181</v>
       </c>
       <c r="M9">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -12863,7 +12866,7 @@
         <v>450</v>
       </c>
       <c r="M10">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12904,7 +12907,7 @@
         <v>663</v>
       </c>
       <c r="M11">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -13052,7 +13055,7 @@
         <v>235</v>
       </c>
       <c r="M3">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13093,7 +13096,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13257,7 +13260,7 @@
         <v>498</v>
       </c>
       <c r="M8">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13298,7 +13301,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13339,7 +13342,7 @@
         <v>1167</v>
       </c>
       <c r="M10">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13380,7 +13383,7 @@
         <v>2494</v>
       </c>
       <c r="M11">
-        <v>2142</v>
+        <v>2153</v>
       </c>
     </row>
   </sheetData>
@@ -13528,7 +13531,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13610,7 +13613,7 @@
         <v>95</v>
       </c>
       <c r="M5">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13733,7 +13736,7 @@
         <v>319</v>
       </c>
       <c r="M8">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13815,7 +13818,7 @@
         <v>740</v>
       </c>
       <c r="M10">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13856,7 +13859,7 @@
         <v>1920</v>
       </c>
       <c r="M11">
-        <v>1350</v>
+        <v>1358</v>
       </c>
     </row>
   </sheetData>
@@ -13963,7 +13966,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14127,7 +14130,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14320,7 +14323,7 @@
         <v>361</v>
       </c>
       <c r="M11">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -14628,7 +14631,7 @@
         <v>41</v>
       </c>
       <c r="M8">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14710,7 +14713,7 @@
         <v>97</v>
       </c>
       <c r="M10">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14751,7 +14754,7 @@
         <v>180</v>
       </c>
       <c r="M11">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -14858,7 +14861,7 @@
         <v>85</v>
       </c>
       <c r="M2">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15101,7 +15104,7 @@
         <v>358</v>
       </c>
       <c r="M8">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15142,7 +15145,7 @@
         <v>207</v>
       </c>
       <c r="M9">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -15183,7 +15186,7 @@
         <v>2940</v>
       </c>
       <c r="M10">
-        <v>1909</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15224,7 +15227,7 @@
         <v>3832</v>
       </c>
       <c r="M11">
-        <v>2495</v>
+        <v>2508</v>
       </c>
     </row>
   </sheetData>
@@ -15638,7 +15641,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15679,7 +15682,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -16014,7 +16017,7 @@
         <v>360</v>
       </c>
       <c r="M8">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16055,7 +16058,7 @@
         <v>94</v>
       </c>
       <c r="M9">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16096,7 +16099,7 @@
         <v>1954</v>
       </c>
       <c r="M10">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16137,7 +16140,7 @@
         <v>2671</v>
       </c>
       <c r="M11">
-        <v>1917</v>
+        <v>1923</v>
       </c>
     </row>
   </sheetData>
@@ -17039,7 +17042,7 @@
         <v>976</v>
       </c>
       <c r="M10">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17080,7 +17083,7 @@
         <v>1582</v>
       </c>
       <c r="M11">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>
@@ -17310,7 +17313,7 @@
         <v>44</v>
       </c>
       <c r="M5">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17515,7 +17518,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17556,7 +17559,7 @@
         <v>442</v>
       </c>
       <c r="M11">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -17964,7 +17967,7 @@
         <v>791</v>
       </c>
       <c r="M10">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18005,7 +18008,7 @@
         <v>1128</v>
       </c>
       <c r="M11">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -18596,7 +18599,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18678,7 +18681,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18719,7 +18722,7 @@
         <v>48</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18801,7 +18804,7 @@
         <v>288</v>
       </c>
       <c r="M8">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18883,7 +18886,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18924,7 +18927,7 @@
         <v>1697</v>
       </c>
       <c r="M11">
-        <v>1152</v>
+        <v>1161</v>
       </c>
     </row>
   </sheetData>
@@ -19072,7 +19075,7 @@
         <v>294</v>
       </c>
       <c r="M3">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19277,7 +19280,7 @@
         <v>418</v>
       </c>
       <c r="M8">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19318,7 +19321,7 @@
         <v>210</v>
       </c>
       <c r="M9">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19359,7 +19362,7 @@
         <v>902</v>
       </c>
       <c r="M10">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19400,7 +19403,7 @@
         <v>2337</v>
       </c>
       <c r="M11">
-        <v>1580</v>
+        <v>1584</v>
       </c>
     </row>
   </sheetData>
@@ -19753,7 +19756,7 @@
         <v>184</v>
       </c>
       <c r="M8">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19876,7 +19879,7 @@
         <v>1413</v>
       </c>
       <c r="M11">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -19983,7 +19986,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20024,7 +20027,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20147,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -20311,7 +20314,7 @@
         <v>492</v>
       </c>
       <c r="M10">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20352,7 +20355,7 @@
         <v>1241</v>
       </c>
       <c r="M11">
-        <v>852</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -20664,7 +20667,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -20828,7 +20831,7 @@
         <v>874</v>
       </c>
       <c r="M11">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -21428,7 +21431,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21510,7 +21513,7 @@
         <v>101</v>
       </c>
       <c r="M5">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21633,7 +21636,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21756,7 +21759,7 @@
         <v>1385</v>
       </c>
       <c r="M11">
-        <v>961</v>
+        <v>967</v>
       </c>
     </row>
   </sheetData>
@@ -21863,7 +21866,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22097,7 +22100,7 @@
         <v>56</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22220,7 +22223,7 @@
         <v>467</v>
       </c>
       <c r="M11">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -22368,7 +22371,7 @@
         <v>131</v>
       </c>
       <c r="M3">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22573,7 +22576,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22614,7 +22617,7 @@
         <v>39</v>
       </c>
       <c r="M9">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -22696,7 +22699,7 @@
         <v>968</v>
       </c>
       <c r="M11">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -23272,7 +23275,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23447,7 +23450,7 @@
         <v>189</v>
       </c>
       <c r="M8">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23570,7 +23573,7 @@
         <v>1462</v>
       </c>
       <c r="M11">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -23677,7 +23680,7 @@
         <v>187</v>
       </c>
       <c r="M2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23923,7 +23926,7 @@
         <v>469</v>
       </c>
       <c r="M8">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24005,7 +24008,7 @@
         <v>863</v>
       </c>
       <c r="M10">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24046,7 +24049,7 @@
         <v>2091</v>
       </c>
       <c r="M11">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
   </sheetData>
@@ -24812,7 +24815,7 @@
         <v>61</v>
       </c>
       <c r="M8">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24894,7 +24897,7 @@
         <v>302</v>
       </c>
       <c r="M10">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24935,7 +24938,7 @@
         <v>437</v>
       </c>
       <c r="M11">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -25355,7 +25358,7 @@
         <v>750</v>
       </c>
       <c r="M10">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25396,7 +25399,7 @@
         <v>1020</v>
       </c>
       <c r="M11">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -25503,7 +25506,7 @@
         <v>370</v>
       </c>
       <c r="M2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25544,7 +25547,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25667,7 +25670,7 @@
         <v>66</v>
       </c>
       <c r="M6">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25749,7 +25752,7 @@
         <v>639</v>
       </c>
       <c r="M8">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25790,7 +25793,7 @@
         <v>287</v>
       </c>
       <c r="M9">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -25831,7 +25834,7 @@
         <v>1272</v>
       </c>
       <c r="M10">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25872,7 +25875,7 @@
         <v>3363</v>
       </c>
       <c r="M11">
-        <v>2268</v>
+        <v>2278</v>
       </c>
     </row>
   </sheetData>
@@ -26662,7 +26665,7 @@
         <v>225</v>
       </c>
       <c r="M8">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26785,7 +26788,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -27666,7 +27669,7 @@
         <v>1425</v>
       </c>
       <c r="M10">
-        <v>1049</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27707,7 +27710,7 @@
         <v>2036</v>
       </c>
       <c r="M11">
-        <v>1451</v>
+        <v>1458</v>
       </c>
     </row>
   </sheetData>
@@ -27855,7 +27858,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28142,7 +28145,7 @@
         <v>587</v>
       </c>
       <c r="M10">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28183,7 +28186,7 @@
         <v>1080</v>
       </c>
       <c r="M11">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
   </sheetData>
@@ -28331,7 +28334,7 @@
         <v>180</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28536,7 +28539,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28577,7 +28580,7 @@
         <v>165</v>
       </c>
       <c r="M9">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -28659,7 +28662,7 @@
         <v>2333</v>
       </c>
       <c r="M11">
-        <v>1435</v>
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
@@ -28807,7 +28810,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29053,7 +29056,7 @@
         <v>38</v>
       </c>
       <c r="M9">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29094,7 +29097,7 @@
         <v>425</v>
       </c>
       <c r="M10">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29135,7 +29138,7 @@
         <v>812</v>
       </c>
       <c r="M11">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -29488,7 +29491,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29529,7 +29532,7 @@
         <v>107</v>
       </c>
       <c r="M9">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29611,7 +29614,7 @@
         <v>1487</v>
       </c>
       <c r="M11">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -30031,7 +30034,7 @@
         <v>108</v>
       </c>
       <c r="M10">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30072,7 +30075,7 @@
         <v>276</v>
       </c>
       <c r="M11">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -30179,7 +30182,7 @@
         <v>133</v>
       </c>
       <c r="M2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30220,7 +30223,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30422,7 +30425,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30463,7 +30466,7 @@
         <v>90</v>
       </c>
       <c r="M9">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -30504,7 +30507,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30545,7 +30548,7 @@
         <v>1779</v>
       </c>
       <c r="M11">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
   </sheetData>
@@ -30923,7 +30926,7 @@
         <v>584</v>
       </c>
       <c r="M10">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30964,7 +30967,7 @@
         <v>621</v>
       </c>
       <c r="M11">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -31393,7 +31396,7 @@
         <v>1107</v>
       </c>
       <c r="M10">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31434,7 +31437,7 @@
         <v>1719</v>
       </c>
       <c r="M11">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
@@ -31851,7 +31854,7 @@
         <v>307</v>
       </c>
       <c r="M10">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31892,7 +31895,7 @@
         <v>533</v>
       </c>
       <c r="M11">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -32283,7 +32286,7 @@
         <v>38</v>
       </c>
       <c r="M9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -32365,7 +32368,7 @@
         <v>739</v>
       </c>
       <c r="M11">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -32718,7 +32721,7 @@
         <v>185</v>
       </c>
       <c r="M8">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32841,7 +32844,7 @@
         <v>642</v>
       </c>
       <c r="M11">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -33071,7 +33074,7 @@
         <v>82</v>
       </c>
       <c r="M5">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -33276,7 +33279,7 @@
         <v>480</v>
       </c>
       <c r="M10">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33317,7 +33320,7 @@
         <v>1090</v>
       </c>
       <c r="M11">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -33740,7 +33743,7 @@
         <v>553</v>
       </c>
       <c r="M10">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33781,7 +33784,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
@@ -34095,7 +34098,7 @@
         <v>103</v>
       </c>
       <c r="M8">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -34218,7 +34221,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -34486,7 +34489,7 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -34609,7 +34612,7 @@
         <v>57</v>
       </c>
       <c r="M9">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -34650,7 +34653,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34691,7 +34694,7 @@
         <v>1445</v>
       </c>
       <c r="M11">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -34839,7 +34842,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35167,7 +35170,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -35517,7 +35520,7 @@
         <v>207</v>
       </c>
       <c r="M8">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35640,7 +35643,7 @@
         <v>1349</v>
       </c>
       <c r="M11">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -35747,7 +35750,7 @@
         <v>78</v>
       </c>
       <c r="M2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35788,7 +35791,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35993,7 +35996,7 @@
         <v>251</v>
       </c>
       <c r="M8">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36034,7 +36037,7 @@
         <v>67</v>
       </c>
       <c r="M9">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -36075,7 +36078,7 @@
         <v>762</v>
       </c>
       <c r="M10">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36116,7 +36119,7 @@
         <v>1359</v>
       </c>
       <c r="M11">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -36223,7 +36226,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -36457,7 +36460,7 @@
         <v>126</v>
       </c>
       <c r="M8">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36539,7 +36542,7 @@
         <v>814</v>
       </c>
       <c r="M10">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36580,7 +36583,7 @@
         <v>1242</v>
       </c>
       <c r="M11">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -37627,7 +37630,7 @@
         <v>48</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -37811,7 +37814,7 @@
         <v>587</v>
       </c>
       <c r="M10">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37852,7 +37855,7 @@
         <v>746</v>
       </c>
       <c r="M11">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -38606,7 +38609,7 @@
         <v>69</v>
       </c>
       <c r="M8">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -38729,7 +38732,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -40035,7 +40038,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40076,7 +40079,7 @@
         <v>277</v>
       </c>
       <c r="M11">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -40224,7 +40227,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -40475,7 +40478,7 @@
         <v>253</v>
       </c>
       <c r="M10">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40516,7 +40519,7 @@
         <v>414</v>
       </c>
       <c r="M11">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -40664,7 +40667,7 @@
         <v>69</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -40933,7 +40936,7 @@
         <v>2032</v>
       </c>
       <c r="M10">
-        <v>1482</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40974,7 +40977,7 @@
         <v>2767</v>
       </c>
       <c r="M11">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
   </sheetData>
@@ -41081,7 +41084,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41201,7 +41204,7 @@
         <v>50</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41315,7 +41318,7 @@
         <v>156</v>
       </c>
       <c r="M8">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41438,7 +41441,7 @@
         <v>803</v>
       </c>
       <c r="M11">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -41545,7 +41548,7 @@
         <v>42</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41626,6 +41629,9 @@
       <c r="L4">
         <v>2</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -41870,7 +41876,7 @@
         <v>218</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41911,7 +41917,7 @@
         <v>580</v>
       </c>
       <c r="M11">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -42210,7 +42216,7 @@
         <v>30</v>
       </c>
       <c r="M8">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42292,7 +42298,7 @@
         <v>366</v>
       </c>
       <c r="M10">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42333,7 +42339,7 @@
         <v>470</v>
       </c>
       <c r="M11">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -43184,7 +43190,7 @@
         <v>660</v>
       </c>
       <c r="M10">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43225,7 +43231,7 @@
         <v>902</v>
       </c>
       <c r="M11">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -43455,7 +43461,7 @@
         <v>13</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43701,7 +43707,7 @@
         <v>374</v>
       </c>
       <c r="M11">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -44077,7 +44083,7 @@
         <v>74</v>
       </c>
       <c r="M9">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44118,7 +44124,7 @@
         <v>141</v>
       </c>
       <c r="M10">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -44460,7 +44466,7 @@
         <v>129</v>
       </c>
       <c r="M10">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44501,7 +44507,7 @@
         <v>143</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -45241,7 +45247,7 @@
         <v>264</v>
       </c>
       <c r="M10">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45282,7 +45288,7 @@
         <v>309</v>
       </c>
       <c r="M11">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -45389,7 +45395,7 @@
         <v>266</v>
       </c>
       <c r="M2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45430,7 +45436,7 @@
         <v>342</v>
       </c>
       <c r="M3">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45553,7 +45559,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -45635,7 +45641,7 @@
         <v>460</v>
       </c>
       <c r="M8">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45676,7 +45682,7 @@
         <v>271</v>
       </c>
       <c r="M9">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45717,7 +45723,7 @@
         <v>877</v>
       </c>
       <c r="M10">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45758,7 +45764,7 @@
         <v>2445</v>
       </c>
       <c r="M11">
-        <v>1780</v>
+        <v>1791</v>
       </c>
     </row>
   </sheetData>
@@ -46130,7 +46136,7 @@
         <v>265</v>
       </c>
       <c r="M10">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46171,7 +46177,7 @@
         <v>323</v>
       </c>
       <c r="M11">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -47034,7 +47040,7 @@
         <v>427</v>
       </c>
       <c r="M10">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47075,7 +47081,7 @@
         <v>728</v>
       </c>
       <c r="M11">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -48782,7 +48788,7 @@
         <v>121</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48823,7 +48829,7 @@
         <v>266</v>
       </c>
       <c r="M11">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -49581,7 +49587,7 @@
         <v>170</v>
       </c>
       <c r="M10">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49622,7 +49628,7 @@
         <v>239</v>
       </c>
       <c r="M11">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -86,26 +86,26 @@
     <sheet name="North Park" sheetId="77" r:id="rId77"/>
     <sheet name="Chinatown" sheetId="78" r:id="rId78"/>
     <sheet name="Beverly" sheetId="79" r:id="rId79"/>
-    <sheet name="West Lawn" sheetId="80" r:id="rId80"/>
-    <sheet name="East Side" sheetId="81" r:id="rId81"/>
+    <sheet name="Sauganash,Forest Glen" sheetId="80" r:id="rId80"/>
+    <sheet name="Garfield Ridge" sheetId="81" r:id="rId81"/>
     <sheet name="Rush &amp; Division" sheetId="82" r:id="rId82"/>
-    <sheet name="Pullman" sheetId="83" r:id="rId83"/>
-    <sheet name="Streeterville" sheetId="84" r:id="rId84"/>
-    <sheet name="Riverdale" sheetId="85" r:id="rId85"/>
-    <sheet name="Jackson Park" sheetId="86" r:id="rId86"/>
-    <sheet name="Millenium Park" sheetId="87" r:id="rId87"/>
-    <sheet name="Museum Campus" sheetId="88" r:id="rId88"/>
-    <sheet name="Printers Row" sheetId="89" r:id="rId89"/>
-    <sheet name="Gold Coast" sheetId="90" r:id="rId90"/>
-    <sheet name="Burnside" sheetId="91" r:id="rId91"/>
-    <sheet name="Bridgeport" sheetId="92" r:id="rId92"/>
-    <sheet name="Mount Greenwood" sheetId="93" r:id="rId93"/>
-    <sheet name="Garfield Ridge" sheetId="94" r:id="rId94"/>
-    <sheet name="Wrigleyville" sheetId="95" r:id="rId95"/>
-    <sheet name="Armour Square" sheetId="96" r:id="rId96"/>
-    <sheet name="Edison Park" sheetId="97" r:id="rId97"/>
-    <sheet name="Andersonville" sheetId="98" r:id="rId98"/>
-    <sheet name="Sauganash,Forest Glen" sheetId="99" r:id="rId99"/>
+    <sheet name="West Lawn" sheetId="83" r:id="rId83"/>
+    <sheet name="East Side" sheetId="84" r:id="rId84"/>
+    <sheet name="Pullman" sheetId="85" r:id="rId85"/>
+    <sheet name="Streeterville" sheetId="86" r:id="rId86"/>
+    <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
+    <sheet name="Jackson Park" sheetId="88" r:id="rId88"/>
+    <sheet name="Millenium Park" sheetId="89" r:id="rId89"/>
+    <sheet name="Museum Campus" sheetId="90" r:id="rId90"/>
+    <sheet name="Printers Row" sheetId="91" r:id="rId91"/>
+    <sheet name="Gold Coast" sheetId="92" r:id="rId92"/>
+    <sheet name="Burnside" sheetId="93" r:id="rId93"/>
+    <sheet name="Bridgeport" sheetId="94" r:id="rId94"/>
+    <sheet name="Armour Square" sheetId="95" r:id="rId95"/>
+    <sheet name="Wrigleyville" sheetId="96" r:id="rId96"/>
+    <sheet name="Mount Greenwood" sheetId="97" r:id="rId97"/>
+    <sheet name="Edison Park" sheetId="98" r:id="rId98"/>
+    <sheet name="Andersonville" sheetId="99" r:id="rId99"/>
     <sheet name="Grant Park" sheetId="100" r:id="rId100"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41051,40 +41051,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41092,77 +41092,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
       <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
     </row>
@@ -41171,40 +41147,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41212,72 +41188,39 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>6</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
         <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41285,40 +41228,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H8">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="K8">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="M8">
-        <v>132</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41326,40 +41269,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>32</v>
-      </c>
-      <c r="M9">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41367,40 +41307,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>641</v>
+        <v>119</v>
       </c>
       <c r="C10">
-        <v>540</v>
+        <v>146</v>
       </c>
       <c r="D10">
-        <v>482</v>
+        <v>152</v>
       </c>
       <c r="E10">
-        <v>485</v>
+        <v>152</v>
       </c>
       <c r="F10">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="G10">
-        <v>310</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>248</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>383</v>
+        <v>137</v>
       </c>
       <c r="J10">
-        <v>360</v>
+        <v>151</v>
       </c>
       <c r="K10">
-        <v>479</v>
+        <v>146</v>
       </c>
       <c r="L10">
-        <v>486</v>
+        <v>117</v>
       </c>
       <c r="M10">
-        <v>282</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41408,40 +41348,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1023</v>
+        <v>194</v>
       </c>
       <c r="C11">
-        <v>1021</v>
+        <v>271</v>
       </c>
       <c r="D11">
-        <v>860</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>846</v>
+        <v>246</v>
       </c>
       <c r="F11">
-        <v>718</v>
+        <v>186</v>
       </c>
       <c r="G11">
-        <v>519</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>501</v>
+        <v>156</v>
       </c>
       <c r="I11">
-        <v>727</v>
+        <v>222</v>
       </c>
       <c r="J11">
-        <v>845</v>
+        <v>256</v>
       </c>
       <c r="K11">
-        <v>936</v>
+        <v>243</v>
       </c>
       <c r="L11">
-        <v>803</v>
+        <v>187</v>
       </c>
       <c r="M11">
-        <v>533</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -41515,40 +41455,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="L2">
         <v>42</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -41556,40 +41496,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>33</v>
       </c>
-      <c r="G3">
-        <v>38</v>
-      </c>
-      <c r="H3">
-        <v>45</v>
-      </c>
       <c r="I3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41597,40 +41537,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -41638,40 +41578,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>119</v>
+      </c>
+      <c r="E5">
+        <v>112</v>
+      </c>
+      <c r="F5">
+        <v>99</v>
+      </c>
+      <c r="G5">
+        <v>66</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <v>66</v>
+      </c>
+      <c r="J5">
         <v>65</v>
       </c>
-      <c r="D5">
-        <v>54</v>
-      </c>
-      <c r="E5">
-        <v>46</v>
-      </c>
-      <c r="F5">
-        <v>31</v>
-      </c>
-      <c r="G5">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>30</v>
-      </c>
-      <c r="I5">
-        <v>35</v>
-      </c>
-      <c r="J5">
-        <v>33</v>
-      </c>
       <c r="K5">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41679,37 +41619,37 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>7</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
         <v>9</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -41720,40 +41660,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -41761,40 +41698,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="I8">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="J8">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="K8">
-        <v>174</v>
+        <v>339</v>
       </c>
       <c r="L8">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41802,40 +41739,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="I9">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41843,40 +41780,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>180</v>
+        <v>395</v>
       </c>
       <c r="C10">
-        <v>215</v>
+        <v>492</v>
       </c>
       <c r="D10">
-        <v>184</v>
+        <v>381</v>
       </c>
       <c r="E10">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="F10">
-        <v>137</v>
+        <v>489</v>
       </c>
       <c r="G10">
-        <v>126</v>
+        <v>276</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="I10">
-        <v>192</v>
+        <v>445</v>
       </c>
       <c r="J10">
-        <v>269</v>
+        <v>502</v>
       </c>
       <c r="K10">
-        <v>193</v>
+        <v>411</v>
       </c>
       <c r="L10">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="M10">
-        <v>149</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41884,40 +41821,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>385</v>
+        <v>654</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>876</v>
       </c>
       <c r="D11">
-        <v>397</v>
+        <v>743</v>
       </c>
       <c r="E11">
-        <v>354</v>
+        <v>789</v>
       </c>
       <c r="F11">
-        <v>298</v>
+        <v>728</v>
       </c>
       <c r="G11">
-        <v>290</v>
+        <v>491</v>
       </c>
       <c r="H11">
-        <v>326</v>
+        <v>565</v>
       </c>
       <c r="I11">
-        <v>434</v>
+        <v>767</v>
       </c>
       <c r="J11">
-        <v>592</v>
+        <v>949</v>
       </c>
       <c r="K11">
-        <v>554</v>
+        <v>973</v>
       </c>
       <c r="L11">
-        <v>580</v>
+        <v>703</v>
       </c>
       <c r="M11">
-        <v>363</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -42413,40 +42350,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H2">
+        <v>48</v>
+      </c>
+      <c r="I2">
+        <v>41</v>
+      </c>
+      <c r="J2">
         <v>36</v>
-      </c>
-      <c r="I2">
-        <v>26</v>
-      </c>
-      <c r="J2">
-        <v>35</v>
       </c>
       <c r="K2">
         <v>35</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42454,40 +42391,40 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>43</v>
+      </c>
+      <c r="D3">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>28</v>
+      </c>
+      <c r="F3">
         <v>24</v>
       </c>
-      <c r="C3">
-        <v>26</v>
-      </c>
-      <c r="D3">
-        <v>16</v>
-      </c>
-      <c r="E3">
+      <c r="G3">
+        <v>33</v>
+      </c>
+      <c r="H3">
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>37</v>
+      </c>
+      <c r="J3">
+        <v>37</v>
+      </c>
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3">
         <v>31</v>
       </c>
-      <c r="F3">
-        <v>29</v>
-      </c>
-      <c r="G3">
-        <v>36</v>
-      </c>
-      <c r="H3">
-        <v>31</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>28</v>
-      </c>
-      <c r="K3">
-        <v>31</v>
-      </c>
-      <c r="L3">
-        <v>28</v>
-      </c>
       <c r="M3">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42495,31 +42432,37 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -42527,40 +42470,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C5">
+        <v>175</v>
+      </c>
+      <c r="D5">
+        <v>120</v>
+      </c>
+      <c r="E5">
+        <v>152</v>
+      </c>
+      <c r="F5">
+        <v>91</v>
+      </c>
+      <c r="G5">
         <v>44</v>
       </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-      <c r="E5">
-        <v>35</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
-      </c>
-      <c r="G5">
-        <v>30</v>
-      </c>
       <c r="H5">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="K5">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="L5">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42568,40 +42511,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>13</v>
+      </c>
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
+      <c r="M6">
         <v>7</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -42609,31 +42552,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>3</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -42641,40 +42584,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="D8">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H8">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="I8">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="J8">
-        <v>124</v>
+        <v>268</v>
       </c>
       <c r="K8">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="L8">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42682,40 +42625,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C9">
+        <v>101</v>
+      </c>
+      <c r="D9">
+        <v>84</v>
+      </c>
+      <c r="E9">
+        <v>49</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>42</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>62</v>
+      </c>
+      <c r="J9">
         <v>36</v>
       </c>
-      <c r="D9">
-        <v>26</v>
-      </c>
-      <c r="E9">
-        <v>21</v>
-      </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>21</v>
-      </c>
-      <c r="J9">
-        <v>17</v>
-      </c>
       <c r="K9">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -42723,40 +42666,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>641</v>
       </c>
       <c r="C10">
-        <v>250</v>
+        <v>540</v>
       </c>
       <c r="D10">
-        <v>270</v>
+        <v>482</v>
       </c>
       <c r="E10">
-        <v>297</v>
+        <v>485</v>
       </c>
       <c r="F10">
-        <v>226</v>
+        <v>443</v>
       </c>
       <c r="G10">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="H10">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="I10">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="J10">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="K10">
-        <v>275</v>
+        <v>479</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>486</v>
       </c>
       <c r="M10">
-        <v>181</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42764,40 +42707,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>359</v>
+        <v>1023</v>
       </c>
       <c r="C11">
-        <v>432</v>
+        <v>1021</v>
       </c>
       <c r="D11">
-        <v>427</v>
+        <v>860</v>
       </c>
       <c r="E11">
-        <v>450</v>
+        <v>846</v>
       </c>
       <c r="F11">
-        <v>388</v>
+        <v>718</v>
       </c>
       <c r="G11">
-        <v>284</v>
+        <v>519</v>
       </c>
       <c r="H11">
-        <v>324</v>
+        <v>501</v>
       </c>
       <c r="I11">
-        <v>346</v>
+        <v>727</v>
       </c>
       <c r="J11">
-        <v>418</v>
+        <v>845</v>
       </c>
       <c r="K11">
-        <v>490</v>
+        <v>936</v>
       </c>
       <c r="L11">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="M11">
-        <v>315</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -42871,40 +42814,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42912,60 +42855,81 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
         <v>33</v>
       </c>
-      <c r="F3">
+      <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
         <v>28</v>
-      </c>
-      <c r="G3">
-        <v>19</v>
-      </c>
-      <c r="H3">
-        <v>19</v>
-      </c>
-      <c r="I3">
-        <v>15</v>
-      </c>
-      <c r="J3">
-        <v>29</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -42973,40 +42937,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E5">
+        <v>46</v>
+      </c>
+      <c r="F5">
+        <v>31</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>33</v>
+      </c>
+      <c r="K5">
+        <v>51</v>
+      </c>
+      <c r="L5">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>23</v>
-      </c>
-      <c r="F5">
-        <v>23</v>
-      </c>
-      <c r="G5">
-        <v>56</v>
-      </c>
-      <c r="H5">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5">
-        <v>23</v>
-      </c>
-      <c r="L5">
-        <v>21</v>
-      </c>
-      <c r="M5">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43014,60 +42978,81 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
       <c r="D7">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43075,40 +43060,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H8">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="I8">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="J8">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="K8">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="L8">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="M8">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43116,40 +43101,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
         <v>19</v>
       </c>
-      <c r="C9">
-        <v>32</v>
-      </c>
-      <c r="D9">
-        <v>51</v>
-      </c>
-      <c r="E9">
-        <v>29</v>
-      </c>
-      <c r="F9">
-        <v>47</v>
-      </c>
       <c r="G9">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9">
         <v>29</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43157,40 +43142,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>632</v>
+        <v>180</v>
       </c>
       <c r="C10">
-        <v>762</v>
+        <v>215</v>
       </c>
       <c r="D10">
-        <v>938</v>
+        <v>184</v>
       </c>
       <c r="E10">
-        <v>859</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>913</v>
+        <v>137</v>
       </c>
       <c r="G10">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="H10">
-        <v>413</v>
+        <v>120</v>
       </c>
       <c r="I10">
-        <v>716</v>
+        <v>192</v>
       </c>
       <c r="J10">
-        <v>690</v>
+        <v>269</v>
       </c>
       <c r="K10">
-        <v>724</v>
+        <v>193</v>
       </c>
       <c r="L10">
-        <v>660</v>
+        <v>218</v>
       </c>
       <c r="M10">
-        <v>530</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43198,40 +43183,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>721</v>
+        <v>385</v>
       </c>
       <c r="C11">
-        <v>927</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>1129</v>
+        <v>397</v>
       </c>
       <c r="E11">
-        <v>1075</v>
+        <v>354</v>
       </c>
       <c r="F11">
-        <v>1141</v>
+        <v>298</v>
       </c>
       <c r="G11">
-        <v>616</v>
+        <v>290</v>
       </c>
       <c r="H11">
-        <v>689</v>
+        <v>326</v>
       </c>
       <c r="I11">
-        <v>1063</v>
+        <v>434</v>
       </c>
       <c r="J11">
-        <v>997</v>
+        <v>592</v>
       </c>
       <c r="K11">
-        <v>1009</v>
+        <v>554</v>
       </c>
       <c r="L11">
-        <v>902</v>
+        <v>580</v>
       </c>
       <c r="M11">
-        <v>693</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -43305,40 +43290,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="J2">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="K2">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43346,40 +43331,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="L3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -43387,40 +43372,31 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -43428,40 +43404,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K5">
+        <v>22</v>
+      </c>
+      <c r="L5">
         <v>18</v>
       </c>
-      <c r="L5">
-        <v>13</v>
-      </c>
       <c r="M5">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43472,78 +43448,69 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>7</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -43551,40 +43518,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>37</v>
+      </c>
+      <c r="G8">
+        <v>44</v>
+      </c>
+      <c r="H8">
+        <v>48</v>
+      </c>
+      <c r="I8">
+        <v>94</v>
+      </c>
+      <c r="J8">
+        <v>124</v>
+      </c>
+      <c r="K8">
+        <v>101</v>
+      </c>
+      <c r="L8">
+        <v>64</v>
+      </c>
+      <c r="M8">
         <v>52</v>
-      </c>
-      <c r="E8">
-        <v>48</v>
-      </c>
-      <c r="F8">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>57</v>
-      </c>
-      <c r="I8">
-        <v>134</v>
-      </c>
-      <c r="J8">
-        <v>136</v>
-      </c>
-      <c r="K8">
-        <v>97</v>
-      </c>
-      <c r="L8">
-        <v>80</v>
-      </c>
-      <c r="M8">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43592,40 +43559,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
         <v>21</v>
       </c>
-      <c r="I9">
-        <v>40</v>
-      </c>
       <c r="J9">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43633,40 +43600,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="D10">
+        <v>270</v>
+      </c>
+      <c r="E10">
+        <v>297</v>
+      </c>
+      <c r="F10">
+        <v>226</v>
+      </c>
+      <c r="G10">
+        <v>133</v>
+      </c>
+      <c r="H10">
+        <v>143</v>
+      </c>
+      <c r="I10">
         <v>149</v>
       </c>
-      <c r="E10">
-        <v>169</v>
-      </c>
-      <c r="F10">
-        <v>157</v>
-      </c>
-      <c r="G10">
-        <v>112</v>
-      </c>
-      <c r="H10">
-        <v>127</v>
-      </c>
-      <c r="I10">
-        <v>131</v>
-      </c>
       <c r="J10">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="K10">
-        <v>148</v>
+        <v>275</v>
       </c>
       <c r="L10">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>107</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43674,40 +43641,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C11">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="D11">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="E11">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G11">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="H11">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I11">
-        <v>466</v>
+        <v>346</v>
       </c>
       <c r="J11">
-        <v>528</v>
+        <v>418</v>
       </c>
       <c r="K11">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="L11">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="M11">
-        <v>291</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -43717,7 +43684,7 @@
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -43784,37 +43751,37 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>16</v>
       </c>
       <c r="I2">
+        <v>31</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>29</v>
+      </c>
+      <c r="L2">
         <v>19</v>
       </c>
-      <c r="J2">
-        <v>14</v>
-      </c>
-      <c r="K2">
+      <c r="M2">
         <v>11</v>
-      </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -43822,309 +43789,326 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G3">
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <v>19</v>
+      </c>
+      <c r="I3">
         <v>15</v>
       </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
       <c r="J3">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>39</v>
+      </c>
+      <c r="G6">
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <v>95</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="L8">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>47</v>
+      </c>
+      <c r="G9">
         <v>37</v>
       </c>
-      <c r="D9">
+      <c r="H9">
+        <v>46</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>29</v>
+      </c>
+      <c r="K9">
         <v>39</v>
       </c>
-      <c r="E9">
-        <v>67</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>33</v>
-      </c>
-      <c r="H9">
-        <v>80</v>
-      </c>
-      <c r="I9">
-        <v>94</v>
-      </c>
-      <c r="J9">
-        <v>70</v>
-      </c>
-      <c r="K9">
-        <v>102</v>
-      </c>
       <c r="L9">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="M9">
-        <v>51</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>632</v>
+      </c>
+      <c r="C10">
+        <v>762</v>
+      </c>
+      <c r="D10">
+        <v>938</v>
+      </c>
+      <c r="E10">
+        <v>859</v>
+      </c>
+      <c r="F10">
+        <v>913</v>
+      </c>
+      <c r="G10">
+        <v>398</v>
+      </c>
+      <c r="H10">
+        <v>413</v>
+      </c>
+      <c r="I10">
+        <v>716</v>
+      </c>
+      <c r="J10">
+        <v>690</v>
+      </c>
+      <c r="K10">
+        <v>724</v>
+      </c>
+      <c r="L10">
+        <v>660</v>
+      </c>
+      <c r="M10">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>106</v>
-      </c>
-      <c r="C10">
-        <v>79</v>
-      </c>
-      <c r="D10">
-        <v>73</v>
-      </c>
-      <c r="E10">
-        <v>117</v>
-      </c>
-      <c r="F10">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>94</v>
-      </c>
-      <c r="H10">
-        <v>141</v>
-      </c>
-      <c r="I10">
-        <v>182</v>
-      </c>
-      <c r="J10">
-        <v>155</v>
-      </c>
-      <c r="K10">
-        <v>170</v>
-      </c>
-      <c r="L10">
-        <v>141</v>
-      </c>
-      <c r="M10">
-        <v>102</v>
+      <c r="B11">
+        <v>721</v>
+      </c>
+      <c r="C11">
+        <v>927</v>
+      </c>
+      <c r="D11">
+        <v>1129</v>
+      </c>
+      <c r="E11">
+        <v>1075</v>
+      </c>
+      <c r="F11">
+        <v>1141</v>
+      </c>
+      <c r="G11">
+        <v>616</v>
+      </c>
+      <c r="H11">
+        <v>689</v>
+      </c>
+      <c r="I11">
+        <v>1063</v>
+      </c>
+      <c r="J11">
+        <v>997</v>
+      </c>
+      <c r="K11">
+        <v>1009</v>
+      </c>
+      <c r="L11">
+        <v>902</v>
+      </c>
+      <c r="M11">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -44198,69 +44182,81 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="C2">
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>47</v>
+      </c>
+      <c r="G2">
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>53</v>
+      </c>
       <c r="C3">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -44268,7 +44264,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -44276,31 +44305,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>38</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>13</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44308,45 +44346,81 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
       <c r="C7">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -44354,37 +44428,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>42</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44392,40 +44469,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>39</v>
+      </c>
+      <c r="K9">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>32</v>
+      </c>
+      <c r="M9">
         <v>10</v>
-      </c>
-      <c r="E9">
-        <v>12</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
-      <c r="M9">
-        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44433,40 +44510,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>209</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>344</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>445</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>307</v>
+        <v>169</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>157</v>
       </c>
       <c r="G10">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="H10">
-        <v>321</v>
+        <v>127</v>
       </c>
       <c r="I10">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="J10">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="K10">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="L10">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="M10">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44474,40 +44551,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="C11">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="D11">
-        <v>474</v>
+        <v>395</v>
       </c>
       <c r="E11">
-        <v>328</v>
+        <v>414</v>
       </c>
       <c r="F11">
-        <v>340</v>
+        <v>387</v>
       </c>
       <c r="G11">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="H11">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="I11">
-        <v>391</v>
+        <v>466</v>
       </c>
       <c r="J11">
-        <v>203</v>
+        <v>528</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>448</v>
       </c>
       <c r="L11">
-        <v>143</v>
+        <v>374</v>
       </c>
       <c r="M11">
-        <v>116</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -44517,7 +44594,7 @@
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -44581,40 +44658,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+      <c r="M2">
         <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -44622,70 +44699,115 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
       <c r="L4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -44694,188 +44816,192 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>2</v>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
       </c>
       <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>16</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>9</v>
+      </c>
+      <c r="M8">
         <v>6</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>9</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="I10">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="J10">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="K10">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="L10">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="M10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>123</v>
-      </c>
-      <c r="C11">
-        <v>97</v>
-      </c>
-      <c r="D11">
-        <v>89</v>
-      </c>
-      <c r="E11">
-        <v>44</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11">
-        <v>23</v>
-      </c>
-      <c r="H11">
-        <v>27</v>
-      </c>
-      <c r="I11">
-        <v>56</v>
-      </c>
-      <c r="J11">
-        <v>82</v>
-      </c>
-      <c r="K11">
-        <v>76</v>
-      </c>
-      <c r="L11">
-        <v>61</v>
-      </c>
-      <c r="M11">
-        <v>53</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -44949,97 +45075,76 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <v>4</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
         <v>6</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>3</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
+      <c r="J3">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
       <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -45048,40 +45153,31 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45089,19 +45185,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -45110,12 +45206,12 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -45123,7 +45219,10 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -45132,40 +45231,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="G8">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>16</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>40</v>
-      </c>
       <c r="K8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45173,40 +45269,40 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>15</v>
-      </c>
       <c r="K9">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45214,40 +45310,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C10">
-        <v>213</v>
+        <v>344</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>445</v>
       </c>
       <c r="E10">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="F10">
-        <v>229</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>158</v>
+        <v>321</v>
       </c>
       <c r="I10">
-        <v>226</v>
+        <v>367</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="K10">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="L10">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="M10">
-        <v>177</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45255,40 +45351,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>364</v>
       </c>
       <c r="D11">
-        <v>270</v>
+        <v>474</v>
       </c>
       <c r="E11">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="F11">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="G11">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>198</v>
+        <v>338</v>
       </c>
       <c r="I11">
-        <v>308</v>
+        <v>391</v>
       </c>
       <c r="J11">
-        <v>314</v>
+        <v>203</v>
       </c>
       <c r="K11">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="L11">
-        <v>309</v>
+        <v>143</v>
       </c>
       <c r="M11">
-        <v>208</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -45841,34 +45937,37 @@
         <v>1</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>8</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45876,47 +45975,44 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
       <c r="J3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -45925,94 +46021,61 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
         <v>3</v>
       </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
       <c r="K5">
-        <v>13</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="K7">
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -46021,40 +46084,31 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
         <v>12</v>
       </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
         <v>11</v>
       </c>
-      <c r="E8">
-        <v>23</v>
-      </c>
-      <c r="F8">
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>24</v>
-      </c>
-      <c r="J8">
-        <v>27</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46062,40 +46116,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46103,40 +46154,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="C10">
-        <v>260</v>
+        <v>87</v>
       </c>
       <c r="D10">
-        <v>256</v>
+        <v>69</v>
       </c>
       <c r="E10">
-        <v>262</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="H10">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="I10">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="J10">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="K10">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="L10">
-        <v>265</v>
+        <v>36</v>
       </c>
       <c r="M10">
-        <v>150</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46144,40 +46195,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="C11">
-        <v>323</v>
+        <v>97</v>
       </c>
       <c r="D11">
-        <v>311</v>
+        <v>89</v>
       </c>
       <c r="E11">
-        <v>342</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="G11">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="H11">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="I11">
-        <v>236</v>
+        <v>56</v>
       </c>
       <c r="J11">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="K11">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="L11">
-        <v>323</v>
+        <v>61</v>
       </c>
       <c r="M11">
-        <v>192</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -46251,40 +46302,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>11</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46292,63 +46343,54 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="I4">
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -46359,40 +46401,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>8</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46400,60 +46442,42 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46461,40 +46485,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>31</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
         <v>14</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>21</v>
-      </c>
-      <c r="I8">
-        <v>39</v>
-      </c>
-      <c r="J8">
-        <v>50</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46502,40 +46526,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>31</v>
+      </c>
+      <c r="E9">
         <v>17</v>
       </c>
-      <c r="D9">
-        <v>13</v>
-      </c>
-      <c r="E9">
-        <v>26</v>
-      </c>
       <c r="F9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
         <v>11</v>
       </c>
-      <c r="H9">
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
         <v>15</v>
       </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
       <c r="K9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -46543,40 +46567,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="I10">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="J10">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="K10">
-        <v>37</v>
+        <v>295</v>
       </c>
       <c r="L10">
-        <v>56</v>
+        <v>264</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46584,40 +46608,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="D11">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="E11">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="F11">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="G11">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="I11">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="J11">
-        <v>146</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>128</v>
+        <v>309</v>
       </c>
       <c r="M11">
-        <v>74</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -46691,40 +46715,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>41</v>
-      </c>
-      <c r="L2">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -46732,78 +46753,48 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
       <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -46811,40 +46802,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="L5">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -46852,72 +46843,54 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>3</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
       <c r="G7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
       <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -46925,40 +46898,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46966,40 +46939,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
         <v>17</v>
       </c>
-      <c r="G9">
-        <v>40</v>
-      </c>
-      <c r="H9">
-        <v>59</v>
-      </c>
       <c r="I9">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J9">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47007,40 +46980,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>369</v>
+        <v>197</v>
       </c>
       <c r="C10">
-        <v>394</v>
+        <v>260</v>
       </c>
       <c r="D10">
-        <v>372</v>
+        <v>256</v>
       </c>
       <c r="E10">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="F10">
-        <v>325</v>
+        <v>211</v>
       </c>
       <c r="G10">
-        <v>266</v>
+        <v>122</v>
       </c>
       <c r="H10">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="I10">
-        <v>372</v>
+        <v>175</v>
       </c>
       <c r="J10">
-        <v>319</v>
+        <v>199</v>
       </c>
       <c r="K10">
-        <v>369</v>
+        <v>256</v>
       </c>
       <c r="L10">
-        <v>427</v>
+        <v>265</v>
       </c>
       <c r="M10">
-        <v>330</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47048,40 +47021,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>713</v>
+        <v>255</v>
       </c>
       <c r="C11">
-        <v>714</v>
+        <v>323</v>
       </c>
       <c r="D11">
-        <v>697</v>
+        <v>311</v>
       </c>
       <c r="E11">
-        <v>616</v>
+        <v>342</v>
       </c>
       <c r="F11">
-        <v>568</v>
+        <v>261</v>
       </c>
       <c r="G11">
-        <v>492</v>
+        <v>197</v>
       </c>
       <c r="H11">
-        <v>474</v>
+        <v>233</v>
       </c>
       <c r="I11">
-        <v>722</v>
+        <v>236</v>
       </c>
       <c r="J11">
-        <v>739</v>
+        <v>268</v>
       </c>
       <c r="K11">
-        <v>720</v>
+        <v>337</v>
       </c>
       <c r="L11">
-        <v>728</v>
+        <v>323</v>
       </c>
       <c r="M11">
-        <v>532</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -47155,40 +47128,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I2">
+        <v>11</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>21</v>
+      </c>
+      <c r="L2">
+        <v>9</v>
+      </c>
+      <c r="M2">
         <v>8</v>
-      </c>
-      <c r="J2">
-        <v>17</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47196,40 +47169,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47243,9 +47216,18 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -47254,37 +47236,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <v>30</v>
       </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
       <c r="G5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J5">
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
         <v>8</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -47295,42 +47277,60 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47338,40 +47338,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L8">
         <v>26</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47379,40 +47379,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47420,40 +47420,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="G10">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="K10">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="M10">
-        <v>69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47461,40 +47461,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="D11">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="E11">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G11">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H11">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I11">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J11">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="K11">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="L11">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -47568,40 +47568,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -47609,40 +47609,40 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>44</v>
+      </c>
+      <c r="G3">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>31</v>
+      </c>
+      <c r="I3">
+        <v>36</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>31</v>
+      </c>
+      <c r="L3">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>18</v>
-      </c>
-      <c r="C3">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>33</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>36</v>
-      </c>
-      <c r="K3">
-        <v>41</v>
-      </c>
-      <c r="L3">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47650,37 +47650,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -47691,40 +47688,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E5">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="K5">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L5">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -47732,40 +47729,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -47773,37 +47770,31 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>3</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
       </c>
       <c r="K7">
         <v>3</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -47811,40 +47802,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>96</v>
+      </c>
+      <c r="C8">
         <v>59</v>
       </c>
-      <c r="C8">
-        <v>104</v>
-      </c>
       <c r="D8">
+        <v>59</v>
+      </c>
+      <c r="E8">
+        <v>63</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>110</v>
+      </c>
+      <c r="J8">
+        <v>171</v>
+      </c>
+      <c r="K8">
+        <v>143</v>
+      </c>
+      <c r="L8">
         <v>122</v>
       </c>
-      <c r="E8">
-        <v>89</v>
-      </c>
-      <c r="F8">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>70</v>
-      </c>
-      <c r="I8">
-        <v>140</v>
-      </c>
-      <c r="J8">
-        <v>242</v>
-      </c>
-      <c r="K8">
-        <v>339</v>
-      </c>
-      <c r="L8">
-        <v>141</v>
-      </c>
       <c r="M8">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47852,40 +47843,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I9">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J9">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K9">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -47893,40 +47884,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="C10">
-        <v>492</v>
+        <v>394</v>
       </c>
       <c r="D10">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E10">
-        <v>489</v>
+        <v>305</v>
       </c>
       <c r="F10">
-        <v>489</v>
+        <v>325</v>
       </c>
       <c r="G10">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="H10">
+        <v>224</v>
+      </c>
+      <c r="I10">
+        <v>372</v>
+      </c>
+      <c r="J10">
+        <v>319</v>
+      </c>
+      <c r="K10">
+        <v>369</v>
+      </c>
+      <c r="L10">
+        <v>427</v>
+      </c>
+      <c r="M10">
         <v>330</v>
-      </c>
-      <c r="I10">
-        <v>445</v>
-      </c>
-      <c r="J10">
-        <v>502</v>
-      </c>
-      <c r="K10">
-        <v>411</v>
-      </c>
-      <c r="L10">
-        <v>386</v>
-      </c>
-      <c r="M10">
-        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47934,40 +47925,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>654</v>
+        <v>713</v>
       </c>
       <c r="C11">
-        <v>876</v>
+        <v>714</v>
       </c>
       <c r="D11">
-        <v>743</v>
+        <v>697</v>
       </c>
       <c r="E11">
-        <v>789</v>
+        <v>616</v>
       </c>
       <c r="F11">
+        <v>568</v>
+      </c>
+      <c r="G11">
+        <v>492</v>
+      </c>
+      <c r="H11">
+        <v>474</v>
+      </c>
+      <c r="I11">
+        <v>722</v>
+      </c>
+      <c r="J11">
+        <v>739</v>
+      </c>
+      <c r="K11">
+        <v>720</v>
+      </c>
+      <c r="L11">
         <v>728</v>
       </c>
-      <c r="G11">
-        <v>491</v>
-      </c>
-      <c r="H11">
-        <v>565</v>
-      </c>
-      <c r="I11">
-        <v>767</v>
-      </c>
-      <c r="J11">
-        <v>949</v>
-      </c>
-      <c r="K11">
-        <v>973</v>
-      </c>
-      <c r="L11">
-        <v>703</v>
-      </c>
       <c r="M11">
-        <v>461</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -48041,37 +48032,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48079,56 +48073,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48137,34 +48134,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
       <c r="H5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
         <v>13</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48177,48 +48174,72 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
       <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48227,40 +48248,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="K8">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48268,40 +48289,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>29</v>
+      </c>
+      <c r="F9">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
       <c r="G9">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48309,40 +48330,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="C10">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="D10">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="J10">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="L10">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="M10">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48350,40 +48371,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="C11">
+        <v>227</v>
+      </c>
+      <c r="D11">
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>248</v>
+      </c>
+      <c r="F11">
+        <v>249</v>
+      </c>
+      <c r="G11">
+        <v>169</v>
+      </c>
+      <c r="H11">
+        <v>193</v>
+      </c>
+      <c r="I11">
+        <v>251</v>
+      </c>
+      <c r="J11">
         <v>291</v>
       </c>
-      <c r="D11">
-        <v>212</v>
-      </c>
-      <c r="E11">
-        <v>216</v>
-      </c>
-      <c r="F11">
-        <v>247</v>
-      </c>
-      <c r="G11">
-        <v>155</v>
-      </c>
-      <c r="H11">
-        <v>179</v>
-      </c>
-      <c r="I11">
-        <v>238</v>
-      </c>
-      <c r="J11">
-        <v>318</v>
-      </c>
       <c r="K11">
-        <v>347</v>
+        <v>251</v>
       </c>
       <c r="L11">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="M11">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -48457,40 +48478,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>19</v>
-      </c>
       <c r="I2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48498,59 +48516,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="F4">
         <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -48559,34 +48574,34 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>26</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>13</v>
       </c>
       <c r="L5">
         <v>19</v>
@@ -48599,72 +48614,48 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -48673,40 +48664,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8">
+        <v>42</v>
+      </c>
+      <c r="L8">
         <v>18</v>
       </c>
-      <c r="E8">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>88</v>
-      </c>
-      <c r="K8">
-        <v>46</v>
-      </c>
-      <c r="L8">
-        <v>50</v>
-      </c>
       <c r="M8">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48714,40 +48705,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="H9">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>42</v>
-      </c>
-      <c r="K9">
-        <v>38</v>
-      </c>
       <c r="L9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -48755,40 +48746,40 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <v>192</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>142</v>
+      </c>
+      <c r="E10">
+        <v>135</v>
+      </c>
+      <c r="F10">
+        <v>184</v>
+      </c>
+      <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
         <v>112</v>
       </c>
-      <c r="C10">
-        <v>108</v>
-      </c>
-      <c r="D10">
-        <v>119</v>
-      </c>
-      <c r="E10">
-        <v>133</v>
-      </c>
-      <c r="F10">
-        <v>146</v>
-      </c>
-      <c r="G10">
-        <v>68</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
       <c r="I10">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="J10">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="K10">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="L10">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48796,40 +48787,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="C11">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="E11">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F11">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H11">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="I11">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J11">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="K11">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="L11">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M11">
-        <v>209</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -48903,37 +48894,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
         <v>5</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48941,37 +48935,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
         <v>7</v>
       </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
       <c r="L3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -48981,16 +48975,16 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -49002,37 +48996,37 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F5">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
         <v>6</v>
       </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
+      <c r="L5">
+        <v>15</v>
+      </c>
+      <c r="M5">
         <v>8</v>
-      </c>
-      <c r="I5">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>12</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49040,38 +49034,41 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -49080,40 +49077,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
         <v>11</v>
-      </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>8</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49121,34 +49118,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
         <v>5</v>
       </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
+      <c r="K9">
         <v>4</v>
       </c>
-      <c r="K9">
-        <v>3</v>
+      <c r="L9">
+        <v>6</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -49159,40 +49159,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="D10">
+        <v>150</v>
+      </c>
+      <c r="E10">
+        <v>134</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
         <v>62</v>
       </c>
-      <c r="E10">
-        <v>45</v>
-      </c>
-      <c r="F10">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>52</v>
-      </c>
       <c r="H10">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>22</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49200,40 +49200,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="C11">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="D11">
-        <v>87</v>
+        <v>204</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="F11">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="H11">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="I11">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="J11">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="K11">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="L11">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="M11">
-        <v>31</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -49307,40 +49307,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>9</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
         <v>3</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49348,44 +49345,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -49394,40 +49403,40 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>27</v>
-      </c>
-      <c r="E5">
-        <v>32</v>
-      </c>
       <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>32</v>
-      </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49435,13 +49444,16 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+      <c r="F6">
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -49452,10 +49464,10 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -49463,7 +49475,7 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -49472,40 +49484,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
-      </c>
-      <c r="J8">
-        <v>37</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
       <c r="L8">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49513,40 +49525,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49554,40 +49563,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="J10">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="K10">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="M10">
-        <v>91</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49595,40 +49604,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="F11">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="H11">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="J11">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="K11">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="L11">
-        <v>239</v>
+        <v>87</v>
       </c>
       <c r="M11">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -49702,40 +49711,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49743,54 +49752,45 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="E3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
         <v>3</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -49798,40 +49798,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49839,38 +49839,35 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="D6">
         <v>3</v>
       </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
-        <v>2</v>
+      <c r="M6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -49879,40 +49876,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
         <v>15</v>
       </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
       <c r="D8">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>14</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J8">
         <v>37</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49920,36 +49917,39 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>7</v>
-      </c>
-      <c r="L9">
+      <c r="M9">
         <v>3</v>
       </c>
     </row>
@@ -49958,40 +49958,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C10">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="D10">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G10">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H10">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I10">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="J10">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="K10">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="L10">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="M10">
-        <v>56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49999,40 +49999,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="C11">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="D11">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="E11">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="F11">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="G11">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="H11">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="I11">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="J11">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="K11">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="L11">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="M11">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -101,11 +101,11 @@
     <sheet name="Wrigleyville" sheetId="92" r:id="rId92"/>
     <sheet name="Burnside" sheetId="93" r:id="rId93"/>
     <sheet name="Andersonville" sheetId="94" r:id="rId94"/>
-    <sheet name="Jackson Park" sheetId="95" r:id="rId95"/>
-    <sheet name="Mount Greenwood" sheetId="96" r:id="rId96"/>
-    <sheet name="Printers Row" sheetId="97" r:id="rId97"/>
-    <sheet name="Sauganash,Forest Glen" sheetId="98" r:id="rId98"/>
-    <sheet name="Grant Park" sheetId="99" r:id="rId99"/>
+    <sheet name="Grant Park" sheetId="95" r:id="rId95"/>
+    <sheet name="Jackson Park" sheetId="96" r:id="rId96"/>
+    <sheet name="Mount Greenwood" sheetId="97" r:id="rId97"/>
+    <sheet name="Printers Row" sheetId="98" r:id="rId98"/>
+    <sheet name="Sauganash,Forest Glen" sheetId="99" r:id="rId99"/>
     <sheet name="Museum Campus" sheetId="100" r:id="rId100"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4833</v>
+        <v>4847</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7126</v>
       </c>
       <c r="M3">
-        <v>5423</v>
+        <v>5443</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1030,13 +1030,13 @@
         <v>7492</v>
       </c>
       <c r="K5">
-        <v>7662</v>
+        <v>7661</v>
       </c>
       <c r="L5">
-        <v>6212</v>
+        <v>6213</v>
       </c>
       <c r="M5">
-        <v>4224</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1956</v>
       </c>
       <c r="M6">
-        <v>1468</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>435</v>
       </c>
       <c r="M7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17258</v>
       </c>
       <c r="M8">
-        <v>13688</v>
+        <v>13740</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1197,10 +1197,10 @@
         <v>9120</v>
       </c>
       <c r="L9">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="M9">
-        <v>3559</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1235,13 +1235,13 @@
         <v>57529</v>
       </c>
       <c r="K10">
-        <v>61334</v>
+        <v>61335</v>
       </c>
       <c r="L10">
         <v>58729</v>
       </c>
       <c r="M10">
-        <v>43818</v>
+        <v>43989</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1279,10 +1279,10 @@
         <v>118958</v>
       </c>
       <c r="L11">
-        <v>104493</v>
+        <v>104495</v>
       </c>
       <c r="M11">
-        <v>77623</v>
+        <v>77928</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1512,7 +1512,7 @@
         <v>304</v>
       </c>
       <c r="M5">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1050</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2665</v>
+        <v>2678</v>
       </c>
     </row>
   </sheetData>
@@ -2356,7 +2356,7 @@
         <v>90</v>
       </c>
       <c r="M5">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1200</v>
       </c>
       <c r="M10">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1413</v>
+        <v>1421</v>
       </c>
     </row>
   </sheetData>
@@ -2832,7 +2832,7 @@
         <v>62</v>
       </c>
       <c r="M5">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2952,7 +2952,7 @@
         <v>121</v>
       </c>
       <c r="M8">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>889</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -3463,7 +3463,7 @@
         <v>34</v>
       </c>
       <c r="M9">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>782</v>
       </c>
       <c r="M11">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -3652,7 +3652,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3898,7 +3898,7 @@
         <v>138</v>
       </c>
       <c r="M8">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4245,7 +4245,7 @@
         <v>223</v>
       </c>
       <c r="K5">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L5">
         <v>216</v>
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1375</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4491,13 +4491,13 @@
         <v>5063</v>
       </c>
       <c r="K11">
-        <v>4975</v>
+        <v>4974</v>
       </c>
       <c r="L11">
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3291</v>
+        <v>3303</v>
       </c>
     </row>
   </sheetData>
@@ -4604,7 +4604,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4727,7 +4727,7 @@
         <v>194</v>
       </c>
       <c r="M5">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4809,7 +4809,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1718</v>
+        <v>1724</v>
       </c>
     </row>
   </sheetData>
@@ -5367,7 +5367,7 @@
         <v>79</v>
       </c>
       <c r="M9">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
@@ -5679,7 +5679,7 @@
         <v>76</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1139</v>
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -6269,7 +6269,7 @@
         <v>208</v>
       </c>
       <c r="M8">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1885</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2387</v>
+        <v>2393</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6622,7 +6622,7 @@
         <v>266</v>
       </c>
       <c r="M5">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>782</v>
       </c>
       <c r="M6">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1718</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6739,13 +6739,13 @@
         <v>5063</v>
       </c>
       <c r="K8">
-        <v>4975</v>
+        <v>4974</v>
       </c>
       <c r="L8">
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3291</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>889</v>
+        <v>899</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1777</v>
       </c>
       <c r="M11">
-        <v>1426</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6909,7 +6909,7 @@
         <v>408</v>
       </c>
       <c r="M12">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1584</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1694</v>
       </c>
       <c r="M20">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7319,7 +7319,7 @@
         <v>383</v>
       </c>
       <c r="M22">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>578</v>
       </c>
       <c r="M25">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7483,7 +7483,7 @@
         <v>234</v>
       </c>
       <c r="M26">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3353</v>
       </c>
       <c r="M29">
-        <v>2484</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7647,7 +7647,7 @@
         <v>274</v>
       </c>
       <c r="M30">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7729,7 +7729,7 @@
         <v>180</v>
       </c>
       <c r="M32">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>1968</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1139</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1764</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -7975,7 +7975,7 @@
         <v>133</v>
       </c>
       <c r="M38">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -8016,7 +8016,7 @@
         <v>180</v>
       </c>
       <c r="M39">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -8098,7 +8098,7 @@
         <v>360</v>
       </c>
       <c r="M41">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2489</v>
       </c>
       <c r="M42">
-        <v>2377</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8218,10 +8218,10 @@
         <v>1295</v>
       </c>
       <c r="L44">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M44">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2067</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1385</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1413</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2768</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8795,7 +8795,7 @@
         <v>143</v>
       </c>
       <c r="M58">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8836,7 +8836,7 @@
         <v>297</v>
       </c>
       <c r="M59">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8877,7 +8877,7 @@
         <v>737</v>
       </c>
       <c r="M60">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8994,13 +8994,13 @@
         <v>1256</v>
       </c>
       <c r="K63">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="L63">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="M63">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1914</v>
       </c>
       <c r="M67">
-        <v>1493</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9205,7 +9205,7 @@
         <v>500</v>
       </c>
       <c r="M68">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>346</v>
       </c>
       <c r="M71">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>958</v>
+        <v>964</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9492,7 +9492,7 @@
         <v>426</v>
       </c>
       <c r="M75">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2387</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9574,7 +9574,7 @@
         <v>374</v>
       </c>
       <c r="M77">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9779,7 +9779,7 @@
         <v>231</v>
       </c>
       <c r="M82">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2665</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2096</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>922</v>
+        <v>930</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10555,10 +10555,10 @@
         <v>118958</v>
       </c>
       <c r="L101">
-        <v>104493</v>
+        <v>104495</v>
       </c>
       <c r="M101">
-        <v>77623</v>
+        <v>77928</v>
       </c>
     </row>
   </sheetData>
@@ -10887,7 +10887,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10995,7 +10995,7 @@
         <v>163</v>
       </c>
       <c r="M8">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1385</v>
+        <v>1388</v>
       </c>
     </row>
   </sheetData>
@@ -11529,7 +11529,7 @@
         <v>169</v>
       </c>
       <c r="M10">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11570,7 +11570,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
   </sheetData>
@@ -12381,7 +12381,7 @@
         <v>145</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12422,7 +12422,7 @@
         <v>180</v>
       </c>
       <c r="M9">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -12754,7 +12754,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13107,7 +13107,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13271,7 +13271,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1164</v>
       </c>
       <c r="M10">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2489</v>
       </c>
       <c r="M11">
-        <v>2377</v>
+        <v>2386</v>
       </c>
     </row>
   </sheetData>
@@ -13501,7 +13501,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13583,7 +13583,7 @@
         <v>95</v>
       </c>
       <c r="M5">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13706,7 +13706,7 @@
         <v>317</v>
       </c>
       <c r="M8">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1914</v>
       </c>
       <c r="M11">
-        <v>1493</v>
+        <v>1501</v>
       </c>
     </row>
   </sheetData>
@@ -14059,7 +14059,7 @@
         <v>25</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14252,7 +14252,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14293,7 +14293,7 @@
         <v>360</v>
       </c>
       <c r="M11">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -14441,7 +14441,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14724,7 +14724,7 @@
         <v>180</v>
       </c>
       <c r="M11">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -15074,7 +15074,7 @@
         <v>357</v>
       </c>
       <c r="M8">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2122</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2768</v>
+        <v>2772</v>
       </c>
     </row>
   </sheetData>
@@ -15614,7 +15614,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2096</v>
+        <v>2099</v>
       </c>
     </row>
   </sheetData>
@@ -16457,7 +16457,7 @@
         <v>148</v>
       </c>
       <c r="M8">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16536,10 +16536,10 @@
         <v>712</v>
       </c>
       <c r="L10">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M10">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16577,10 +16577,10 @@
         <v>1295</v>
       </c>
       <c r="L11">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M11">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -16851,7 +16851,7 @@
         <v>34</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16933,7 +16933,7 @@
         <v>222</v>
       </c>
       <c r="M8">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -17491,7 +17491,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -17680,7 +17680,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17747,7 +17747,7 @@
         <v>66</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>922</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -18654,7 +18654,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18777,7 +18777,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18818,7 +18818,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1694</v>
       </c>
       <c r="M11">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
   </sheetData>
@@ -19048,7 +19048,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19253,7 +19253,7 @@
         <v>417</v>
       </c>
       <c r="M8">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19294,7 +19294,7 @@
         <v>209</v>
       </c>
       <c r="M9">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1764</v>
+        <v>1771</v>
       </c>
     </row>
   </sheetData>
@@ -19959,7 +19959,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20205,7 +20205,7 @@
         <v>284</v>
       </c>
       <c r="M8">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -21133,7 +21133,7 @@
         <v>119</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21215,7 +21215,7 @@
         <v>161</v>
       </c>
       <c r="M10">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21256,7 +21256,7 @@
         <v>346</v>
       </c>
       <c r="M11">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -21486,7 +21486,7 @@
         <v>101</v>
       </c>
       <c r="M5">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21691,7 +21691,7 @@
         <v>603</v>
       </c>
       <c r="M10">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>
@@ -22073,7 +22073,7 @@
         <v>56</v>
       </c>
       <c r="M8">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -22467,7 +22467,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22549,7 +22549,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22631,7 +22631,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -23059,7 +23059,7 @@
         <v>524</v>
       </c>
       <c r="M10">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -23207,7 +23207,7 @@
         <v>33</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1035</v>
       </c>
       <c r="M10">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
   </sheetData>
@@ -23940,7 +23940,7 @@
         <v>161</v>
       </c>
       <c r="M9">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
   </sheetData>
@@ -24677,7 +24677,7 @@
         <v>15</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24870,7 +24870,7 @@
         <v>301</v>
       </c>
       <c r="M10">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
   </sheetData>
@@ -25520,7 +25520,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25643,7 +25643,7 @@
         <v>66</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3353</v>
       </c>
       <c r="M11">
-        <v>2484</v>
+        <v>2493</v>
       </c>
     </row>
   </sheetData>
@@ -25955,7 +25955,7 @@
         <v>23</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26116,7 +26116,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26180,7 +26180,7 @@
         <v>90</v>
       </c>
       <c r="M8">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26262,7 +26262,7 @@
         <v>189</v>
       </c>
       <c r="M10">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26303,7 +26303,7 @@
         <v>383</v>
       </c>
       <c r="M11">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -26565,7 +26565,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26641,7 +26641,7 @@
         <v>225</v>
       </c>
       <c r="M8">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -27172,7 +27172,7 @@
         <v>338</v>
       </c>
       <c r="M10">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -27484,7 +27484,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1191</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
   </sheetData>
@@ -27793,7 +27793,7 @@
         <v>65</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28121,7 +28121,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -28392,7 +28392,7 @@
         <v>190</v>
       </c>
       <c r="M5">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1584</v>
+        <v>1589</v>
       </c>
     </row>
   </sheetData>
@@ -28745,7 +28745,7 @@
         <v>69</v>
       </c>
       <c r="M2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28868,7 +28868,7 @@
         <v>73</v>
       </c>
       <c r="M5">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29032,7 +29032,7 @@
         <v>37</v>
       </c>
       <c r="M9">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29073,7 +29073,7 @@
         <v>423</v>
       </c>
       <c r="M10">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -29262,7 +29262,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29508,7 +29508,7 @@
         <v>106</v>
       </c>
       <c r="M9">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
@@ -29697,7 +29697,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30057,7 +30057,7 @@
         <v>274</v>
       </c>
       <c r="M11">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30205,7 +30205,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30448,7 +30448,7 @@
         <v>90</v>
       </c>
       <c r="M9">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -30489,7 +30489,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30530,7 +30530,7 @@
         <v>1777</v>
       </c>
       <c r="M11">
-        <v>1426</v>
+        <v>1433</v>
       </c>
     </row>
   </sheetData>
@@ -31173,7 +31173,7 @@
         <v>112</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31296,7 +31296,7 @@
         <v>324</v>
       </c>
       <c r="M8">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31378,7 +31378,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31419,7 +31419,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>
@@ -32227,7 +32227,7 @@
         <v>105</v>
       </c>
       <c r="M8">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32268,7 +32268,7 @@
         <v>38</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -32350,7 +32350,7 @@
         <v>737</v>
       </c>
       <c r="M11">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -32498,7 +32498,7 @@
         <v>51</v>
       </c>
       <c r="M3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -32826,7 +32826,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -33261,7 +33261,7 @@
         <v>478</v>
       </c>
       <c r="M10">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33302,7 +33302,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -33725,7 +33725,7 @@
         <v>553</v>
       </c>
       <c r="M10">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33766,7 +33766,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -34310,7 +34310,7 @@
         <v>83</v>
       </c>
       <c r="M2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -34635,7 +34635,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34676,7 +34676,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
   </sheetData>
@@ -34824,7 +34824,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35152,7 +35152,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -35382,7 +35382,7 @@
         <v>69</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -35502,7 +35502,7 @@
         <v>206</v>
       </c>
       <c r="M8">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35584,7 +35584,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35625,7 +35625,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>958</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -35855,7 +35855,7 @@
         <v>104</v>
       </c>
       <c r="M5">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -36060,7 +36060,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36101,7 +36101,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -36442,7 +36442,7 @@
         <v>125</v>
       </c>
       <c r="M8">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36524,7 +36524,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36565,7 +36565,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -37362,7 +37362,7 @@
         <v>152</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37403,7 +37403,7 @@
         <v>231</v>
       </c>
       <c r="M11">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -37796,7 +37796,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37837,7 +37837,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -38209,7 +38209,7 @@
         <v>164</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38250,7 +38250,7 @@
         <v>234</v>
       </c>
       <c r="M11">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -38632,7 +38632,7 @@
         <v>23</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -38714,7 +38714,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -38821,7 +38821,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -39149,7 +39149,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39190,7 +39190,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -39338,7 +39338,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -39516,7 +39516,7 @@
         <v>62</v>
       </c>
       <c r="M8">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39639,7 +39639,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -40020,7 +40020,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40061,7 +40061,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -40378,7 +40378,7 @@
         <v>76</v>
       </c>
       <c r="M8">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -40501,7 +40501,7 @@
         <v>408</v>
       </c>
       <c r="M11">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -40725,7 +40725,7 @@
         <v>206</v>
       </c>
       <c r="M5">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -40836,7 +40836,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -40918,7 +40918,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1600</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40959,7 +40959,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2067</v>
+        <v>2078</v>
       </c>
     </row>
   </sheetData>
@@ -41107,7 +41107,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41394,7 +41394,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41435,7 +41435,7 @@
         <v>578</v>
       </c>
       <c r="M11">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -41685,7 +41685,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -41828,7 +41828,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41869,7 +41869,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -42686,7 +42686,7 @@
         <v>80</v>
       </c>
       <c r="M8">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42809,7 +42809,7 @@
         <v>374</v>
       </c>
       <c r="M11">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -43030,7 +43030,7 @@
         <v>18</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43144,7 +43144,7 @@
         <v>64</v>
       </c>
       <c r="M8">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -43267,7 +43267,7 @@
         <v>426</v>
       </c>
       <c r="M11">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -43476,7 +43476,7 @@
         <v>19</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -43713,7 +43713,7 @@
         <v>266</v>
       </c>
       <c r="M11">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -44476,7 +44476,7 @@
         <v>140</v>
       </c>
       <c r="M8">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44558,7 +44558,7 @@
         <v>385</v>
       </c>
       <c r="M10">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44599,7 +44599,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -45633,7 +45633,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45838,7 +45838,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45879,7 +45879,7 @@
         <v>271</v>
       </c>
       <c r="M9">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45920,7 +45920,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45961,7 +45961,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>1968</v>
+        <v>1974</v>
       </c>
     </row>
   </sheetData>
@@ -46221,7 +46221,7 @@
         <v>3</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46344,7 +46344,7 @@
         <v>143</v>
       </c>
       <c r="M11">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -48009,6 +48009,404 @@
 
 <file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>16</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>12</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>104</v>
+      </c>
+      <c r="C10">
+        <v>117</v>
+      </c>
+      <c r="D10">
+        <v>119</v>
+      </c>
+      <c r="E10">
+        <v>123</v>
+      </c>
+      <c r="F10">
+        <v>118</v>
+      </c>
+      <c r="G10">
+        <v>45</v>
+      </c>
+      <c r="H10">
+        <v>77</v>
+      </c>
+      <c r="I10">
+        <v>155</v>
+      </c>
+      <c r="J10">
+        <v>229</v>
+      </c>
+      <c r="K10">
+        <v>120</v>
+      </c>
+      <c r="L10">
+        <v>92</v>
+      </c>
+      <c r="M10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>115</v>
+      </c>
+      <c r="C11">
+        <v>146</v>
+      </c>
+      <c r="D11">
+        <v>154</v>
+      </c>
+      <c r="E11">
+        <v>141</v>
+      </c>
+      <c r="F11">
+        <v>138</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11">
+        <v>104</v>
+      </c>
+      <c r="I11">
+        <v>192</v>
+      </c>
+      <c r="J11">
+        <v>261</v>
+      </c>
+      <c r="K11">
+        <v>151</v>
+      </c>
+      <c r="L11">
+        <v>133</v>
+      </c>
+      <c r="M11">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -48417,419 +48815,6 @@
       </c>
       <c r="M10">
         <v>112</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>17</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>16</v>
-      </c>
-      <c r="C5">
-        <v>30</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>15</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-      <c r="K9">
-        <v>4</v>
-      </c>
-      <c r="L9">
-        <v>6</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>151</v>
-      </c>
-      <c r="C10">
-        <v>153</v>
-      </c>
-      <c r="D10">
-        <v>150</v>
-      </c>
-      <c r="E10">
-        <v>134</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>62</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>101</v>
-      </c>
-      <c r="J10">
-        <v>98</v>
-      </c>
-      <c r="K10">
-        <v>112</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>202</v>
-      </c>
-      <c r="C11">
-        <v>210</v>
-      </c>
-      <c r="D11">
-        <v>204</v>
-      </c>
-      <c r="E11">
-        <v>186</v>
-      </c>
-      <c r="F11">
-        <v>144</v>
-      </c>
-      <c r="G11">
-        <v>112</v>
-      </c>
-      <c r="H11">
-        <v>125</v>
-      </c>
-      <c r="I11">
-        <v>160</v>
-      </c>
-      <c r="J11">
-        <v>167</v>
-      </c>
-      <c r="K11">
-        <v>167</v>
-      </c>
-      <c r="L11">
-        <v>161</v>
-      </c>
-      <c r="M11">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -48903,40 +48888,40 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J2">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
       <c r="M2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -48947,53 +48932,53 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
         <v>6</v>
       </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -49002,40 +48987,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="J5">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
-      </c>
       <c r="K5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5">
+        <v>15</v>
+      </c>
+      <c r="M5">
         <v>8</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49043,34 +49028,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="E6">
         <v>3</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>4</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -49086,40 +49071,40 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
       <c r="D8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49127,40 +49112,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
         <v>11</v>
       </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
       <c r="J9">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49168,40 +49153,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="C10">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="F10">
-        <v>229</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="H10">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="K10">
-        <v>295</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>192</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49209,40 +49194,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="D11">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="E11">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="F11">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="G11">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="H11">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="I11">
-        <v>308</v>
+        <v>160</v>
       </c>
       <c r="J11">
-        <v>314</v>
+        <v>167</v>
       </c>
       <c r="K11">
-        <v>360</v>
+        <v>167</v>
       </c>
       <c r="L11">
-        <v>308</v>
+        <v>161</v>
       </c>
       <c r="M11">
-        <v>226</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -49316,40 +49301,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>11</v>
+      </c>
+      <c r="J2">
         <v>6</v>
       </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>14</v>
-      </c>
-      <c r="H2">
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
         <v>5</v>
       </c>
-      <c r="I2">
-        <v>12</v>
-      </c>
-      <c r="J2">
-        <v>10</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>7</v>
-      </c>
       <c r="M2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49357,54 +49342,57 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
         <v>6</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>4</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -49412,40 +49400,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49453,38 +49441,41 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -49493,40 +49484,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L8">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M8">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49534,37 +49525,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
         <v>7</v>
       </c>
-      <c r="L9">
-        <v>3</v>
+      <c r="M9">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49572,40 +49566,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="C10">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="D10">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="G10">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="I10">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="J10">
-        <v>151</v>
+        <v>229</v>
       </c>
       <c r="K10">
-        <v>146</v>
+        <v>295</v>
       </c>
       <c r="L10">
-        <v>117</v>
+        <v>263</v>
       </c>
       <c r="M10">
-        <v>60</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49613,40 +49607,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="C11">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="D11">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="E11">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F11">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="G11">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="I11">
-        <v>222</v>
+        <v>308</v>
       </c>
       <c r="J11">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>243</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>187</v>
+        <v>308</v>
       </c>
       <c r="M11">
-        <v>105</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -49719,70 +49713,79 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L2">
+        <v>7</v>
+      </c>
+      <c r="M2">
         <v>5</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -49792,16 +49795,13 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>2</v>
       </c>
     </row>
@@ -49810,34 +49810,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>45</v>
+      </c>
+      <c r="E5">
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49847,39 +49853,36 @@
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M7">
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -49888,40 +49891,40 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -49929,40 +49932,37 @@
         <v>8</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
         <v>4</v>
       </c>
-      <c r="C9">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>9</v>
-      </c>
       <c r="F9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="H9">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>8</v>
       </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
       <c r="K9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>7</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49970,40 +49970,40 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C10">
+        <v>146</v>
+      </c>
+      <c r="D10">
+        <v>152</v>
+      </c>
+      <c r="E10">
+        <v>152</v>
+      </c>
+      <c r="F10">
         <v>117</v>
       </c>
-      <c r="D10">
-        <v>119</v>
-      </c>
-      <c r="E10">
-        <v>123</v>
-      </c>
-      <c r="F10">
-        <v>118</v>
-      </c>
       <c r="G10">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="H10">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="J10">
-        <v>229</v>
+        <v>151</v>
       </c>
       <c r="K10">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="L10">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="M10">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -50011,40 +50011,40 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="C11">
-        <v>146</v>
+        <v>271</v>
       </c>
       <c r="D11">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>141</v>
+        <v>246</v>
       </c>
       <c r="F11">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="G11">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="H11">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="I11">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="J11">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K11">
-        <v>151</v>
+        <v>243</v>
       </c>
       <c r="L11">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="M11">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4878</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7126</v>
       </c>
       <c r="M3">
-        <v>5484</v>
+        <v>5506</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6213</v>
       </c>
       <c r="M5">
-        <v>4297</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1956</v>
       </c>
       <c r="M6">
-        <v>1486</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>435</v>
       </c>
       <c r="M7">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17259</v>
       </c>
       <c r="M8">
-        <v>13826</v>
+        <v>13869</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3596</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>58729</v>
       </c>
       <c r="M10">
-        <v>44290</v>
+        <v>44463</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1282,7 +1282,7 @@
         <v>104496</v>
       </c>
       <c r="M11">
-        <v>78476</v>
+        <v>78780</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>636</v>
       </c>
       <c r="M8">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1676,7 +1676,7 @@
         <v>226</v>
       </c>
       <c r="M9">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2693</v>
+        <v>2702</v>
       </c>
     </row>
   </sheetData>
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2520,7 +2520,7 @@
         <v>77</v>
       </c>
       <c r="M9">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1200</v>
       </c>
       <c r="M10">
-        <v>999</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1426</v>
+        <v>1439</v>
       </c>
     </row>
   </sheetData>
@@ -2832,7 +2832,7 @@
         <v>62</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2952,7 +2952,7 @@
         <v>121</v>
       </c>
       <c r="M8">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
   </sheetData>
@@ -3504,7 +3504,7 @@
         <v>321</v>
       </c>
       <c r="M10">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>782</v>
       </c>
       <c r="M11">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -3652,7 +3652,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3816,7 +3816,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3898,7 +3898,7 @@
         <v>138</v>
       </c>
       <c r="M8">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4292,7 +4292,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3317</v>
+        <v>3333</v>
       </c>
     </row>
   </sheetData>
@@ -4645,7 +4645,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4727,7 +4727,7 @@
         <v>194</v>
       </c>
       <c r="M5">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1737</v>
+        <v>1743</v>
       </c>
     </row>
   </sheetData>
@@ -5080,7 +5080,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5121,7 +5121,7 @@
         <v>150</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5203,7 +5203,7 @@
         <v>91</v>
       </c>
       <c r="M5">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5326,7 +5326,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5367,7 +5367,7 @@
         <v>79</v>
       </c>
       <c r="M9">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1200</v>
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -5679,7 +5679,7 @@
         <v>76</v>
       </c>
       <c r="M5">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1151</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>
@@ -6269,7 +6269,7 @@
         <v>208</v>
       </c>
       <c r="M8">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1904</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2412</v>
+        <v>2431</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>782</v>
       </c>
       <c r="M6">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1737</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3317</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1444</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6950,7 +6950,7 @@
         <v>267</v>
       </c>
       <c r="M13">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -6991,7 +6991,7 @@
         <v>727</v>
       </c>
       <c r="M14">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1597</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1694</v>
       </c>
       <c r="M20">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7319,7 +7319,7 @@
         <v>383</v>
       </c>
       <c r="M22">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7401,7 +7401,7 @@
         <v>531</v>
       </c>
       <c r="M24">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7483,7 +7483,7 @@
         <v>234</v>
       </c>
       <c r="M26">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3353</v>
       </c>
       <c r="M29">
-        <v>2509</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>1992</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7852,7 +7852,7 @@
         <v>323</v>
       </c>
       <c r="M35">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1151</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1783</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8057,7 +8057,7 @@
         <v>329</v>
       </c>
       <c r="M40">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2489</v>
       </c>
       <c r="M42">
-        <v>2398</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8221,7 +8221,7 @@
         <v>973</v>
       </c>
       <c r="M44">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8303,7 +8303,7 @@
         <v>300</v>
       </c>
       <c r="M46">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2081</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1394</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>797</v>
+        <v>801</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1407</v>
       </c>
       <c r="M52">
-        <v>1025</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1426</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2804</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8795,7 +8795,7 @@
         <v>143</v>
       </c>
       <c r="M58">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8836,7 +8836,7 @@
         <v>297</v>
       </c>
       <c r="M59">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -9000,7 +9000,7 @@
         <v>1382</v>
       </c>
       <c r="M63">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9123,7 +9123,7 @@
         <v>602</v>
       </c>
       <c r="M66">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1914</v>
       </c>
       <c r="M67">
-        <v>1518</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9205,7 +9205,7 @@
         <v>500</v>
       </c>
       <c r="M68">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>346</v>
       </c>
       <c r="M71">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9492,7 +9492,7 @@
         <v>426</v>
       </c>
       <c r="M75">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2412</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1402</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2693</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1647</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1200</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10558,7 +10558,7 @@
         <v>104496</v>
       </c>
       <c r="M101">
-        <v>78476</v>
+        <v>78780</v>
       </c>
     </row>
   </sheetData>
@@ -10767,7 +10767,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10887,7 +10887,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1394</v>
+        <v>1400</v>
       </c>
     </row>
   </sheetData>
@@ -11447,7 +11447,7 @@
         <v>65</v>
       </c>
       <c r="M8">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11570,7 +11570,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -11677,7 +11677,7 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13107,7 +13107,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13271,7 +13271,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1164</v>
       </c>
       <c r="M10">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2489</v>
       </c>
       <c r="M11">
-        <v>2398</v>
+        <v>2405</v>
       </c>
     </row>
   </sheetData>
@@ -13501,7 +13501,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13583,7 +13583,7 @@
         <v>95</v>
       </c>
       <c r="M5">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13747,7 +13747,7 @@
         <v>175</v>
       </c>
       <c r="M9">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1914</v>
       </c>
       <c r="M11">
-        <v>1518</v>
+        <v>1526</v>
       </c>
     </row>
   </sheetData>
@@ -15074,7 +15074,7 @@
         <v>357</v>
       </c>
       <c r="M8">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2150</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2804</v>
+        <v>2819</v>
       </c>
     </row>
   </sheetData>
@@ -15345,7 +15345,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15614,7 +15614,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1525</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
   </sheetData>
@@ -16498,7 +16498,7 @@
         <v>37</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16539,7 +16539,7 @@
         <v>597</v>
       </c>
       <c r="M10">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16580,7 +16580,7 @@
         <v>973</v>
       </c>
       <c r="M11">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -16974,7 +16974,7 @@
         <v>82</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
   </sheetData>
@@ -17409,7 +17409,7 @@
         <v>102</v>
       </c>
       <c r="M8">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17491,7 +17491,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -17747,7 +17747,7 @@
         <v>66</v>
       </c>
       <c r="M5">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -18383,7 +18383,7 @@
         <v>179</v>
       </c>
       <c r="M10">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18424,7 +18424,7 @@
         <v>300</v>
       </c>
       <c r="M11">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1694</v>
       </c>
       <c r="M11">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
   </sheetData>
@@ -19007,7 +19007,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19130,7 +19130,7 @@
         <v>171</v>
       </c>
       <c r="M5">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19171,7 +19171,7 @@
         <v>52</v>
       </c>
       <c r="M6">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19253,7 +19253,7 @@
         <v>417</v>
       </c>
       <c r="M8">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19294,7 +19294,7 @@
         <v>209</v>
       </c>
       <c r="M9">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1783</v>
+        <v>1791</v>
       </c>
     </row>
   </sheetData>
@@ -19524,7 +19524,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1407</v>
       </c>
       <c r="M11">
-        <v>1025</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -19959,7 +19959,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20205,7 +20205,7 @@
         <v>284</v>
       </c>
       <c r="M8">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -21133,7 +21133,7 @@
         <v>119</v>
       </c>
       <c r="M8">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21215,7 +21215,7 @@
         <v>161</v>
       </c>
       <c r="M10">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21256,7 +21256,7 @@
         <v>346</v>
       </c>
       <c r="M11">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -21404,7 +21404,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21609,7 +21609,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21650,7 +21650,7 @@
         <v>104</v>
       </c>
       <c r="M9">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
@@ -22073,7 +22073,7 @@
         <v>56</v>
       </c>
       <c r="M8">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -22549,7 +22549,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22631,7 +22631,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -22922,7 +22922,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22977,7 +22977,7 @@
         <v>82</v>
       </c>
       <c r="M8">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -23248,7 +23248,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23312,7 +23312,7 @@
         <v>70</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23423,7 +23423,7 @@
         <v>189</v>
       </c>
       <c r="M8">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -23653,7 +23653,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23694,7 +23694,7 @@
         <v>195</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23776,7 +23776,7 @@
         <v>149</v>
       </c>
       <c r="M5">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23899,7 +23899,7 @@
         <v>468</v>
       </c>
       <c r="M8">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23940,7 +23940,7 @@
         <v>161</v>
       </c>
       <c r="M9">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1402</v>
+        <v>1411</v>
       </c>
     </row>
   </sheetData>
@@ -24339,7 +24339,7 @@
         <v>85</v>
       </c>
       <c r="M8">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24462,7 +24462,7 @@
         <v>602</v>
       </c>
       <c r="M11">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -24870,7 +24870,7 @@
         <v>301</v>
       </c>
       <c r="M10">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -25018,7 +25018,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>797</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25725,7 +25725,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25766,7 +25766,7 @@
         <v>286</v>
       </c>
       <c r="M9">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3353</v>
       </c>
       <c r="M11">
-        <v>2509</v>
+        <v>2518</v>
       </c>
     </row>
   </sheetData>
@@ -26262,7 +26262,7 @@
         <v>189</v>
       </c>
       <c r="M10">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26303,7 +26303,7 @@
         <v>383</v>
       </c>
       <c r="M11">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -26565,7 +26565,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -27090,7 +27090,7 @@
         <v>57</v>
       </c>
       <c r="M8">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27172,7 +27172,7 @@
         <v>338</v>
       </c>
       <c r="M10">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -27443,7 +27443,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1647</v>
+        <v>1653</v>
       </c>
     </row>
   </sheetData>
@@ -28121,7 +28121,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
   </sheetData>
@@ -28474,7 +28474,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -28556,7 +28556,7 @@
         <v>164</v>
       </c>
       <c r="M9">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1597</v>
+        <v>1602</v>
       </c>
     </row>
   </sheetData>
@@ -28991,7 +28991,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29032,7 +29032,7 @@
         <v>37</v>
       </c>
       <c r="M9">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30368,6 +30368,9 @@
       <c r="L7">
         <v>4</v>
       </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
@@ -30407,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30489,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30530,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1444</v>
+        <v>1451</v>
       </c>
     </row>
   </sheetData>
@@ -30908,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30949,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -31378,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31419,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
@@ -31646,7 +31649,7 @@
         <v>40</v>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31836,7 +31839,7 @@
         <v>306</v>
       </c>
       <c r="M10">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31877,7 +31880,7 @@
         <v>531</v>
       </c>
       <c r="M11">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -32104,7 +32107,7 @@
         <v>41</v>
       </c>
       <c r="M5">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -32309,7 +32312,7 @@
         <v>446</v>
       </c>
       <c r="M10">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32498,7 +32501,7 @@
         <v>51</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -32785,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32826,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -32974,7 +32977,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -33261,7 +33264,7 @@
         <v>478</v>
       </c>
       <c r="M10">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33302,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -33643,7 +33646,7 @@
         <v>192</v>
       </c>
       <c r="M8">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33725,7 +33728,7 @@
         <v>553</v>
       </c>
       <c r="M10">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33766,7 +33769,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -34080,7 +34083,7 @@
         <v>103</v>
       </c>
       <c r="M8">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -34162,7 +34165,7 @@
         <v>152</v>
       </c>
       <c r="M10">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34203,7 +34206,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -34553,7 +34556,7 @@
         <v>308</v>
       </c>
       <c r="M8">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -34635,7 +34638,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34676,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -34783,7 +34786,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35111,7 +35114,7 @@
         <v>400</v>
       </c>
       <c r="M10">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35152,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -35505,7 +35508,7 @@
         <v>206</v>
       </c>
       <c r="M8">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35546,7 +35549,7 @@
         <v>40</v>
       </c>
       <c r="M9">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -35587,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35628,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>
@@ -35735,7 +35738,7 @@
         <v>78</v>
       </c>
       <c r="M2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35776,7 +35779,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35858,7 +35861,7 @@
         <v>104</v>
       </c>
       <c r="M5">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -36063,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36104,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -36445,7 +36448,7 @@
         <v>125</v>
       </c>
       <c r="M8">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36527,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36568,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -36943,7 +36946,7 @@
         <v>204</v>
       </c>
       <c r="M10">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36984,7 +36987,7 @@
         <v>267</v>
       </c>
       <c r="M11">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -38037,7 +38040,7 @@
         <v>19</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -38130,7 +38133,7 @@
         <v>33</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -38253,7 +38256,7 @@
         <v>234</v>
       </c>
       <c r="M11">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -38676,7 +38679,7 @@
         <v>151</v>
       </c>
       <c r="M10">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38717,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -38824,7 +38827,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -38947,7 +38950,7 @@
         <v>42</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -39152,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39193,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -39601,7 +39604,7 @@
         <v>328</v>
       </c>
       <c r="M10">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39642,7 +39645,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -40023,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40064,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -40839,7 +40842,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -40921,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1615</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40962,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2081</v>
+        <v>2085</v>
       </c>
     </row>
   </sheetData>
@@ -41831,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41872,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -42295,7 +42298,7 @@
         <v>426</v>
       </c>
       <c r="M10">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42336,7 +42339,7 @@
         <v>727</v>
       </c>
       <c r="M11">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -43074,7 +43077,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -43270,7 +43273,7 @@
         <v>426</v>
       </c>
       <c r="M11">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -44088,7 +44091,7 @@
         <v>265</v>
       </c>
       <c r="M10">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44129,7 +44132,7 @@
         <v>323</v>
       </c>
       <c r="M11">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -44277,7 +44280,7 @@
         <v>32</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -44602,7 +44605,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -45131,7 +45134,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45172,7 +45175,7 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45365,7 +45368,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45447,7 +45450,7 @@
         <v>485</v>
       </c>
       <c r="M10">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45488,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -45595,7 +45598,7 @@
         <v>265</v>
       </c>
       <c r="M2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45636,7 +45639,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45882,7 +45885,7 @@
         <v>271</v>
       </c>
       <c r="M9">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45923,7 +45926,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45964,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>1992</v>
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -46306,7 +46309,7 @@
         <v>129</v>
       </c>
       <c r="M10">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46347,7 +46350,7 @@
         <v>143</v>
       </c>
       <c r="M11">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -47044,7 +47047,7 @@
         <v>18</v>
       </c>
       <c r="M8">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47126,7 +47129,7 @@
         <v>200</v>
       </c>
       <c r="M10">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:13">

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>4895</v>
+        <v>4911</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7126</v>
       </c>
       <c r="M3">
-        <v>5506</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6213</v>
       </c>
       <c r="M5">
-        <v>4319</v>
+        <v>4334</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1956</v>
       </c>
       <c r="M6">
-        <v>1492</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17259</v>
       </c>
       <c r="M8">
-        <v>13869</v>
+        <v>13911</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3615</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>58729</v>
       </c>
       <c r="M10">
-        <v>44463</v>
+        <v>44588</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1282,7 +1282,7 @@
         <v>104496</v>
       </c>
       <c r="M11">
-        <v>78780</v>
+        <v>79045</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1512,7 +1512,7 @@
         <v>304</v>
       </c>
       <c r="M5">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>636</v>
       </c>
       <c r="M8">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1676,7 +1676,7 @@
         <v>226</v>
       </c>
       <c r="M9">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2702</v>
+        <v>2709</v>
       </c>
     </row>
   </sheetData>
@@ -2085,7 +2085,7 @@
         <v>36</v>
       </c>
       <c r="M10">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2126,7 +2126,7 @@
         <v>61</v>
       </c>
       <c r="M11">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2561,7 +2561,7 @@
         <v>1200</v>
       </c>
       <c r="M10">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1439</v>
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +2952,7 @@
         <v>121</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2993,7 +2993,7 @@
         <v>41</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>906</v>
+        <v>914</v>
       </c>
     </row>
   </sheetData>
@@ -3652,7 +3652,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4251,7 +4251,7 @@
         <v>216</v>
       </c>
       <c r="M5">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1392</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3333</v>
+        <v>3345</v>
       </c>
     </row>
   </sheetData>
@@ -4604,7 +4604,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4645,7 +4645,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1743</v>
+        <v>1750</v>
       </c>
     </row>
   </sheetData>
@@ -5080,7 +5080,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5367,7 +5367,7 @@
         <v>79</v>
       </c>
       <c r="M9">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1206</v>
+        <v>1209</v>
       </c>
     </row>
   </sheetData>
@@ -5556,7 +5556,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5597,7 +5597,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
@@ -6070,7 +6070,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6146,7 +6146,7 @@
         <v>82</v>
       </c>
       <c r="M5">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1921</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2431</v>
+        <v>2437</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1743</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3333</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>906</v>
+        <v>914</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1451</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6991,7 +6991,7 @@
         <v>727</v>
       </c>
       <c r="M14">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1694</v>
       </c>
       <c r="M20">
-        <v>1291</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>578</v>
       </c>
       <c r="M25">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3353</v>
       </c>
       <c r="M29">
-        <v>2518</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7647,7 +7647,7 @@
         <v>274</v>
       </c>
       <c r="M30">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2002</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1791</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8057,7 +8057,7 @@
         <v>329</v>
       </c>
       <c r="M40">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -8098,7 +8098,7 @@
         <v>360</v>
       </c>
       <c r="M41">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2489</v>
       </c>
       <c r="M42">
-        <v>2405</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8221,7 +8221,7 @@
         <v>973</v>
       </c>
       <c r="M44">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8262,7 +8262,7 @@
         <v>141</v>
       </c>
       <c r="M45">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2085</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1400</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1407</v>
       </c>
       <c r="M52">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1439</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2819</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8959,7 +8959,7 @@
         <v>61</v>
       </c>
       <c r="M62">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -9000,7 +9000,7 @@
         <v>1382</v>
       </c>
       <c r="M63">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1096</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1914</v>
       </c>
       <c r="M67">
-        <v>1526</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>346</v>
       </c>
       <c r="M71">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9451,7 +9451,7 @@
         <v>308</v>
       </c>
       <c r="M74">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2431</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>921</v>
+        <v>929</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1411</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1124</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2702</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>768</v>
+        <v>777</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2123</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1206</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10558,7 +10558,7 @@
         <v>104496</v>
       </c>
       <c r="M101">
-        <v>78780</v>
+        <v>79045</v>
       </c>
     </row>
   </sheetData>
@@ -10808,7 +10808,7 @@
         <v>17</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1051</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1400</v>
+        <v>1405</v>
       </c>
     </row>
   </sheetData>
@@ -11914,7 +11914,7 @@
         <v>354</v>
       </c>
       <c r="M8">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
   </sheetData>
@@ -12754,7 +12754,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1164</v>
       </c>
       <c r="M10">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2489</v>
       </c>
       <c r="M11">
-        <v>2405</v>
+        <v>2409</v>
       </c>
     </row>
   </sheetData>
@@ -13501,7 +13501,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13583,7 +13583,7 @@
         <v>95</v>
       </c>
       <c r="M5">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13706,7 +13706,7 @@
         <v>317</v>
       </c>
       <c r="M8">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1914</v>
       </c>
       <c r="M11">
-        <v>1526</v>
+        <v>1533</v>
       </c>
     </row>
   </sheetData>
@@ -14252,7 +14252,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14293,7 +14293,7 @@
         <v>360</v>
       </c>
       <c r="M11">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -15115,7 +15115,7 @@
         <v>207</v>
       </c>
       <c r="M9">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2163</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2819</v>
+        <v>2825</v>
       </c>
     </row>
   </sheetData>
@@ -15803,7 +15803,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15990,7 +15990,7 @@
         <v>360</v>
       </c>
       <c r="M8">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2123</v>
+        <v>2130</v>
       </c>
     </row>
   </sheetData>
@@ -16381,7 +16381,7 @@
         <v>11</v>
       </c>
       <c r="M6">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16580,7 +16580,7 @@
         <v>973</v>
       </c>
       <c r="M11">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -16974,7 +16974,7 @@
         <v>82</v>
       </c>
       <c r="M9">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>921</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>
@@ -17409,7 +17409,7 @@
         <v>102</v>
       </c>
       <c r="M8">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -17747,7 +17747,7 @@
         <v>66</v>
       </c>
       <c r="M5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -18572,7 +18572,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18654,7 +18654,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18695,7 +18695,7 @@
         <v>48</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18777,7 +18777,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1694</v>
       </c>
       <c r="M11">
-        <v>1291</v>
+        <v>1301</v>
       </c>
     </row>
   </sheetData>
@@ -19007,7 +19007,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19048,7 +19048,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19089,7 +19089,7 @@
         <v>16</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19130,7 +19130,7 @@
         <v>171</v>
       </c>
       <c r="M5">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19294,7 +19294,7 @@
         <v>209</v>
       </c>
       <c r="M9">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1791</v>
+        <v>1803</v>
       </c>
     </row>
   </sheetData>
@@ -19524,7 +19524,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1407</v>
       </c>
       <c r="M11">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -20000,7 +20000,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20082,7 +20082,7 @@
         <v>147</v>
       </c>
       <c r="M5">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -20476,7 +20476,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20681,7 +20681,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -20952,7 +20952,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21174,7 +21174,7 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21256,7 +21256,7 @@
         <v>346</v>
       </c>
       <c r="M11">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -21363,7 +21363,7 @@
         <v>165</v>
       </c>
       <c r="M2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21609,7 +21609,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21650,7 +21650,7 @@
         <v>104</v>
       </c>
       <c r="M9">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21691,7 +21691,7 @@
         <v>603</v>
       </c>
       <c r="M10">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1096</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -21839,7 +21839,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -22922,7 +22922,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -23248,7 +23248,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1035</v>
       </c>
       <c r="M10">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
   </sheetData>
@@ -23653,7 +23653,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23694,7 +23694,7 @@
         <v>195</v>
       </c>
       <c r="M3">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23776,7 +23776,7 @@
         <v>149</v>
       </c>
       <c r="M5">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1411</v>
+        <v>1417</v>
       </c>
     </row>
   </sheetData>
@@ -24339,7 +24339,7 @@
         <v>85</v>
       </c>
       <c r="M8">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24421,7 +24421,7 @@
         <v>383</v>
       </c>
       <c r="M10">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -25479,7 +25479,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25520,7 +25520,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25643,7 +25643,7 @@
         <v>66</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25725,7 +25725,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25766,7 +25766,7 @@
         <v>286</v>
       </c>
       <c r="M9">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3353</v>
       </c>
       <c r="M11">
-        <v>2518</v>
+        <v>2529</v>
       </c>
     </row>
   </sheetData>
@@ -26524,7 +26524,7 @@
         <v>40</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -27563,7 +27563,7 @@
         <v>178</v>
       </c>
       <c r="M8">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
   </sheetData>
@@ -28310,7 +28310,7 @@
         <v>180</v>
       </c>
       <c r="M3">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -28786,7 +28786,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28868,7 +28868,7 @@
         <v>73</v>
       </c>
       <c r="M5">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28991,7 +28991,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29073,7 +29073,7 @@
         <v>423</v>
       </c>
       <c r="M10">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -29262,7 +29262,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29508,7 +29508,7 @@
         <v>106</v>
       </c>
       <c r="M9">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1124</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -30016,7 +30016,7 @@
         <v>108</v>
       </c>
       <c r="M10">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30057,7 +30057,7 @@
         <v>274</v>
       </c>
       <c r="M11">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -30205,7 +30205,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30287,7 +30287,7 @@
         <v>99</v>
       </c>
       <c r="M5">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1451</v>
+        <v>1457</v>
       </c>
     </row>
   </sheetData>
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -31299,7 +31299,7 @@
         <v>324</v>
       </c>
       <c r="M8">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31381,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -32706,7 +32706,7 @@
         <v>185</v>
       </c>
       <c r="M8">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32788,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -33182,7 +33182,7 @@
         <v>293</v>
       </c>
       <c r="M8">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33223,7 +33223,7 @@
         <v>62</v>
       </c>
       <c r="M9">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -33917,7 +33917,7 @@
         <v>26</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -34124,7 +34124,7 @@
         <v>13</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -34206,7 +34206,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -34638,7 +34638,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
   </sheetData>
@@ -35114,7 +35114,7 @@
         <v>400</v>
       </c>
       <c r="M10">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35155,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -35303,7 +35303,7 @@
         <v>50</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35508,7 +35508,7 @@
         <v>206</v>
       </c>
       <c r="M8">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35590,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
   </sheetData>
@@ -35984,7 +35984,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36066,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36107,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -36214,7 +36214,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -38638,7 +38638,7 @@
         <v>23</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -38720,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -38827,7 +38827,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -39114,7 +39114,7 @@
         <v>45</v>
       </c>
       <c r="M9">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -39196,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -40842,7 +40842,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1620</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2085</v>
+        <v>2089</v>
       </c>
     </row>
   </sheetData>
@@ -41113,7 +41113,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41400,7 +41400,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41441,7 +41441,7 @@
         <v>578</v>
       </c>
       <c r="M11">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -41691,7 +41691,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -41752,7 +41752,7 @@
         <v>87</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41834,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41875,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>768</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -42257,7 +42257,7 @@
         <v>25</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -42339,7 +42339,7 @@
         <v>727</v>
       </c>
       <c r="M11">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -44362,7 +44362,7 @@
         <v>52</v>
       </c>
       <c r="M5">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44564,7 +44564,7 @@
         <v>385</v>
       </c>
       <c r="M10">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44605,7 +44605,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -45134,7 +45134,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45450,7 +45450,7 @@
         <v>485</v>
       </c>
       <c r="M10">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -45639,7 +45639,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45844,7 +45844,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45926,7 +45926,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2002</v>
+        <v>2005</v>
       </c>
     </row>
   </sheetData>
@@ -49192,7 +49192,7 @@
         <v>74</v>
       </c>
       <c r="M9">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -49233,7 +49233,7 @@
         <v>141</v>
       </c>
       <c r="M10">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -49605,7 +49605,7 @@
         <v>263</v>
       </c>
       <c r="M10">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49646,7 +49646,7 @@
         <v>308</v>
       </c>
       <c r="M11">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5042</v>
+        <v>5064</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7128</v>
       </c>
       <c r="M3">
-        <v>5655</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6214</v>
       </c>
       <c r="M5">
-        <v>4465</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1958</v>
       </c>
       <c r="M6">
-        <v>1534</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17260</v>
       </c>
       <c r="M8">
-        <v>14198</v>
+        <v>14248</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3698</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>58729</v>
       </c>
       <c r="M10">
-        <v>45578</v>
+        <v>45727</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1282,7 +1282,7 @@
         <v>104503</v>
       </c>
       <c r="M11">
-        <v>80805</v>
+        <v>81082</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>636</v>
       </c>
       <c r="M8">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1676,7 +1676,7 @@
         <v>226</v>
       </c>
       <c r="M9">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2762</v>
+        <v>2770</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2233,7 @@
         <v>71</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1199</v>
       </c>
       <c r="M10">
-        <v>1034</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1471</v>
+        <v>1480</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +2952,7 @@
         <v>121</v>
       </c>
       <c r="M8">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -3182,7 +3182,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3299,7 +3299,7 @@
         <v>54</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3504,7 +3504,7 @@
         <v>321</v>
       </c>
       <c r="M10">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>783</v>
       </c>
       <c r="M11">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>964</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4292,7 +4292,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1427</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3420</v>
+        <v>3430</v>
       </c>
     </row>
   </sheetData>
@@ -4768,7 +4768,7 @@
         <v>43</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4891,7 +4891,7 @@
         <v>166</v>
       </c>
       <c r="M9">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1789</v>
+        <v>1795</v>
       </c>
     </row>
   </sheetData>
@@ -5203,7 +5203,7 @@
         <v>91</v>
       </c>
       <c r="M5">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5326,7 +5326,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
   </sheetData>
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -6029,7 +6029,7 @@
         <v>68</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6269,7 +6269,7 @@
         <v>208</v>
       </c>
       <c r="M8">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6310,7 +6310,7 @@
         <v>159</v>
       </c>
       <c r="M9">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1964</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2488</v>
+        <v>2499</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>783</v>
       </c>
       <c r="M6">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1789</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3420</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1489</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6909,7 +6909,7 @@
         <v>408</v>
       </c>
       <c r="M12">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6950,7 +6950,7 @@
         <v>267</v>
       </c>
       <c r="M13">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -6991,7 +6991,7 @@
         <v>727</v>
       </c>
       <c r="M14">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1642</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1696</v>
       </c>
       <c r="M20">
-        <v>1340</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7401,7 +7401,7 @@
         <v>531</v>
       </c>
       <c r="M24">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>578</v>
       </c>
       <c r="M25">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7483,7 +7483,7 @@
         <v>234</v>
       </c>
       <c r="M26">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7565,7 +7565,7 @@
         <v>86</v>
       </c>
       <c r="M28">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3353</v>
       </c>
       <c r="M29">
-        <v>2580</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>964</v>
+        <v>970</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2059</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1851</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -7975,7 +7975,7 @@
         <v>133</v>
       </c>
       <c r="M38">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2488</v>
       </c>
       <c r="M42">
-        <v>2459</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8221,7 +8221,7 @@
         <v>973</v>
       </c>
       <c r="M44">
-        <v>778</v>
+        <v>785</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2131</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1407</v>
       </c>
       <c r="M52">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1471</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2887</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8795,7 +8795,7 @@
         <v>143</v>
       </c>
       <c r="M58">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8836,7 +8836,7 @@
         <v>297</v>
       </c>
       <c r="M59">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8877,7 +8877,7 @@
         <v>737</v>
       </c>
       <c r="M60">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -9000,7 +9000,7 @@
         <v>1387</v>
       </c>
       <c r="M63">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9123,7 +9123,7 @@
         <v>602</v>
       </c>
       <c r="M66">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1914</v>
       </c>
       <c r="M67">
-        <v>1565</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9205,7 +9205,7 @@
         <v>500</v>
       </c>
       <c r="M68">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>346</v>
       </c>
       <c r="M71">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9492,7 +9492,7 @@
         <v>426</v>
       </c>
       <c r="M75">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2488</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9574,7 +9574,7 @@
         <v>374</v>
       </c>
       <c r="M77">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1461</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9697,7 +9697,7 @@
         <v>468</v>
       </c>
       <c r="M80">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9779,7 +9779,7 @@
         <v>231</v>
       </c>
       <c r="M82">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1157</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2762</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1692</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2187</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>968</v>
+        <v>972</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10558,7 +10558,7 @@
         <v>104503</v>
       </c>
       <c r="M101">
-        <v>80805</v>
+        <v>81082</v>
       </c>
     </row>
   </sheetData>
@@ -11036,7 +11036,7 @@
         <v>45</v>
       </c>
       <c r="M9">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
   </sheetData>
@@ -11529,7 +11529,7 @@
         <v>169</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11570,7 +11570,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -11677,7 +11677,7 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11914,7 +11914,7 @@
         <v>354</v>
       </c>
       <c r="M8">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -12754,7 +12754,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13148,7 +13148,7 @@
         <v>52</v>
       </c>
       <c r="M6">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1163</v>
       </c>
       <c r="M10">
-        <v>1193</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2488</v>
       </c>
       <c r="M11">
-        <v>2459</v>
+        <v>2468</v>
       </c>
     </row>
   </sheetData>
@@ -13501,7 +13501,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1914</v>
       </c>
       <c r="M11">
-        <v>1565</v>
+        <v>1568</v>
       </c>
     </row>
   </sheetData>
@@ -14954,7 +14954,7 @@
         <v>71</v>
       </c>
       <c r="M5">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2213</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2887</v>
+        <v>2891</v>
       </c>
     </row>
   </sheetData>
@@ -15532,7 +15532,7 @@
         <v>76</v>
       </c>
       <c r="M8">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15614,7 +15614,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1576</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2187</v>
+        <v>2192</v>
       </c>
     </row>
   </sheetData>
@@ -16340,7 +16340,7 @@
         <v>78</v>
       </c>
       <c r="M5">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16457,7 +16457,7 @@
         <v>148</v>
       </c>
       <c r="M8">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16539,7 +16539,7 @@
         <v>597</v>
       </c>
       <c r="M10">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16580,7 +16580,7 @@
         <v>973</v>
       </c>
       <c r="M11">
-        <v>778</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -16933,7 +16933,7 @@
         <v>222</v>
       </c>
       <c r="M8">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>
@@ -17163,7 +17163,7 @@
         <v>40</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17204,7 +17204,7 @@
         <v>45</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -18777,7 +18777,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1696</v>
       </c>
       <c r="M11">
-        <v>1340</v>
+        <v>1346</v>
       </c>
     </row>
   </sheetData>
@@ -19048,7 +19048,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19253,7 +19253,7 @@
         <v>417</v>
       </c>
       <c r="M8">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1851</v>
+        <v>1857</v>
       </c>
     </row>
   </sheetData>
@@ -19483,7 +19483,7 @@
         <v>145</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19770,7 +19770,7 @@
         <v>127</v>
       </c>
       <c r="M9">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1407</v>
       </c>
       <c r="M11">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -19959,7 +19959,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20205,7 +20205,7 @@
         <v>284</v>
       </c>
       <c r="M8">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>968</v>
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -20435,7 +20435,7 @@
         <v>66</v>
       </c>
       <c r="M2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>
@@ -20952,7 +20952,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21256,7 +21256,7 @@
         <v>346</v>
       </c>
       <c r="M11">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -21404,7 +21404,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21609,7 +21609,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
   </sheetData>
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -22549,7 +22549,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>
@@ -23059,7 +23059,7 @@
         <v>524</v>
       </c>
       <c r="M10">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -23423,7 +23423,7 @@
         <v>189</v>
       </c>
       <c r="M8">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1035</v>
       </c>
       <c r="M10">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -23653,7 +23653,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1461</v>
+        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -24421,7 +24421,7 @@
         <v>383</v>
       </c>
       <c r="M10">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24462,7 +24462,7 @@
         <v>602</v>
       </c>
       <c r="M11">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -24829,7 +24829,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -25249,7 +25249,7 @@
         <v>95</v>
       </c>
       <c r="M8">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -25479,7 +25479,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25520,7 +25520,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25643,7 +25643,7 @@
         <v>66</v>
       </c>
       <c r="M6">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25725,7 +25725,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25766,7 +25766,7 @@
         <v>286</v>
       </c>
       <c r="M9">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>989</v>
+        <v>993</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3353</v>
       </c>
       <c r="M11">
-        <v>2580</v>
+        <v>2593</v>
       </c>
     </row>
   </sheetData>
@@ -26641,7 +26641,7 @@
         <v>225</v>
       </c>
       <c r="M8">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -27172,7 +27172,7 @@
         <v>338</v>
       </c>
       <c r="M10">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -27361,7 +27361,7 @@
         <v>86</v>
       </c>
       <c r="M3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27443,7 +27443,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27563,7 +27563,7 @@
         <v>178</v>
       </c>
       <c r="M8">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1692</v>
+        <v>1697</v>
       </c>
     </row>
   </sheetData>
@@ -27875,7 +27875,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -28039,7 +28039,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28121,7 +28121,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -28310,7 +28310,7 @@
         <v>180</v>
       </c>
       <c r="M3">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1642</v>
+        <v>1647</v>
       </c>
     </row>
   </sheetData>
@@ -29073,7 +29073,7 @@
         <v>423</v>
       </c>
       <c r="M10">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -29262,7 +29262,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29344,7 +29344,7 @@
         <v>125</v>
       </c>
       <c r="M5">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1157</v>
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30205,7 +30205,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>901</v>
+        <v>907</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1489</v>
+        <v>1498</v>
       </c>
     </row>
   </sheetData>
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -31299,7 +31299,7 @@
         <v>324</v>
       </c>
       <c r="M8">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31381,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -31649,7 +31649,7 @@
         <v>40</v>
       </c>
       <c r="M5">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31839,7 +31839,7 @@
         <v>306</v>
       </c>
       <c r="M10">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31880,7 +31880,7 @@
         <v>531</v>
       </c>
       <c r="M11">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -32230,7 +32230,7 @@
         <v>105</v>
       </c>
       <c r="M8">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32353,7 +32353,7 @@
         <v>737</v>
       </c>
       <c r="M11">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -32706,7 +32706,7 @@
         <v>185</v>
       </c>
       <c r="M8">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32788,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -32936,7 +32936,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -32977,7 +32977,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -34354,7 +34354,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -34597,7 +34597,7 @@
         <v>57</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -34638,7 +34638,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>
@@ -35114,7 +35114,7 @@
         <v>400</v>
       </c>
       <c r="M10">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35155,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -35262,7 +35262,7 @@
         <v>61</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35590,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -35984,7 +35984,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36066,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36107,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
   </sheetData>
@@ -36530,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -36864,7 +36864,7 @@
         <v>17</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36987,7 +36987,7 @@
         <v>267</v>
       </c>
       <c r="M11">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -37286,7 +37286,7 @@
         <v>19</v>
       </c>
       <c r="M8">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -37409,7 +37409,7 @@
         <v>231</v>
       </c>
       <c r="M11">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -38215,7 +38215,7 @@
         <v>164</v>
       </c>
       <c r="M10">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38256,7 +38256,7 @@
         <v>234</v>
       </c>
       <c r="M11">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -38404,7 +38404,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -38597,7 +38597,7 @@
         <v>69</v>
       </c>
       <c r="M8">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -38720,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -39073,7 +39073,7 @@
         <v>158</v>
       </c>
       <c r="M8">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39155,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39196,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -39344,7 +39344,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -39645,7 +39645,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -40026,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40067,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -40466,7 +40466,7 @@
         <v>247</v>
       </c>
       <c r="M10">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40507,7 +40507,7 @@
         <v>408</v>
       </c>
       <c r="M11">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -40772,7 +40772,7 @@
         <v>56</v>
       </c>
       <c r="M6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -40842,7 +40842,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2131</v>
+        <v>2133</v>
       </c>
     </row>
   </sheetData>
@@ -41318,7 +41318,7 @@
         <v>203</v>
       </c>
       <c r="M8">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41359,7 +41359,7 @@
         <v>19</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41441,7 +41441,7 @@
         <v>578</v>
       </c>
       <c r="M11">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -41834,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41875,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -42143,7 +42143,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -42216,7 +42216,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -42298,7 +42298,7 @@
         <v>426</v>
       </c>
       <c r="M10">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42339,7 +42339,7 @@
         <v>727</v>
       </c>
       <c r="M11">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -42446,7 +42446,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42487,7 +42487,7 @@
         <v>47</v>
       </c>
       <c r="M3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42774,7 +42774,7 @@
         <v>133</v>
       </c>
       <c r="M10">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42815,7 +42815,7 @@
         <v>374</v>
       </c>
       <c r="M11">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -43191,7 +43191,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -43273,7 +43273,7 @@
         <v>426</v>
       </c>
       <c r="M11">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -44482,7 +44482,7 @@
         <v>140</v>
       </c>
       <c r="M8">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44564,7 +44564,7 @@
         <v>385</v>
       </c>
       <c r="M10">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44605,7 +44605,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -44986,7 +44986,7 @@
         <v>364</v>
       </c>
       <c r="M10">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45027,7 +45027,7 @@
         <v>468</v>
       </c>
       <c r="M11">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -45134,7 +45134,7 @@
         <v>38</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45254,7 +45254,7 @@
         <v>50</v>
       </c>
       <c r="M5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -45639,7 +45639,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45721,7 +45721,7 @@
         <v>125</v>
       </c>
       <c r="M5">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45762,7 +45762,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -45844,7 +45844,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45926,7 +45926,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2059</v>
+        <v>2067</v>
       </c>
     </row>
   </sheetData>
@@ -46309,7 +46309,7 @@
         <v>129</v>
       </c>
       <c r="M10">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46350,7 +46350,7 @@
         <v>143</v>
       </c>
       <c r="M11">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -46634,7 +46634,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -46754,7 +46754,7 @@
         <v>86</v>
       </c>
       <c r="M11">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -47047,7 +47047,7 @@
         <v>18</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47129,7 +47129,7 @@
         <v>200</v>
       </c>
       <c r="M10">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48362,7 +48362,7 @@
         <v>92</v>
       </c>
       <c r="M10">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48403,7 +48403,7 @@
         <v>133</v>
       </c>
       <c r="M11">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5064</v>
+        <v>5081</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>8363</v>
       </c>
       <c r="I3">
-        <v>7508</v>
+        <v>7509</v>
       </c>
       <c r="J3">
         <v>8099</v>
@@ -954,7 +954,7 @@
         <v>7128</v>
       </c>
       <c r="M3">
-        <v>5681</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1033,10 +1033,10 @@
         <v>7661</v>
       </c>
       <c r="L5">
-        <v>6214</v>
+        <v>6215</v>
       </c>
       <c r="M5">
-        <v>4475</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>1886</v>
       </c>
       <c r="I6">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="J6">
         <v>2043</v>
@@ -1074,10 +1074,10 @@
         <v>1958</v>
       </c>
       <c r="L6">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="M6">
-        <v>1539</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>436</v>
       </c>
       <c r="M7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17260</v>
       </c>
       <c r="M8">
-        <v>14248</v>
+        <v>14288</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3712</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>58729</v>
       </c>
       <c r="M10">
-        <v>45727</v>
+        <v>45887</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1270,7 +1270,7 @@
         <v>84848</v>
       </c>
       <c r="I11">
-        <v>110884</v>
+        <v>110886</v>
       </c>
       <c r="J11">
         <v>124341</v>
@@ -1279,10 +1279,10 @@
         <v>118959</v>
       </c>
       <c r="L11">
-        <v>104503</v>
+        <v>104505</v>
       </c>
       <c r="M11">
-        <v>81082</v>
+        <v>81357</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1512,7 +1512,7 @@
         <v>304</v>
       </c>
       <c r="M5">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1553,7 +1553,7 @@
         <v>66</v>
       </c>
       <c r="M6">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1676,7 +1676,7 @@
         <v>226</v>
       </c>
       <c r="M9">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2770</v>
+        <v>2776</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2520,7 @@
         <v>77</v>
       </c>
       <c r="M9">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1199</v>
       </c>
       <c r="M10">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1480</v>
+        <v>1485</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +2952,7 @@
         <v>121</v>
       </c>
       <c r="M8">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -3182,7 +3182,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>783</v>
       </c>
       <c r="M11">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4292,7 +4292,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3430</v>
+        <v>3441</v>
       </c>
     </row>
   </sheetData>
@@ -4604,7 +4604,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4727,7 +4727,7 @@
         <v>194</v>
       </c>
       <c r="M5">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4850,7 +4850,7 @@
         <v>569</v>
       </c>
       <c r="M8">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1795</v>
+        <v>1801</v>
       </c>
     </row>
   </sheetData>
@@ -5080,7 +5080,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
   </sheetData>
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1196</v>
+        <v>1202</v>
       </c>
     </row>
   </sheetData>
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1970</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2499</v>
+        <v>2507</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>783</v>
       </c>
       <c r="M6">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1795</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3430</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1498</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6909,7 +6909,7 @@
         <v>408</v>
       </c>
       <c r="M12">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6991,7 +6991,7 @@
         <v>727</v>
       </c>
       <c r="M14">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1696</v>
       </c>
       <c r="M20">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7319,7 +7319,7 @@
         <v>383</v>
       </c>
       <c r="M22">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>578</v>
       </c>
       <c r="M25">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7483,7 +7483,7 @@
         <v>234</v>
       </c>
       <c r="M26">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3353</v>
       </c>
       <c r="M29">
-        <v>2593</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7647,7 +7647,7 @@
         <v>274</v>
       </c>
       <c r="M30">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2067</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1196</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1857</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8057,7 +8057,7 @@
         <v>329</v>
       </c>
       <c r="M40">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -8098,7 +8098,7 @@
         <v>360</v>
       </c>
       <c r="M41">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2488</v>
       </c>
       <c r="M42">
-        <v>2468</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8221,7 +8221,7 @@
         <v>973</v>
       </c>
       <c r="M44">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8303,7 +8303,7 @@
         <v>300</v>
       </c>
       <c r="M46">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2133</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1434</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1407</v>
       </c>
       <c r="M52">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1480</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2891</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8836,7 +8836,7 @@
         <v>297</v>
       </c>
       <c r="M59">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8877,7 +8877,7 @@
         <v>737</v>
       </c>
       <c r="M60">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8988,7 +8988,7 @@
         <v>2419</v>
       </c>
       <c r="I63">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="J63">
         <v>1259</v>
@@ -8997,10 +8997,10 @@
         <v>1085</v>
       </c>
       <c r="L63">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="M63">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1134</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1914</v>
       </c>
       <c r="M67">
-        <v>1568</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>346</v>
       </c>
       <c r="M71">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9451,7 +9451,7 @@
         <v>308</v>
       </c>
       <c r="M74">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2499</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1464</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2770</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1697</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2192</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10517,7 +10517,7 @@
         <v>277</v>
       </c>
       <c r="M100">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -10546,7 +10546,7 @@
         <v>84848</v>
       </c>
       <c r="I101">
-        <v>110884</v>
+        <v>110886</v>
       </c>
       <c r="J101">
         <v>124341</v>
@@ -10555,10 +10555,10 @@
         <v>118959</v>
       </c>
       <c r="L101">
-        <v>104503</v>
+        <v>104505</v>
       </c>
       <c r="M101">
-        <v>81082</v>
+        <v>81357</v>
       </c>
     </row>
   </sheetData>
@@ -11036,7 +11036,7 @@
         <v>45</v>
       </c>
       <c r="M9">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1072</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1434</v>
+        <v>1438</v>
       </c>
     </row>
   </sheetData>
@@ -11529,7 +11529,7 @@
         <v>169</v>
       </c>
       <c r="M10">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11570,7 +11570,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -11914,7 +11914,7 @@
         <v>354</v>
       </c>
       <c r="M8">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
   </sheetData>
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -12984,7 +12984,7 @@
         <v>187</v>
       </c>
       <c r="M2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1163</v>
       </c>
       <c r="M10">
-        <v>1195</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2488</v>
       </c>
       <c r="M11">
-        <v>2468</v>
+        <v>2475</v>
       </c>
     </row>
   </sheetData>
@@ -13665,7 +13665,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1914</v>
       </c>
       <c r="M11">
-        <v>1568</v>
+        <v>1575</v>
       </c>
     </row>
   </sheetData>
@@ -13977,7 +13977,7 @@
         <v>28</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14059,7 +14059,7 @@
         <v>25</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14252,7 +14252,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14293,7 +14293,7 @@
         <v>360</v>
       </c>
       <c r="M11">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -14831,7 +14831,7 @@
         <v>85</v>
       </c>
       <c r="M2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14872,7 +14872,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2216</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2891</v>
+        <v>2904</v>
       </c>
     </row>
   </sheetData>
@@ -15421,7 +15421,7 @@
         <v>35</v>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15532,7 +15532,7 @@
         <v>76</v>
       </c>
       <c r="M8">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -15762,7 +15762,7 @@
         <v>62</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15803,7 +15803,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15990,7 +15990,7 @@
         <v>360</v>
       </c>
       <c r="M8">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1581</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2192</v>
+        <v>2199</v>
       </c>
     </row>
   </sheetData>
@@ -16498,7 +16498,7 @@
         <v>37</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16580,7 +16580,7 @@
         <v>973</v>
       </c>
       <c r="M11">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -16728,7 +16728,7 @@
         <v>93</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16933,7 +16933,7 @@
         <v>222</v>
       </c>
       <c r="M8">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -17450,7 +17450,7 @@
         <v>30</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -17899,7 +17899,7 @@
         <v>50</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
   </sheetData>
@@ -18383,7 +18383,7 @@
         <v>179</v>
       </c>
       <c r="M10">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18424,7 +18424,7 @@
         <v>300</v>
       </c>
       <c r="M11">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -18777,7 +18777,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1696</v>
       </c>
       <c r="M11">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
   </sheetData>
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1857</v>
+        <v>1860</v>
       </c>
     </row>
   </sheetData>
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1407</v>
       </c>
       <c r="M11">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -20000,7 +20000,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20205,7 +20205,7 @@
         <v>284</v>
       </c>
       <c r="M8">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
   </sheetData>
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -21133,7 +21133,7 @@
         <v>119</v>
       </c>
       <c r="M8">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21215,7 +21215,7 @@
         <v>161</v>
       </c>
       <c r="M10">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21256,7 +21256,7 @@
         <v>346</v>
       </c>
       <c r="M11">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -21404,7 +21404,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21486,7 +21486,7 @@
         <v>101</v>
       </c>
       <c r="M5">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21650,7 +21650,7 @@
         <v>104</v>
       </c>
       <c r="M9">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21691,7 +21691,7 @@
         <v>603</v>
       </c>
       <c r="M10">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1134</v>
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -21880,7 +21880,7 @@
         <v>21</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21956,7 +21956,7 @@
         <v>39</v>
       </c>
       <c r="M5">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -22426,7 +22426,7 @@
         <v>40</v>
       </c>
       <c r="M5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22549,7 +22549,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -23059,7 +23059,7 @@
         <v>524</v>
       </c>
       <c r="M10">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -23312,7 +23312,7 @@
         <v>70</v>
       </c>
       <c r="M5">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1035</v>
       </c>
       <c r="M10">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -23776,7 +23776,7 @@
         <v>149</v>
       </c>
       <c r="M5">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23858,7 +23858,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1464</v>
+        <v>1469</v>
       </c>
     </row>
   </sheetData>
@@ -24788,7 +24788,7 @@
         <v>61</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -25520,7 +25520,7 @@
         <v>465</v>
       </c>
       <c r="M3">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3353</v>
       </c>
       <c r="M11">
-        <v>2593</v>
+        <v>2604</v>
       </c>
     </row>
   </sheetData>
@@ -26262,7 +26262,7 @@
         <v>189</v>
       </c>
       <c r="M10">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26303,7 +26303,7 @@
         <v>383</v>
       </c>
       <c r="M11">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -26524,7 +26524,7 @@
         <v>40</v>
       </c>
       <c r="M5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -26641,7 +26641,7 @@
         <v>225</v>
       </c>
       <c r="M8">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -26871,7 +26871,7 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -27320,7 +27320,7 @@
         <v>75</v>
       </c>
       <c r="M2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27361,7 +27361,7 @@
         <v>86</v>
       </c>
       <c r="M3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27443,7 +27443,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27563,7 +27563,7 @@
         <v>178</v>
       </c>
       <c r="M8">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1243</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1697</v>
+        <v>1708</v>
       </c>
     </row>
   </sheetData>
@@ -27834,7 +27834,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28121,7 +28121,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -28991,7 +28991,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
   </sheetData>
@@ -29934,7 +29934,7 @@
         <v>59</v>
       </c>
       <c r="M8">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30016,7 +30016,7 @@
         <v>108</v>
       </c>
       <c r="M10">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30057,7 +30057,7 @@
         <v>274</v>
       </c>
       <c r="M11">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1498</v>
+        <v>1505</v>
       </c>
     </row>
   </sheetData>
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -31381,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
   </sheetData>
@@ -32312,7 +32312,7 @@
         <v>446</v>
       </c>
       <c r="M10">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32353,7 +32353,7 @@
         <v>737</v>
       </c>
       <c r="M11">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -32788,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -32936,7 +32936,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -32977,7 +32977,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -33100,7 +33100,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -33182,7 +33182,7 @@
         <v>293</v>
       </c>
       <c r="M8">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -33412,7 +33412,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -33728,7 +33728,7 @@
         <v>553</v>
       </c>
       <c r="M10">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33769,7 +33769,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -33984,7 +33984,7 @@
         <v>16</v>
       </c>
       <c r="M5">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -34206,7 +34206,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -34354,7 +34354,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -34597,7 +34597,7 @@
         <v>57</v>
       </c>
       <c r="M9">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
   </sheetData>
@@ -35073,7 +35073,7 @@
         <v>58</v>
       </c>
       <c r="M9">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -35155,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -35508,7 +35508,7 @@
         <v>206</v>
       </c>
       <c r="M8">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35590,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -35984,7 +35984,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36066,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36107,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -36214,7 +36214,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -36530,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -38040,7 +38040,7 @@
         <v>19</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -38256,7 +38256,7 @@
         <v>234</v>
       </c>
       <c r="M11">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -38638,7 +38638,7 @@
         <v>23</v>
       </c>
       <c r="M9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -38720,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -39114,7 +39114,7 @@
         <v>45</v>
       </c>
       <c r="M9">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -39155,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39196,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -39985,7 +39985,7 @@
         <v>34</v>
       </c>
       <c r="M9">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -40026,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40067,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -40466,7 +40466,7 @@
         <v>247</v>
       </c>
       <c r="M10">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40507,7 +40507,7 @@
         <v>408</v>
       </c>
       <c r="M11">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -40772,7 +40772,7 @@
         <v>56</v>
       </c>
       <c r="M6">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -40842,7 +40842,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -40883,7 +40883,7 @@
         <v>110</v>
       </c>
       <c r="M9">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1662</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2133</v>
+        <v>2146</v>
       </c>
     </row>
   </sheetData>
@@ -41318,7 +41318,7 @@
         <v>203</v>
       </c>
       <c r="M8">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41441,7 +41441,7 @@
         <v>578</v>
       </c>
       <c r="M11">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -41834,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41875,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -42102,7 +42102,7 @@
         <v>76</v>
       </c>
       <c r="M5">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42339,7 +42339,7 @@
         <v>727</v>
       </c>
       <c r="M11">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -44482,7 +44482,7 @@
         <v>140</v>
       </c>
       <c r="M8">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44605,7 +44605,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -45254,7 +45254,7 @@
         <v>50</v>
       </c>
       <c r="M5">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45368,7 +45368,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45450,7 +45450,7 @@
         <v>485</v>
       </c>
       <c r="M10">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -45598,7 +45598,7 @@
         <v>265</v>
       </c>
       <c r="M2">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -45762,7 +45762,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -45844,7 +45844,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45926,7 +45926,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2067</v>
+        <v>2073</v>
       </c>
     </row>
   </sheetData>
@@ -47047,7 +47047,7 @@
         <v>18</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -47170,7 +47170,7 @@
         <v>277</v>
       </c>
       <c r="M11">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -49340,7 +49340,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -49605,7 +49605,7 @@
         <v>263</v>
       </c>
       <c r="M10">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49646,7 +49646,7 @@
         <v>308</v>
       </c>
       <c r="M11">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5137</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5759</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6214</v>
       </c>
       <c r="M5">
-        <v>4560</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1062,7 +1062,7 @@
         <v>1628</v>
       </c>
       <c r="H6">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="I6">
         <v>1996</v>
@@ -1074,10 +1074,10 @@
         <v>1958</v>
       </c>
       <c r="L6">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="M6">
-        <v>1567</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17261</v>
       </c>
       <c r="M8">
-        <v>14413</v>
+        <v>14461</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3752</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>58730</v>
       </c>
       <c r="M10">
-        <v>46350</v>
+        <v>46521</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1267,7 +1267,7 @@
         <v>85549</v>
       </c>
       <c r="H11">
-        <v>84848</v>
+        <v>84849</v>
       </c>
       <c r="I11">
         <v>110886</v>
@@ -1279,10 +1279,10 @@
         <v>118959</v>
       </c>
       <c r="L11">
-        <v>104508</v>
+        <v>104509</v>
       </c>
       <c r="M11">
-        <v>82181</v>
+        <v>82489</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>636</v>
       </c>
       <c r="M8">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1107</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2811</v>
+        <v>2826</v>
       </c>
     </row>
   </sheetData>
@@ -2356,7 +2356,7 @@
         <v>91</v>
       </c>
       <c r="M5">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1199</v>
       </c>
       <c r="M10">
-        <v>1049</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1500</v>
+        <v>1506</v>
       </c>
     </row>
   </sheetData>
@@ -2832,7 +2832,7 @@
         <v>62</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2952,7 +2952,7 @@
         <v>121</v>
       </c>
       <c r="M8">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2993,7 +2993,7 @@
         <v>41</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>951</v>
+        <v>959</v>
       </c>
     </row>
   </sheetData>
@@ -3299,7 +3299,7 @@
         <v>54</v>
       </c>
       <c r="M5">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3504,7 +3504,7 @@
         <v>321</v>
       </c>
       <c r="M10">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>783</v>
       </c>
       <c r="M11">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4251,7 +4251,7 @@
         <v>216</v>
       </c>
       <c r="M5">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4292,7 +4292,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1443</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3469</v>
+        <v>3484</v>
       </c>
     </row>
   </sheetData>
@@ -4604,7 +4604,7 @@
         <v>242</v>
       </c>
       <c r="M2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4645,7 +4645,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1820</v>
+        <v>1826</v>
       </c>
     </row>
   </sheetData>
@@ -5080,7 +5080,7 @@
         <v>113</v>
       </c>
       <c r="M2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5121,7 +5121,7 @@
         <v>150</v>
       </c>
       <c r="M3">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5367,7 +5367,7 @@
         <v>79</v>
       </c>
       <c r="M9">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1250</v>
+        <v>1255</v>
       </c>
     </row>
   </sheetData>
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1211</v>
+        <v>1216</v>
       </c>
     </row>
   </sheetData>
@@ -6310,7 +6310,7 @@
         <v>159</v>
       </c>
       <c r="M9">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1992</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2523</v>
+        <v>2530</v>
       </c>
     </row>
   </sheetData>
@@ -6540,7 +6540,7 @@
         <v>239</v>
       </c>
       <c r="M3">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>783</v>
       </c>
       <c r="M6">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1820</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3469</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>951</v>
+        <v>959</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1518</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6909,7 +6909,7 @@
         <v>408</v>
       </c>
       <c r="M12">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6950,7 +6950,7 @@
         <v>267</v>
       </c>
       <c r="M13">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -6991,7 +6991,7 @@
         <v>727</v>
       </c>
       <c r="M14">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1659</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1696</v>
       </c>
       <c r="M20">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7401,7 +7401,7 @@
         <v>531</v>
       </c>
       <c r="M24">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>578</v>
       </c>
       <c r="M25">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7483,7 +7483,7 @@
         <v>234</v>
       </c>
       <c r="M26">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3354</v>
       </c>
       <c r="M29">
-        <v>2630</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7729,7 +7729,7 @@
         <v>180</v>
       </c>
       <c r="M32">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2091</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1211</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1883</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -7975,7 +7975,7 @@
         <v>133</v>
       </c>
       <c r="M38">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -8016,7 +8016,7 @@
         <v>180</v>
       </c>
       <c r="M39">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -8098,7 +8098,7 @@
         <v>361</v>
       </c>
       <c r="M41">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2488</v>
       </c>
       <c r="M42">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>925</v>
+        <v>936</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8303,7 +8303,7 @@
         <v>300</v>
       </c>
       <c r="M46">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2163</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1456</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8546,10 +8546,10 @@
         <v>1848</v>
       </c>
       <c r="L52">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="M52">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1500</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2945</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8877,7 +8877,7 @@
         <v>737</v>
       </c>
       <c r="M60">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8985,7 +8985,7 @@
         <v>2060</v>
       </c>
       <c r="H63">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="I63">
         <v>2146</v>
@@ -9000,7 +9000,7 @@
         <v>1390</v>
       </c>
       <c r="M63">
-        <v>433</v>
+        <v>412</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1143</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9123,7 +9123,7 @@
         <v>602</v>
       </c>
       <c r="M66">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1914</v>
       </c>
       <c r="M67">
-        <v>1589</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9451,7 +9451,7 @@
         <v>308</v>
       </c>
       <c r="M74">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -9492,7 +9492,7 @@
         <v>426</v>
       </c>
       <c r="M75">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2523</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9574,7 +9574,7 @@
         <v>374</v>
       </c>
       <c r="M77">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1485</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9697,7 +9697,7 @@
         <v>468</v>
       </c>
       <c r="M80">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9779,7 +9779,7 @@
         <v>231</v>
       </c>
       <c r="M82">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1170</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2811</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>811</v>
+        <v>819</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>673</v>
+        <v>681</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2222</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>980</v>
+        <v>984</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1250</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10543,7 +10543,7 @@
         <v>85549</v>
       </c>
       <c r="H101">
-        <v>84848</v>
+        <v>84849</v>
       </c>
       <c r="I101">
         <v>110886</v>
@@ -10555,10 +10555,10 @@
         <v>118959</v>
       </c>
       <c r="L101">
-        <v>104508</v>
+        <v>104509</v>
       </c>
       <c r="M101">
-        <v>82181</v>
+        <v>82489</v>
       </c>
     </row>
   </sheetData>
@@ -10767,7 +10767,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10995,7 +10995,7 @@
         <v>163</v>
       </c>
       <c r="M8">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1091</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1456</v>
+        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
   </sheetData>
@@ -12381,7 +12381,7 @@
         <v>145</v>
       </c>
       <c r="M8">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12422,7 +12422,7 @@
         <v>180</v>
       </c>
       <c r="M9">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -13312,7 +13312,7 @@
         <v>1163</v>
       </c>
       <c r="M10">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2488</v>
       </c>
       <c r="M11">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
   </sheetData>
@@ -13624,7 +13624,7 @@
         <v>51</v>
       </c>
       <c r="M6">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13706,7 +13706,7 @@
         <v>317</v>
       </c>
       <c r="M8">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1914</v>
       </c>
       <c r="M11">
-        <v>1589</v>
+        <v>1595</v>
       </c>
     </row>
   </sheetData>
@@ -14252,7 +14252,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14293,7 +14293,7 @@
         <v>361</v>
       </c>
       <c r="M11">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -14683,7 +14683,7 @@
         <v>97</v>
       </c>
       <c r="M10">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14724,7 +14724,7 @@
         <v>180</v>
       </c>
       <c r="M11">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2258</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2945</v>
+        <v>2953</v>
       </c>
     </row>
   </sheetData>
@@ -15614,7 +15614,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -15914,7 +15914,7 @@
         <v>32</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15990,7 +15990,7 @@
         <v>360</v>
       </c>
       <c r="M8">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1600</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2222</v>
+        <v>2232</v>
       </c>
     </row>
   </sheetData>
@@ -16810,7 +16810,7 @@
         <v>87</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -17491,7 +17491,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -17747,7 +17747,7 @@
         <v>66</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>980</v>
+        <v>984</v>
       </c>
     </row>
   </sheetData>
@@ -18301,7 +18301,7 @@
         <v>55</v>
       </c>
       <c r="M8">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18424,7 +18424,7 @@
         <v>300</v>
       </c>
       <c r="M11">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -18572,7 +18572,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18695,7 +18695,7 @@
         <v>49</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18777,7 +18777,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1696</v>
       </c>
       <c r="M11">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
   </sheetData>
@@ -19007,7 +19007,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19048,7 +19048,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19130,7 +19130,7 @@
         <v>171</v>
       </c>
       <c r="M5">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19253,7 +19253,7 @@
         <v>417</v>
       </c>
       <c r="M8">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>719</v>
+        <v>724</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1883</v>
+        <v>1895</v>
       </c>
     </row>
   </sheetData>
@@ -19524,7 +19524,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19726,10 +19726,10 @@
         <v>234</v>
       </c>
       <c r="L8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M8">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19849,10 +19849,10 @@
         <v>1848</v>
       </c>
       <c r="L11">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="M11">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -20205,7 +20205,7 @@
         <v>284</v>
       </c>
       <c r="M8">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -20435,7 +20435,7 @@
         <v>66</v>
       </c>
       <c r="M2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20476,7 +20476,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20558,7 +20558,7 @@
         <v>33</v>
       </c>
       <c r="M5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20681,7 +20681,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>673</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -21486,7 +21486,7 @@
         <v>101</v>
       </c>
       <c r="M5">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21650,7 +21650,7 @@
         <v>104</v>
       </c>
       <c r="M9">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21691,7 +21691,7 @@
         <v>603</v>
       </c>
       <c r="M10">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1143</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -22344,7 +22344,7 @@
         <v>131</v>
       </c>
       <c r="M3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22549,7 +22549,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -23059,7 +23059,7 @@
         <v>524</v>
       </c>
       <c r="M10">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -23312,7 +23312,7 @@
         <v>69</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23423,7 +23423,7 @@
         <v>189</v>
       </c>
       <c r="M8">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1036</v>
       </c>
       <c r="M10">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>925</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -23776,7 +23776,7 @@
         <v>149</v>
       </c>
       <c r="M5">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23899,7 +23899,7 @@
         <v>468</v>
       </c>
       <c r="M8">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1485</v>
+        <v>1490</v>
       </c>
     </row>
   </sheetData>
@@ -24281,7 +24281,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24339,7 +24339,7 @@
         <v>85</v>
       </c>
       <c r="M8">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -24421,7 +24421,7 @@
         <v>383</v>
       </c>
       <c r="M10">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24462,7 +24462,7 @@
         <v>602</v>
       </c>
       <c r="M11">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -24870,7 +24870,7 @@
         <v>301</v>
       </c>
       <c r="M10">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>
@@ -25479,7 +25479,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>1009</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3354</v>
       </c>
       <c r="M11">
-        <v>2630</v>
+        <v>2638</v>
       </c>
     </row>
   </sheetData>
@@ -26524,7 +26524,7 @@
         <v>40</v>
       </c>
       <c r="M5">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -26985,7 +26985,7 @@
         <v>28</v>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27172,7 +27172,7 @@
         <v>338</v>
       </c>
       <c r="M10">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -27563,7 +27563,7 @@
         <v>178</v>
       </c>
       <c r="M8">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
   </sheetData>
@@ -27834,7 +27834,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27916,7 +27916,7 @@
         <v>78</v>
       </c>
       <c r="M5">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28039,7 +28039,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28080,7 +28080,7 @@
         <v>62</v>
       </c>
       <c r="M9">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -28121,7 +28121,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>
@@ -28269,7 +28269,7 @@
         <v>211</v>
       </c>
       <c r="M2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1659</v>
+        <v>1663</v>
       </c>
     </row>
   </sheetData>
@@ -29262,7 +29262,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29344,7 +29344,7 @@
         <v>125</v>
       </c>
       <c r="M5">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1170</v>
+        <v>1177</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30205,7 +30205,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30328,7 +30328,7 @@
         <v>26</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1518</v>
+        <v>1528</v>
       </c>
     </row>
   </sheetData>
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -31176,7 +31176,7 @@
         <v>112</v>
       </c>
       <c r="M5">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -31381,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -31690,7 +31690,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -31839,7 +31839,7 @@
         <v>306</v>
       </c>
       <c r="M10">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31880,7 +31880,7 @@
         <v>531</v>
       </c>
       <c r="M11">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -32230,7 +32230,7 @@
         <v>105</v>
       </c>
       <c r="M8">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32271,7 +32271,7 @@
         <v>38</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -32353,7 +32353,7 @@
         <v>737</v>
       </c>
       <c r="M11">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -32788,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -32936,7 +32936,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -33059,7 +33059,7 @@
         <v>81</v>
       </c>
       <c r="M5">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -33182,7 +33182,7 @@
         <v>293</v>
       </c>
       <c r="M8">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33264,7 +33264,7 @@
         <v>478</v>
       </c>
       <c r="M10">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -33412,7 +33412,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -33570,7 +33570,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -33646,7 +33646,7 @@
         <v>192</v>
       </c>
       <c r="M8">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33769,7 +33769,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -34313,7 +34313,7 @@
         <v>83</v>
       </c>
       <c r="M2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -34556,7 +34556,7 @@
         <v>308</v>
       </c>
       <c r="M8">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
@@ -35262,7 +35262,7 @@
         <v>61</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35385,7 +35385,7 @@
         <v>69</v>
       </c>
       <c r="M5">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -35508,7 +35508,7 @@
         <v>206</v>
       </c>
       <c r="M8">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35590,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -35779,7 +35779,7 @@
         <v>68</v>
       </c>
       <c r="M3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -35861,7 +35861,7 @@
         <v>104</v>
       </c>
       <c r="M5">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -35984,7 +35984,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36066,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36107,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -36530,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -36946,7 +36946,7 @@
         <v>204</v>
       </c>
       <c r="M10">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36987,7 +36987,7 @@
         <v>267</v>
       </c>
       <c r="M11">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -37368,7 +37368,7 @@
         <v>152</v>
       </c>
       <c r="M10">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37409,7 +37409,7 @@
         <v>231</v>
       </c>
       <c r="M11">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -37618,7 +37618,7 @@
         <v>48</v>
       </c>
       <c r="M5">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -38040,7 +38040,7 @@
         <v>19</v>
       </c>
       <c r="M5">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -38215,7 +38215,7 @@
         <v>164</v>
       </c>
       <c r="M10">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38256,7 +38256,7 @@
         <v>234</v>
       </c>
       <c r="M11">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -38483,7 +38483,7 @@
         <v>25</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -38679,7 +38679,7 @@
         <v>151</v>
       </c>
       <c r="M10">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38720,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -38868,7 +38868,7 @@
         <v>63</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -39155,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40026,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40067,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -40215,7 +40215,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -40507,7 +40507,7 @@
         <v>408</v>
       </c>
       <c r="M11">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -40731,7 +40731,7 @@
         <v>206</v>
       </c>
       <c r="M5">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1685</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2163</v>
+        <v>2170</v>
       </c>
     </row>
   </sheetData>
@@ -41154,7 +41154,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -41400,7 +41400,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41441,7 +41441,7 @@
         <v>578</v>
       </c>
       <c r="M11">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -41691,7 +41691,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -41834,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41875,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>811</v>
+        <v>819</v>
       </c>
     </row>
   </sheetData>
@@ -41982,7 +41982,7 @@
         <v>44</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42298,7 +42298,7 @@
         <v>426</v>
       </c>
       <c r="M10">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42339,7 +42339,7 @@
         <v>727</v>
       </c>
       <c r="M11">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -42487,7 +42487,7 @@
         <v>47</v>
       </c>
       <c r="M3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -42815,7 +42815,7 @@
         <v>374</v>
       </c>
       <c r="M11">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -43232,7 +43232,7 @@
         <v>264</v>
       </c>
       <c r="M10">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43273,7 +43273,7 @@
         <v>426</v>
       </c>
       <c r="M11">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -44362,7 +44362,7 @@
         <v>52</v>
       </c>
       <c r="M5">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44564,7 +44564,7 @@
         <v>385</v>
       </c>
       <c r="M10">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44605,7 +44605,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -44945,7 +44945,7 @@
         <v>35</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44986,7 +44986,7 @@
         <v>364</v>
       </c>
       <c r="M10">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45027,7 +45027,7 @@
         <v>468</v>
       </c>
       <c r="M11">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -45368,7 +45368,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45409,7 +45409,7 @@
         <v>32</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45450,7 +45450,7 @@
         <v>485</v>
       </c>
       <c r="M10">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -45721,7 +45721,7 @@
         <v>125</v>
       </c>
       <c r="M5">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45844,7 +45844,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45926,7 +45926,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2091</v>
+        <v>2095</v>
       </c>
     </row>
   </sheetData>
@@ -47964,7 +47964,7 @@
         <v>170</v>
       </c>
       <c r="M10">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48005,7 +48005,7 @@
         <v>239</v>
       </c>
       <c r="M11">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -48362,7 +48362,7 @@
         <v>92</v>
       </c>
       <c r="M10">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48403,7 +48403,7 @@
         <v>133</v>
       </c>
       <c r="M11">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -49605,7 +49605,7 @@
         <v>263</v>
       </c>
       <c r="M10">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -49646,7 +49646,7 @@
         <v>308</v>
       </c>
       <c r="M11">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5152</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5780</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6214</v>
       </c>
       <c r="M5">
-        <v>4595</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1053,13 +1053,13 @@
         <v>2025</v>
       </c>
       <c r="E6">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="F6">
         <v>2029</v>
       </c>
       <c r="G6">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H6">
         <v>1887</v>
@@ -1074,10 +1074,10 @@
         <v>1958</v>
       </c>
       <c r="L6">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="M6">
-        <v>1574</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>436</v>
       </c>
       <c r="M7">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17261</v>
       </c>
       <c r="M8">
-        <v>14461</v>
+        <v>14506</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3762</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1238,10 +1238,10 @@
         <v>61336</v>
       </c>
       <c r="L10">
-        <v>58730</v>
+        <v>58731</v>
       </c>
       <c r="M10">
-        <v>46521</v>
+        <v>46694</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1258,13 +1258,13 @@
         <v>117428</v>
       </c>
       <c r="E11">
-        <v>113503</v>
+        <v>113504</v>
       </c>
       <c r="F11">
         <v>105731</v>
       </c>
       <c r="G11">
-        <v>85549</v>
+        <v>85550</v>
       </c>
       <c r="H11">
         <v>84849</v>
@@ -1282,7 +1282,7 @@
         <v>104509</v>
       </c>
       <c r="M11">
-        <v>82489</v>
+        <v>82778</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1471,7 +1471,7 @@
         <v>13</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2826</v>
+        <v>2833</v>
       </c>
     </row>
   </sheetData>
@@ -2085,7 +2085,7 @@
         <v>36</v>
       </c>
       <c r="M10">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2126,7 +2126,7 @@
         <v>61</v>
       </c>
       <c r="M11">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2356,7 +2356,7 @@
         <v>91</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1199</v>
       </c>
       <c r="M10">
-        <v>1053</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1506</v>
+        <v>1513</v>
       </c>
     </row>
   </sheetData>
@@ -2993,7 +2993,7 @@
         <v>41</v>
       </c>
       <c r="M9">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>959</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3422,7 @@
         <v>227</v>
       </c>
       <c r="M8">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3504,7 +3504,7 @@
         <v>321</v>
       </c>
       <c r="M10">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>783</v>
       </c>
       <c r="M11">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -3652,7 +3652,7 @@
         <v>84</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4292,7 +4292,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1448</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3484</v>
+        <v>3492</v>
       </c>
     </row>
   </sheetData>
@@ -4645,7 +4645,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4727,7 +4727,7 @@
         <v>194</v>
       </c>
       <c r="M5">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4850,7 +4850,7 @@
         <v>569</v>
       </c>
       <c r="M8">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4891,7 +4891,7 @@
         <v>166</v>
       </c>
       <c r="M9">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1826</v>
+        <v>1836</v>
       </c>
     </row>
   </sheetData>
@@ -5326,7 +5326,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5367,7 +5367,7 @@
         <v>79</v>
       </c>
       <c r="M9">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
   </sheetData>
@@ -5597,7 +5597,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
   </sheetData>
@@ -6146,7 +6146,7 @@
         <v>82</v>
       </c>
       <c r="M5">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6269,7 +6269,7 @@
         <v>208</v>
       </c>
       <c r="M8">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6310,7 +6310,7 @@
         <v>159</v>
       </c>
       <c r="M9">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>1998</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2530</v>
+        <v>2541</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6622,7 +6622,7 @@
         <v>266</v>
       </c>
       <c r="M5">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>783</v>
       </c>
       <c r="M6">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1826</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3484</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>959</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1528</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6950,7 +6950,7 @@
         <v>267</v>
       </c>
       <c r="M13">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -6991,7 +6991,7 @@
         <v>727</v>
       </c>
       <c r="M14">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7114,7 +7114,7 @@
         <v>129</v>
       </c>
       <c r="M17">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1663</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1696</v>
       </c>
       <c r="M20">
-        <v>1371</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7401,7 +7401,7 @@
         <v>531</v>
       </c>
       <c r="M24">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3354</v>
       </c>
       <c r="M29">
-        <v>2638</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2095</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7811,7 +7811,7 @@
         <v>701</v>
       </c>
       <c r="M34">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1895</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8098,7 +8098,7 @@
         <v>361</v>
       </c>
       <c r="M41">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2488</v>
       </c>
       <c r="M42">
-        <v>2504</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8221,7 +8221,7 @@
         <v>973</v>
       </c>
       <c r="M44">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -8303,7 +8303,7 @@
         <v>300</v>
       </c>
       <c r="M46">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2170</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1464</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1408</v>
       </c>
       <c r="M52">
-        <v>1089</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1506</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2953</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8795,7 +8795,7 @@
         <v>143</v>
       </c>
       <c r="M58">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -8877,7 +8877,7 @@
         <v>737</v>
       </c>
       <c r="M60">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8918,7 +8918,7 @@
         <v>161</v>
       </c>
       <c r="M61">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -8959,7 +8959,7 @@
         <v>61</v>
       </c>
       <c r="M62">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -8976,13 +8976,13 @@
         <v>1593</v>
       </c>
       <c r="E63">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="F63">
         <v>1496</v>
       </c>
       <c r="G63">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="H63">
         <v>2420</v>
@@ -8997,10 +8997,10 @@
         <v>1085</v>
       </c>
       <c r="L63">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="M63">
-        <v>412</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9123,7 +9123,7 @@
         <v>602</v>
       </c>
       <c r="M66">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -9161,10 +9161,10 @@
         <v>2434</v>
       </c>
       <c r="L67">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="M67">
-        <v>1595</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9492,7 +9492,7 @@
         <v>426</v>
       </c>
       <c r="M75">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2530</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9697,7 +9697,7 @@
         <v>468</v>
       </c>
       <c r="M80">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9738,7 +9738,7 @@
         <v>187</v>
       </c>
       <c r="M81">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2826</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1725</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2232</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10534,13 +10534,13 @@
         <v>117428</v>
       </c>
       <c r="E101">
-        <v>113503</v>
+        <v>113504</v>
       </c>
       <c r="F101">
         <v>105731</v>
       </c>
       <c r="G101">
-        <v>85549</v>
+        <v>85550</v>
       </c>
       <c r="H101">
         <v>84849</v>
@@ -10558,7 +10558,7 @@
         <v>104509</v>
       </c>
       <c r="M101">
-        <v>82489</v>
+        <v>82778</v>
       </c>
     </row>
   </sheetData>
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1464</v>
+        <v>1467</v>
       </c>
     </row>
   </sheetData>
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13107,7 +13107,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13148,7 +13148,7 @@
         <v>52</v>
       </c>
       <c r="M6">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13271,7 +13271,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1163</v>
       </c>
       <c r="M10">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2488</v>
       </c>
       <c r="M11">
-        <v>2504</v>
+        <v>2511</v>
       </c>
     </row>
   </sheetData>
@@ -13501,7 +13501,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13583,7 +13583,7 @@
         <v>95</v>
       </c>
       <c r="M5">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13621,7 +13621,7 @@
         <v>61</v>
       </c>
       <c r="L6">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <v>37</v>
@@ -13706,7 +13706,7 @@
         <v>317</v>
       </c>
       <c r="M8">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13826,10 +13826,10 @@
         <v>2434</v>
       </c>
       <c r="L11">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="M11">
-        <v>1595</v>
+        <v>1603</v>
       </c>
     </row>
   </sheetData>
@@ -14252,7 +14252,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14293,7 +14293,7 @@
         <v>361</v>
       </c>
       <c r="M11">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -14995,7 +14995,7 @@
         <v>38</v>
       </c>
       <c r="M6">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15074,7 +15074,7 @@
         <v>357</v>
       </c>
       <c r="M8">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2266</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2953</v>
+        <v>2966</v>
       </c>
     </row>
   </sheetData>
@@ -15614,7 +15614,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -15803,7 +15803,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15990,7 +15990,7 @@
         <v>360</v>
       </c>
       <c r="M8">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1607</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2232</v>
+        <v>2237</v>
       </c>
     </row>
   </sheetData>
@@ -16340,7 +16340,7 @@
         <v>78</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16539,7 +16539,7 @@
         <v>597</v>
       </c>
       <c r="M10">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16580,7 +16580,7 @@
         <v>973</v>
       </c>
       <c r="M11">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
   </sheetData>
@@ -17409,7 +17409,7 @@
         <v>102</v>
       </c>
       <c r="M8">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -17680,7 +17680,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -18383,7 +18383,7 @@
         <v>179</v>
       </c>
       <c r="M10">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18424,7 +18424,7 @@
         <v>300</v>
       </c>
       <c r="M11">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -18531,7 +18531,7 @@
         <v>170</v>
       </c>
       <c r="M2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18572,7 +18572,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18736,7 +18736,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -18777,7 +18777,7 @@
         <v>286</v>
       </c>
       <c r="M8">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18818,7 +18818,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1696</v>
       </c>
       <c r="M11">
-        <v>1371</v>
+        <v>1377</v>
       </c>
     </row>
   </sheetData>
@@ -19007,7 +19007,7 @@
         <v>249</v>
       </c>
       <c r="M2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19294,7 +19294,7 @@
         <v>209</v>
       </c>
       <c r="M9">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1895</v>
+        <v>1899</v>
       </c>
     </row>
   </sheetData>
@@ -19483,7 +19483,7 @@
         <v>145</v>
       </c>
       <c r="M2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19606,7 +19606,7 @@
         <v>80</v>
       </c>
       <c r="M5">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19729,7 +19729,7 @@
         <v>184</v>
       </c>
       <c r="M8">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1408</v>
       </c>
       <c r="M11">
-        <v>1089</v>
+        <v>1098</v>
       </c>
     </row>
   </sheetData>
@@ -19959,7 +19959,7 @@
         <v>105</v>
       </c>
       <c r="M2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20041,7 +20041,7 @@
         <v>15</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -21363,7 +21363,7 @@
         <v>165</v>
       </c>
       <c r="M2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21609,7 +21609,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21650,7 +21650,7 @@
         <v>104</v>
       </c>
       <c r="M9">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -22303,7 +22303,7 @@
         <v>101</v>
       </c>
       <c r="M2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22590,7 +22590,7 @@
         <v>39</v>
       </c>
       <c r="M9">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -23776,7 +23776,7 @@
         <v>149</v>
       </c>
       <c r="M5">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
   </sheetData>
@@ -24421,7 +24421,7 @@
         <v>383</v>
       </c>
       <c r="M10">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24462,7 +24462,7 @@
         <v>602</v>
       </c>
       <c r="M11">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -24870,7 +24870,7 @@
         <v>301</v>
       </c>
       <c r="M10">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>
@@ -25520,7 +25520,7 @@
         <v>466</v>
       </c>
       <c r="M3">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25643,7 +25643,7 @@
         <v>66</v>
       </c>
       <c r="M6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25725,7 +25725,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>1013</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3354</v>
       </c>
       <c r="M11">
-        <v>2638</v>
+        <v>2647</v>
       </c>
     </row>
   </sheetData>
@@ -26641,7 +26641,7 @@
         <v>225</v>
       </c>
       <c r="M8">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1264</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1725</v>
+        <v>1732</v>
       </c>
     </row>
   </sheetData>
@@ -28039,7 +28039,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1663</v>
+        <v>1668</v>
       </c>
     </row>
   </sheetData>
@@ -28991,7 +28991,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -29262,7 +29262,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30205,7 +30205,7 @@
         <v>99</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1528</v>
+        <v>1534</v>
       </c>
     </row>
   </sheetData>
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -31299,7 +31299,7 @@
         <v>324</v>
       </c>
       <c r="M8">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31381,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
   </sheetData>
@@ -31757,7 +31757,7 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31839,7 +31839,7 @@
         <v>306</v>
       </c>
       <c r="M10">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31880,7 +31880,7 @@
         <v>531</v>
       </c>
       <c r="M11">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -32312,7 +32312,7 @@
         <v>446</v>
       </c>
       <c r="M10">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32353,7 +32353,7 @@
         <v>737</v>
       </c>
       <c r="M11">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -32706,7 +32706,7 @@
         <v>185</v>
       </c>
       <c r="M8">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -33182,7 +33182,7 @@
         <v>293</v>
       </c>
       <c r="M8">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -33412,7 +33412,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -33529,7 +33529,7 @@
         <v>38</v>
       </c>
       <c r="M5">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -33646,7 +33646,7 @@
         <v>192</v>
       </c>
       <c r="M8">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33728,7 +33728,7 @@
         <v>553</v>
       </c>
       <c r="M10">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33769,7 +33769,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -34354,7 +34354,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -34474,7 +34474,7 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -34638,7 +34638,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
   </sheetData>
@@ -34786,7 +34786,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35114,7 +35114,7 @@
         <v>400</v>
       </c>
       <c r="M10">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35155,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
@@ -35590,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -35984,7 +35984,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36066,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36107,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -36448,7 +36448,7 @@
         <v>125</v>
       </c>
       <c r="M8">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36530,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
   </sheetData>
@@ -36946,7 +36946,7 @@
         <v>204</v>
       </c>
       <c r="M10">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36987,7 +36987,7 @@
         <v>267</v>
       </c>
       <c r="M11">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -37618,7 +37618,7 @@
         <v>48</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -37720,7 +37720,7 @@
         <v>62</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -37761,7 +37761,7 @@
         <v>30</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -38679,7 +38679,7 @@
         <v>151</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38720,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -38950,7 +38950,7 @@
         <v>42</v>
       </c>
       <c r="M5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -39073,7 +39073,7 @@
         <v>158</v>
       </c>
       <c r="M8">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -39155,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39196,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -40026,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40067,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1691</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2170</v>
+        <v>2177</v>
       </c>
     </row>
   </sheetData>
@@ -41650,7 +41650,7 @@
         <v>21</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -41834,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41875,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
   </sheetData>
@@ -42298,7 +42298,7 @@
         <v>426</v>
       </c>
       <c r="M10">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42339,7 +42339,7 @@
         <v>727</v>
       </c>
       <c r="M11">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -43232,7 +43232,7 @@
         <v>264</v>
       </c>
       <c r="M10">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43273,7 +43273,7 @@
         <v>426</v>
       </c>
       <c r="M11">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -43678,7 +43678,7 @@
         <v>121</v>
       </c>
       <c r="M10">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43719,7 +43719,7 @@
         <v>266</v>
       </c>
       <c r="M11">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -44482,7 +44482,7 @@
         <v>140</v>
       </c>
       <c r="M8">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44605,7 +44605,7 @@
         <v>701</v>
       </c>
       <c r="M11">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -44986,7 +44986,7 @@
         <v>364</v>
       </c>
       <c r="M10">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45027,7 +45027,7 @@
         <v>468</v>
       </c>
       <c r="M11">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -45368,7 +45368,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -45803,7 +45803,7 @@
         <v>25</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -45844,7 +45844,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2095</v>
+        <v>2097</v>
       </c>
     </row>
   </sheetData>
@@ -46309,7 +46309,7 @@
         <v>129</v>
       </c>
       <c r="M10">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -46350,7 +46350,7 @@
         <v>143</v>
       </c>
       <c r="M11">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -47385,7 +47385,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -47569,7 +47569,7 @@
         <v>56</v>
       </c>
       <c r="M10">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47610,7 +47610,7 @@
         <v>129</v>
       </c>
       <c r="M11">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -48775,7 +48775,7 @@
         <v>98</v>
       </c>
       <c r="M10">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48816,7 +48816,7 @@
         <v>161</v>
       </c>
       <c r="M11">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -50009,7 +50009,7 @@
         <v>117</v>
       </c>
       <c r="M10">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -50050,7 +50050,7 @@
         <v>187</v>
       </c>
       <c r="M11">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5168</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5796</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6214</v>
       </c>
       <c r="M5">
-        <v>4607</v>
+        <v>4621</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1960</v>
       </c>
       <c r="M6">
-        <v>1584</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1118,7 +1118,7 @@
         <v>436</v>
       </c>
       <c r="M7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17261</v>
       </c>
       <c r="M8">
-        <v>14506</v>
+        <v>14553</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3775</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1241,7 +1241,7 @@
         <v>58731</v>
       </c>
       <c r="M10">
-        <v>46694</v>
+        <v>46855</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1282,7 +1282,7 @@
         <v>104509</v>
       </c>
       <c r="M11">
-        <v>82778</v>
+        <v>83074</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1430,7 @@
         <v>446</v>
       </c>
       <c r="M3">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1471,7 +1471,7 @@
         <v>13</v>
       </c>
       <c r="M4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2833</v>
+        <v>2843</v>
       </c>
     </row>
   </sheetData>
@@ -2274,7 +2274,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1199</v>
       </c>
       <c r="M10">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1513</v>
+        <v>1520</v>
       </c>
     </row>
   </sheetData>
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3422,7 @@
         <v>227</v>
       </c>
       <c r="M8">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3504,7 +3504,7 @@
         <v>321</v>
       </c>
       <c r="M10">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>783</v>
       </c>
       <c r="M11">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -3775,7 +3775,7 @@
         <v>53</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3980,7 +3980,7 @@
         <v>602</v>
       </c>
       <c r="M10">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4021,7 +4021,7 @@
         <v>1011</v>
       </c>
       <c r="M11">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4292,7 +4292,7 @@
         <v>104</v>
       </c>
       <c r="M6">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1454</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3492</v>
+        <v>3506</v>
       </c>
     </row>
   </sheetData>
@@ -4645,7 +4645,7 @@
         <v>219</v>
       </c>
       <c r="M3">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4850,7 +4850,7 @@
         <v>569</v>
       </c>
       <c r="M8">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1836</v>
+        <v>1844</v>
       </c>
     </row>
   </sheetData>
@@ -5121,7 +5121,7 @@
         <v>150</v>
       </c>
       <c r="M3">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5285,7 +5285,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1259</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -5556,7 +5556,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5597,7 +5597,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -6269,7 +6269,7 @@
         <v>208</v>
       </c>
       <c r="M8">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>2005</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2541</v>
+        <v>2555</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>783</v>
       </c>
       <c r="M6">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1836</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3492</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1534</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6909,7 +6909,7 @@
         <v>408</v>
       </c>
       <c r="M12">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -6950,7 +6950,7 @@
         <v>267</v>
       </c>
       <c r="M13">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1668</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1696</v>
       </c>
       <c r="M20">
-        <v>1377</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7319,7 +7319,7 @@
         <v>383</v>
       </c>
       <c r="M22">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7401,7 +7401,7 @@
         <v>531</v>
       </c>
       <c r="M24">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3354</v>
       </c>
       <c r="M29">
-        <v>2647</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7688,7 +7688,7 @@
         <v>1011</v>
       </c>
       <c r="M31">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2097</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7852,7 +7852,7 @@
         <v>323</v>
       </c>
       <c r="M35">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1899</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8098,7 +8098,7 @@
         <v>361</v>
       </c>
       <c r="M41">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2488</v>
       </c>
       <c r="M42">
-        <v>2511</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>936</v>
+        <v>942</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8303,7 +8303,7 @@
         <v>300</v>
       </c>
       <c r="M46">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>940</v>
       </c>
       <c r="M47">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2177</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1467</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1408</v>
       </c>
       <c r="M52">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1513</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2966</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8836,7 +8836,7 @@
         <v>297</v>
       </c>
       <c r="M59">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8918,7 +8918,7 @@
         <v>161</v>
       </c>
       <c r="M61">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -9000,7 +9000,7 @@
         <v>1391</v>
       </c>
       <c r="M63">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9123,7 +9123,7 @@
         <v>602</v>
       </c>
       <c r="M66">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1913</v>
       </c>
       <c r="M67">
-        <v>1603</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9492,7 +9492,7 @@
         <v>426</v>
       </c>
       <c r="M75">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2541</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9574,7 +9574,7 @@
         <v>374</v>
       </c>
       <c r="M77">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1492</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1181</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2833</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -9943,7 +9943,7 @@
         <v>903</v>
       </c>
       <c r="M86">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -9984,7 +9984,7 @@
         <v>436</v>
       </c>
       <c r="M87">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1732</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10189,7 +10189,7 @@
         <v>316</v>
       </c>
       <c r="M92">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2237</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>987</v>
+        <v>993</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1259</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10517,7 +10517,7 @@
         <v>277</v>
       </c>
       <c r="M100">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -10558,7 +10558,7 @@
         <v>104509</v>
       </c>
       <c r="M101">
-        <v>82778</v>
+        <v>83074</v>
       </c>
     </row>
   </sheetData>
@@ -10887,7 +10887,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1467</v>
+        <v>1469</v>
       </c>
     </row>
   </sheetData>
@@ -11225,7 +11225,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11266,7 +11266,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11570,7 +11570,7 @@
         <v>297</v>
       </c>
       <c r="M11">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -11677,7 +11677,7 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11955,7 +11955,7 @@
         <v>59</v>
       </c>
       <c r="M9">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -12643,7 +12643,7 @@
         <v>53</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13107,7 +13107,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1163</v>
       </c>
       <c r="M10">
-        <v>1214</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2488</v>
       </c>
       <c r="M11">
-        <v>2511</v>
+        <v>2519</v>
       </c>
     </row>
   </sheetData>
@@ -13460,7 +13460,7 @@
         <v>213</v>
       </c>
       <c r="M2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1913</v>
       </c>
       <c r="M11">
-        <v>1603</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -14170,7 +14170,7 @@
         <v>69</v>
       </c>
       <c r="M8">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14211,7 +14211,7 @@
         <v>28</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14252,7 +14252,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14293,7 +14293,7 @@
         <v>361</v>
       </c>
       <c r="M11">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -15074,7 +15074,7 @@
         <v>357</v>
       </c>
       <c r="M8">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2275</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2966</v>
+        <v>2975</v>
       </c>
     </row>
   </sheetData>
@@ -15990,7 +15990,7 @@
         <v>360</v>
       </c>
       <c r="M8">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1611</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2237</v>
+        <v>2246</v>
       </c>
     </row>
   </sheetData>
@@ -16810,7 +16810,7 @@
         <v>87</v>
       </c>
       <c r="M5">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
   </sheetData>
@@ -18301,7 +18301,7 @@
         <v>55</v>
       </c>
       <c r="M8">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18424,7 +18424,7 @@
         <v>300</v>
       </c>
       <c r="M11">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -18572,7 +18572,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18818,7 +18818,7 @@
         <v>123</v>
       </c>
       <c r="M9">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1696</v>
       </c>
       <c r="M11">
-        <v>1377</v>
+        <v>1381</v>
       </c>
     </row>
   </sheetData>
@@ -19130,7 +19130,7 @@
         <v>171</v>
       </c>
       <c r="M5">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19212,7 +19212,7 @@
         <v>24</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19253,7 +19253,7 @@
         <v>417</v>
       </c>
       <c r="M8">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1899</v>
+        <v>1906</v>
       </c>
     </row>
   </sheetData>
@@ -19524,7 +19524,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19688,7 +19688,7 @@
         <v>13</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19729,7 +19729,7 @@
         <v>184</v>
       </c>
       <c r="M8">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19770,7 +19770,7 @@
         <v>127</v>
       </c>
       <c r="M9">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1408</v>
       </c>
       <c r="M11">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -20000,7 +20000,7 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20205,7 +20205,7 @@
         <v>284</v>
       </c>
       <c r="M8">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>987</v>
+        <v>993</v>
       </c>
     </row>
   </sheetData>
@@ -20599,7 +20599,7 @@
         <v>13</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -21060,7 +21060,7 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21215,7 +21215,7 @@
         <v>161</v>
       </c>
       <c r="M10">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21404,7 +21404,7 @@
         <v>137</v>
       </c>
       <c r="M3">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21609,7 +21609,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21691,7 +21691,7 @@
         <v>603</v>
       </c>
       <c r="M10">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
   </sheetData>
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -22549,7 +22549,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -22590,7 +22590,7 @@
         <v>39</v>
       </c>
       <c r="M9">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -22631,7 +22631,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -23248,7 +23248,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23312,7 +23312,7 @@
         <v>69</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23423,7 +23423,7 @@
         <v>189</v>
       </c>
       <c r="M8">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1036</v>
       </c>
       <c r="M10">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>936</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -23653,7 +23653,7 @@
         <v>185</v>
       </c>
       <c r="M2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23940,7 +23940,7 @@
         <v>161</v>
       </c>
       <c r="M9">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1492</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -24421,7 +24421,7 @@
         <v>383</v>
       </c>
       <c r="M10">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24462,7 +24462,7 @@
         <v>602</v>
       </c>
       <c r="M11">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -24718,7 +24718,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24911,7 +24911,7 @@
         <v>436</v>
       </c>
       <c r="M11">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -25479,7 +25479,7 @@
         <v>368</v>
       </c>
       <c r="M2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25520,7 +25520,7 @@
         <v>466</v>
       </c>
       <c r="M3">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25725,7 +25725,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25766,7 +25766,7 @@
         <v>286</v>
       </c>
       <c r="M9">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>1018</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3354</v>
       </c>
       <c r="M11">
-        <v>2647</v>
+        <v>2661</v>
       </c>
     </row>
   </sheetData>
@@ -26180,7 +26180,7 @@
         <v>90</v>
       </c>
       <c r="M8">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26262,7 +26262,7 @@
         <v>189</v>
       </c>
       <c r="M10">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26303,7 +26303,7 @@
         <v>383</v>
       </c>
       <c r="M11">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -26912,7 +26912,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27172,7 +27172,7 @@
         <v>338</v>
       </c>
       <c r="M10">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1732</v>
+        <v>1737</v>
       </c>
     </row>
   </sheetData>
@@ -28080,7 +28080,7 @@
         <v>62</v>
       </c>
       <c r="M9">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
   </sheetData>
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28556,7 +28556,7 @@
         <v>164</v>
       </c>
       <c r="M9">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1668</v>
+        <v>1676</v>
       </c>
     </row>
   </sheetData>
@@ -28991,7 +28991,7 @@
         <v>122</v>
       </c>
       <c r="M8">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29073,7 +29073,7 @@
         <v>423</v>
       </c>
       <c r="M10">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -29262,7 +29262,7 @@
         <v>190</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29467,7 +29467,7 @@
         <v>377</v>
       </c>
       <c r="M8">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1181</v>
+        <v>1189</v>
       </c>
     </row>
   </sheetData>
@@ -30287,7 +30287,7 @@
         <v>99</v>
       </c>
       <c r="M5">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30410,7 +30410,7 @@
         <v>285</v>
       </c>
       <c r="M8">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -30451,7 +30451,7 @@
         <v>90</v>
       </c>
       <c r="M9">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>930</v>
+        <v>934</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1534</v>
+        <v>1544</v>
       </c>
     </row>
   </sheetData>
@@ -30736,7 +30736,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -31059,7 +31059,7 @@
         <v>45</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31299,7 +31299,7 @@
         <v>324</v>
       </c>
       <c r="M8">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -31529,7 +31529,7 @@
         <v>26</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31839,7 +31839,7 @@
         <v>306</v>
       </c>
       <c r="M10">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31880,7 +31880,7 @@
         <v>531</v>
       </c>
       <c r="M11">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -32624,7 +32624,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -32788,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -32936,7 +32936,7 @@
         <v>77</v>
       </c>
       <c r="M2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -33182,7 +33182,7 @@
         <v>293</v>
       </c>
       <c r="M8">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33264,7 +33264,7 @@
         <v>478</v>
       </c>
       <c r="M10">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -33412,7 +33412,7 @@
         <v>56</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -33769,7 +33769,7 @@
         <v>940</v>
       </c>
       <c r="M11">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -34638,7 +34638,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
   </sheetData>
@@ -34786,7 +34786,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35032,7 +35032,7 @@
         <v>194</v>
       </c>
       <c r="M8">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35073,7 +35073,7 @@
         <v>58</v>
       </c>
       <c r="M9">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -35155,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -35508,7 +35508,7 @@
         <v>206</v>
       </c>
       <c r="M8">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
@@ -36331,7 +36331,7 @@
         <v>105</v>
       </c>
       <c r="M5">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -36530,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
   </sheetData>
@@ -36815,7 +36815,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -36946,7 +36946,7 @@
         <v>204</v>
       </c>
       <c r="M10">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36987,7 +36987,7 @@
         <v>267</v>
       </c>
       <c r="M11">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -37761,7 +37761,7 @@
         <v>30</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -38679,7 +38679,7 @@
         <v>151</v>
       </c>
       <c r="M10">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38720,7 +38720,7 @@
         <v>316</v>
       </c>
       <c r="M11">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -38991,7 +38991,7 @@
         <v>18</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -39155,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39196,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -40026,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40067,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -40215,7 +40215,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -40285,7 +40285,7 @@
         <v>33</v>
       </c>
       <c r="M5">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -40466,7 +40466,7 @@
         <v>247</v>
       </c>
       <c r="M10">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40507,7 +40507,7 @@
         <v>408</v>
       </c>
       <c r="M11">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1698</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2177</v>
+        <v>2180</v>
       </c>
     </row>
   </sheetData>
@@ -41793,7 +41793,7 @@
         <v>17</v>
       </c>
       <c r="M9">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41834,7 +41834,7 @@
         <v>661</v>
       </c>
       <c r="M10">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41875,7 +41875,7 @@
         <v>903</v>
       </c>
       <c r="M11">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -42446,7 +42446,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42815,7 +42815,7 @@
         <v>374</v>
       </c>
       <c r="M11">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -43232,7 +43232,7 @@
         <v>264</v>
       </c>
       <c r="M10">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43273,7 +43273,7 @@
         <v>426</v>
       </c>
       <c r="M11">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -44091,7 +44091,7 @@
         <v>265</v>
       </c>
       <c r="M10">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44132,7 +44132,7 @@
         <v>323</v>
       </c>
       <c r="M11">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -44362,7 +44362,7 @@
         <v>52</v>
       </c>
       <c r="M5">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -44564,7 +44564,7 @@
         <v>385</v>
       </c>
       <c r="M10">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45368,7 +45368,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45450,7 +45450,7 @@
         <v>485</v>
       </c>
       <c r="M10">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -45639,7 +45639,7 @@
         <v>341</v>
       </c>
       <c r="M3">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -45721,7 +45721,7 @@
         <v>125</v>
       </c>
       <c r="M5">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45926,7 +45926,7 @@
         <v>873</v>
       </c>
       <c r="M10">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2097</v>
+        <v>2105</v>
       </c>
     </row>
   </sheetData>
@@ -47129,7 +47129,7 @@
         <v>200</v>
       </c>
       <c r="M10">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47170,7 +47170,7 @@
         <v>277</v>
       </c>
       <c r="M11">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -48693,7 +48693,7 @@
         <v>26</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -48816,7 +48816,7 @@
         <v>161</v>
       </c>
       <c r="M11">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/output/index-crime-full-year.xlsx
+++ b/output/index-crime-full-year.xlsx
@@ -913,7 +913,7 @@
         <v>6588</v>
       </c>
       <c r="M2">
-        <v>5193</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -954,7 +954,7 @@
         <v>7129</v>
       </c>
       <c r="M3">
-        <v>5843</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -995,7 +995,7 @@
         <v>374</v>
       </c>
       <c r="M4">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1036,7 +1036,7 @@
         <v>6214</v>
       </c>
       <c r="M5">
-        <v>4635</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1077,7 +1077,7 @@
         <v>1961</v>
       </c>
       <c r="M6">
-        <v>1601</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1159,7 +1159,7 @@
         <v>17261</v>
       </c>
       <c r="M8">
-        <v>14599</v>
+        <v>14633</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1200,7 +1200,7 @@
         <v>5816</v>
       </c>
       <c r="M9">
-        <v>3804</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1235,13 +1235,13 @@
         <v>57530</v>
       </c>
       <c r="K10">
-        <v>61336</v>
+        <v>61337</v>
       </c>
       <c r="L10">
         <v>58732</v>
       </c>
       <c r="M10">
-        <v>47032</v>
+        <v>47180</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1276,13 +1276,13 @@
         <v>124342</v>
       </c>
       <c r="K11">
-        <v>118959</v>
+        <v>118960</v>
       </c>
       <c r="L11">
         <v>104511</v>
       </c>
       <c r="M11">
-        <v>83361</v>
+        <v>83612</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1389,7 @@
         <v>319</v>
       </c>
       <c r="M2">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1512,7 +1512,7 @@
         <v>304</v>
       </c>
       <c r="M5">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1635,7 +1635,7 @@
         <v>636</v>
       </c>
       <c r="M8">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1717,7 +1717,7 @@
         <v>1355</v>
       </c>
       <c r="M10">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1758,7 +1758,7 @@
         <v>3388</v>
       </c>
       <c r="M11">
-        <v>2850</v>
+        <v>2860</v>
       </c>
     </row>
   </sheetData>
@@ -2479,7 +2479,7 @@
         <v>221</v>
       </c>
       <c r="M8">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2561,7 +2561,7 @@
         <v>1199</v>
       </c>
       <c r="M10">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2602,7 +2602,7 @@
         <v>1749</v>
       </c>
       <c r="M11">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
   </sheetData>
@@ -3034,7 +3034,7 @@
         <v>819</v>
       </c>
       <c r="M10">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3075,7 +3075,7 @@
         <v>1149</v>
       </c>
       <c r="M11">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3422,7 @@
         <v>227</v>
       </c>
       <c r="M8">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>783</v>
       </c>
       <c r="M11">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4128,7 @@
         <v>436</v>
       </c>
       <c r="M2">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4169,7 +4169,7 @@
         <v>503</v>
       </c>
       <c r="M3">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4251,7 +4251,7 @@
         <v>216</v>
       </c>
       <c r="M5">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4374,7 +4374,7 @@
         <v>778</v>
       </c>
       <c r="M8">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4415,7 +4415,7 @@
         <v>340</v>
       </c>
       <c r="M9">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4456,7 +4456,7 @@
         <v>1964</v>
       </c>
       <c r="M10">
-        <v>1462</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4497,7 +4497,7 @@
         <v>4416</v>
       </c>
       <c r="M11">
-        <v>3518</v>
+        <v>3529</v>
       </c>
     </row>
   </sheetData>
@@ -4727,7 +4727,7 @@
         <v>194</v>
       </c>
       <c r="M5">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4850,7 +4850,7 @@
         <v>569</v>
       </c>
       <c r="M8">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4932,7 +4932,7 @@
         <v>938</v>
       </c>
       <c r="M10">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4973,7 +4973,7 @@
         <v>2405</v>
       </c>
       <c r="M11">
-        <v>1854</v>
+        <v>1859</v>
       </c>
     </row>
   </sheetData>
@@ -5244,7 +5244,7 @@
         <v>25</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>748</v>
       </c>
       <c r="M10">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5449,7 +5449,7 @@
         <v>1503</v>
       </c>
       <c r="M11">
-        <v>1268</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
@@ -5556,7 +5556,7 @@
         <v>92</v>
       </c>
       <c r="M2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5597,7 +5597,7 @@
         <v>88</v>
       </c>
       <c r="M3">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5799,7 +5799,7 @@
         <v>436</v>
       </c>
       <c r="M8">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5881,7 +5881,7 @@
         <v>637</v>
       </c>
       <c r="M10">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5922,7 +5922,7 @@
         <v>1423</v>
       </c>
       <c r="M11">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
   </sheetData>
@@ -6070,7 +6070,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6187,7 +6187,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6351,7 +6351,7 @@
         <v>2706</v>
       </c>
       <c r="M10">
-        <v>2024</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6392,7 +6392,7 @@
         <v>3347</v>
       </c>
       <c r="M11">
-        <v>2561</v>
+        <v>2569</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6499,7 @@
         <v>924</v>
       </c>
       <c r="M2">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6581,7 +6581,7 @@
         <v>597</v>
       </c>
       <c r="M4">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6622,7 +6622,7 @@
         <v>266</v>
       </c>
       <c r="M5">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6663,7 +6663,7 @@
         <v>783</v>
       </c>
       <c r="M6">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6704,7 +6704,7 @@
         <v>2405</v>
       </c>
       <c r="M7">
-        <v>1854</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6745,7 +6745,7 @@
         <v>4416</v>
       </c>
       <c r="M8">
-        <v>3518</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6786,7 +6786,7 @@
         <v>441</v>
       </c>
       <c r="M9">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6827,7 +6827,7 @@
         <v>1149</v>
       </c>
       <c r="M10">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -6868,7 +6868,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1548</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6950,7 +6950,7 @@
         <v>267</v>
       </c>
       <c r="M13">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -7032,7 +7032,7 @@
         <v>808</v>
       </c>
       <c r="M15">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7073,7 +7073,7 @@
         <v>745</v>
       </c>
       <c r="M16">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7114,7 +7114,7 @@
         <v>129</v>
       </c>
       <c r="M17">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -7155,7 +7155,7 @@
         <v>643</v>
       </c>
       <c r="M18">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7196,7 +7196,7 @@
         <v>2324</v>
       </c>
       <c r="M19">
-        <v>1680</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7237,7 +7237,7 @@
         <v>1696</v>
       </c>
       <c r="M20">
-        <v>1388</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7278,7 +7278,7 @@
         <v>275</v>
       </c>
       <c r="M21">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7319,7 +7319,7 @@
         <v>383</v>
       </c>
       <c r="M22">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7360,7 +7360,7 @@
         <v>1353</v>
       </c>
       <c r="M23">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7401,7 +7401,7 @@
         <v>531</v>
       </c>
       <c r="M24">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>578</v>
       </c>
       <c r="M25">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7483,7 +7483,7 @@
         <v>234</v>
       </c>
       <c r="M26">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7524,7 +7524,7 @@
         <v>1238</v>
       </c>
       <c r="M27">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7606,7 +7606,7 @@
         <v>3354</v>
       </c>
       <c r="M29">
-        <v>2671</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7647,7 +7647,7 @@
         <v>274</v>
       </c>
       <c r="M30">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7770,7 +7770,7 @@
         <v>2438</v>
       </c>
       <c r="M33">
-        <v>2114</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7852,7 +7852,7 @@
         <v>323</v>
       </c>
       <c r="M35">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7893,7 +7893,7 @@
         <v>1423</v>
       </c>
       <c r="M36">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7934,7 +7934,7 @@
         <v>2326</v>
       </c>
       <c r="M37">
-        <v>1917</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8057,7 +8057,7 @@
         <v>329</v>
       </c>
       <c r="M40">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -8139,7 +8139,7 @@
         <v>2488</v>
       </c>
       <c r="M42">
-        <v>2527</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -8180,7 +8180,7 @@
         <v>1461</v>
       </c>
       <c r="M43">
-        <v>944</v>
+        <v>948</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -8344,7 +8344,7 @@
         <v>941</v>
       </c>
       <c r="M47">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -8385,7 +8385,7 @@
         <v>2758</v>
       </c>
       <c r="M48">
-        <v>2190</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8426,7 +8426,7 @@
         <v>1776</v>
       </c>
       <c r="M49">
-        <v>1474</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8467,7 +8467,7 @@
         <v>1014</v>
       </c>
       <c r="M50">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -8508,7 +8508,7 @@
         <v>1444</v>
       </c>
       <c r="M51">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8549,7 +8549,7 @@
         <v>1408</v>
       </c>
       <c r="M52">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -8590,7 +8590,7 @@
         <v>1749</v>
       </c>
       <c r="M53">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8631,7 +8631,7 @@
         <v>3820</v>
       </c>
       <c r="M54">
-        <v>2987</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -8672,7 +8672,7 @@
         <v>1077</v>
       </c>
       <c r="M55">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -8713,7 +8713,7 @@
         <v>619</v>
       </c>
       <c r="M56">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8754,7 +8754,7 @@
         <v>466</v>
       </c>
       <c r="M57">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -8877,7 +8877,7 @@
         <v>737</v>
       </c>
       <c r="M60">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -8918,7 +8918,7 @@
         <v>161</v>
       </c>
       <c r="M61">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -8994,13 +8994,13 @@
         <v>1260</v>
       </c>
       <c r="K63">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="L63">
         <v>1392</v>
       </c>
       <c r="M63">
-        <v>454</v>
+        <v>439</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -9041,7 +9041,7 @@
         <v>947</v>
       </c>
       <c r="M64">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9082,7 +9082,7 @@
         <v>1383</v>
       </c>
       <c r="M65">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -9123,7 +9123,7 @@
         <v>602</v>
       </c>
       <c r="M66">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -9164,7 +9164,7 @@
         <v>1913</v>
       </c>
       <c r="M67">
-        <v>1614</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9205,7 +9205,7 @@
         <v>500</v>
       </c>
       <c r="M68">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
       <c r="M69">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9287,7 +9287,7 @@
         <v>651</v>
       </c>
       <c r="M70">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>346</v>
       </c>
       <c r="M71">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -9369,7 +9369,7 @@
         <v>659</v>
       </c>
       <c r="M72">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -9410,7 +9410,7 @@
         <v>1346</v>
       </c>
       <c r="M73">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -9533,7 +9533,7 @@
         <v>3347</v>
       </c>
       <c r="M76">
-        <v>2561</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -9574,7 +9574,7 @@
         <v>374</v>
       </c>
       <c r="M77">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -9615,7 +9615,7 @@
         <v>1577</v>
       </c>
       <c r="M78">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -9656,7 +9656,7 @@
         <v>2083</v>
       </c>
       <c r="M79">
-        <v>1502</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -9697,7 +9697,7 @@
         <v>468</v>
       </c>
       <c r="M80">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -9738,7 +9738,7 @@
         <v>187</v>
       </c>
       <c r="M81">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -9779,7 +9779,7 @@
         <v>231</v>
       </c>
       <c r="M82">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -9820,7 +9820,7 @@
         <v>1484</v>
       </c>
       <c r="M83">
-        <v>1191</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -9861,7 +9861,7 @@
         <v>843</v>
       </c>
       <c r="M84">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -9902,7 +9902,7 @@
         <v>3388</v>
       </c>
       <c r="M85">
-        <v>2850</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -10025,7 +10025,7 @@
         <v>873</v>
       </c>
       <c r="M88">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -10066,7 +10066,7 @@
         <v>2031</v>
       </c>
       <c r="M89">
-        <v>1741</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -10107,7 +10107,7 @@
         <v>1084</v>
       </c>
       <c r="M90">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -10148,7 +10148,7 @@
         <v>967</v>
       </c>
       <c r="M91">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -10230,7 +10230,7 @@
         <v>801</v>
       </c>
       <c r="M93">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -10271,7 +10271,7 @@
         <v>2666</v>
       </c>
       <c r="M94">
-        <v>2249</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>1239</v>
       </c>
       <c r="M95">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -10353,7 +10353,7 @@
         <v>1357</v>
       </c>
       <c r="M96">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -10394,7 +10394,7 @@
         <v>1716</v>
       </c>
       <c r="M97">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -10435,7 +10435,7 @@
         <v>1125</v>
       </c>
       <c r="M98">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -10476,7 +10476,7 @@
         <v>1503</v>
       </c>
       <c r="M99">
-        <v>1268</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -10552,13 +10552,13 @@
         <v>124342</v>
       </c>
       <c r="K101">
-        <v>118959</v>
+        <v>118960</v>
       </c>
       <c r="L101">
         <v>104511</v>
       </c>
       <c r="M101">
-        <v>83361</v>
+        <v>83612</v>
       </c>
     </row>
   </sheetData>
@@ -10887,7 +10887,7 @@
         <v>124</v>
       </c>
       <c r="M5">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10928,7 +10928,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11077,7 +11077,7 @@
         <v>1377</v>
       </c>
       <c r="M10">
-        <v>1105</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -11118,7 +11118,7 @@
         <v>1776</v>
       </c>
       <c r="M11">
-        <v>1474</v>
+        <v>1481</v>
       </c>
     </row>
   </sheetData>
@@ -11996,7 +11996,7 @@
         <v>725</v>
       </c>
       <c r="M10">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12037,7 +12037,7 @@
         <v>1353</v>
       </c>
       <c r="M11">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -12836,7 +12836,7 @@
         <v>448</v>
       </c>
       <c r="M10">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -12877,7 +12877,7 @@
         <v>659</v>
       </c>
       <c r="M11">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -12984,7 +12984,7 @@
         <v>187</v>
       </c>
       <c r="M2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13025,7 +13025,7 @@
         <v>234</v>
       </c>
       <c r="M3">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13107,7 +13107,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13230,7 +13230,7 @@
         <v>497</v>
       </c>
       <c r="M8">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13271,7 +13271,7 @@
         <v>190</v>
       </c>
       <c r="M9">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13312,7 +13312,7 @@
         <v>1163</v>
       </c>
       <c r="M10">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13353,7 +13353,7 @@
         <v>2488</v>
       </c>
       <c r="M11">
-        <v>2527</v>
+        <v>2536</v>
       </c>
     </row>
   </sheetData>
@@ -13706,7 +13706,7 @@
         <v>317</v>
       </c>
       <c r="M8">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13788,7 +13788,7 @@
         <v>739</v>
       </c>
       <c r="M10">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13829,7 +13829,7 @@
         <v>1913</v>
       </c>
       <c r="M11">
-        <v>1614</v>
+        <v>1616</v>
       </c>
     </row>
   </sheetData>
@@ -14872,7 +14872,7 @@
         <v>115</v>
       </c>
       <c r="M3">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14995,7 +14995,7 @@
         <v>38</v>
       </c>
       <c r="M6">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15074,7 +15074,7 @@
         <v>357</v>
       </c>
       <c r="M8">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -15115,7 +15115,7 @@
         <v>207</v>
       </c>
       <c r="M9">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -15156,7 +15156,7 @@
         <v>2932</v>
       </c>
       <c r="M10">
-        <v>2292</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15197,7 +15197,7 @@
         <v>3820</v>
       </c>
       <c r="M11">
-        <v>2987</v>
+        <v>2999</v>
       </c>
     </row>
   </sheetData>
@@ -15614,7 +15614,7 @@
         <v>408</v>
       </c>
       <c r="M10">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -15655,7 +15655,7 @@
         <v>597</v>
       </c>
       <c r="M11">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -16072,7 +16072,7 @@
         <v>1950</v>
       </c>
       <c r="M10">
-        <v>1620</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16113,7 +16113,7 @@
         <v>2666</v>
       </c>
       <c r="M11">
-        <v>2249</v>
+        <v>2252</v>
       </c>
     </row>
   </sheetData>
@@ -16810,7 +16810,7 @@
         <v>87</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16933,7 +16933,7 @@
         <v>222</v>
       </c>
       <c r="M8">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17015,7 +17015,7 @@
         <v>974</v>
       </c>
       <c r="M10">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17056,7 +17056,7 @@
         <v>1577</v>
       </c>
       <c r="M11">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>
@@ -17491,7 +17491,7 @@
         <v>168</v>
       </c>
       <c r="M10">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17532,7 +17532,7 @@
         <v>441</v>
       </c>
       <c r="M11">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -17858,7 +17858,7 @@
         <v>154</v>
       </c>
       <c r="M8">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -17940,7 +17940,7 @@
         <v>789</v>
       </c>
       <c r="M10">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -17981,7 +17981,7 @@
         <v>1125</v>
       </c>
       <c r="M11">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
   </sheetData>
@@ -18859,7 +18859,7 @@
         <v>730</v>
       </c>
       <c r="M10">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -18900,7 +18900,7 @@
         <v>1696</v>
       </c>
       <c r="M11">
-        <v>1388</v>
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
@@ -19048,7 +19048,7 @@
         <v>293</v>
       </c>
       <c r="M3">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19253,7 +19253,7 @@
         <v>417</v>
       </c>
       <c r="M8">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19335,7 +19335,7 @@
         <v>895</v>
       </c>
       <c r="M10">
-        <v>735</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19376,7 +19376,7 @@
         <v>2326</v>
       </c>
       <c r="M11">
-        <v>1917</v>
+        <v>1927</v>
       </c>
     </row>
   </sheetData>
@@ -19524,7 +19524,7 @@
         <v>141</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19811,7 +19811,7 @@
         <v>679</v>
       </c>
       <c r="M10">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19852,7 +19852,7 @@
         <v>1408</v>
       </c>
       <c r="M11">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
@@ -20287,7 +20287,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20328,7 +20328,7 @@
         <v>1239</v>
       </c>
       <c r="M11">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
   </sheetData>
@@ -20681,7 +20681,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -20763,7 +20763,7 @@
         <v>433</v>
       </c>
       <c r="M10">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -20804,7 +20804,7 @@
         <v>873</v>
       </c>
       <c r="M11">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -20978,7 +20978,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -21019,7 +21019,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21215,7 +21215,7 @@
         <v>161</v>
       </c>
       <c r="M10">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -21256,7 +21256,7 @@
         <v>346</v>
       </c>
       <c r="M11">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -21363,7 +21363,7 @@
         <v>165</v>
       </c>
       <c r="M2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21486,7 +21486,7 @@
         <v>101</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -21609,7 +21609,7 @@
         <v>233</v>
       </c>
       <c r="M8">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21732,7 +21732,7 @@
         <v>1383</v>
       </c>
       <c r="M11">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -21956,7 +21956,7 @@
         <v>39</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22114,7 +22114,7 @@
         <v>19</v>
       </c>
       <c r="M9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -22155,7 +22155,7 @@
         <v>293</v>
       </c>
       <c r="M10">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22196,7 +22196,7 @@
         <v>466</v>
       </c>
       <c r="M11">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -22631,7 +22631,7 @@
         <v>379</v>
       </c>
       <c r="M10">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -22672,7 +22672,7 @@
         <v>967</v>
       </c>
       <c r="M11">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -23059,7 +23059,7 @@
         <v>524</v>
       </c>
       <c r="M10">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23100,7 +23100,7 @@
         <v>651</v>
       </c>
       <c r="M11">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -23464,7 +23464,7 @@
         <v>49</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23505,7 +23505,7 @@
         <v>1036</v>
       </c>
       <c r="M10">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -23546,7 +23546,7 @@
         <v>1461</v>
       </c>
       <c r="M11">
-        <v>944</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -23817,7 +23817,7 @@
         <v>39</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23899,7 +23899,7 @@
         <v>468</v>
       </c>
       <c r="M8">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23981,7 +23981,7 @@
         <v>860</v>
       </c>
       <c r="M10">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24022,7 +24022,7 @@
         <v>2083</v>
       </c>
       <c r="M11">
-        <v>1502</v>
+        <v>1507</v>
       </c>
     </row>
   </sheetData>
@@ -24421,7 +24421,7 @@
         <v>383</v>
       </c>
       <c r="M10">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -24462,7 +24462,7 @@
         <v>602</v>
       </c>
       <c r="M11">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -25331,7 +25331,7 @@
         <v>747</v>
       </c>
       <c r="M10">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25372,7 +25372,7 @@
         <v>1014</v>
       </c>
       <c r="M11">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -25520,7 +25520,7 @@
         <v>466</v>
       </c>
       <c r="M3">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25602,7 +25602,7 @@
         <v>223</v>
       </c>
       <c r="M5">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25725,7 +25725,7 @@
         <v>637</v>
       </c>
       <c r="M8">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -25807,7 +25807,7 @@
         <v>1267</v>
       </c>
       <c r="M10">
-        <v>1030</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -25848,7 +25848,7 @@
         <v>3354</v>
       </c>
       <c r="M11">
-        <v>2671</v>
+        <v>2679</v>
       </c>
     </row>
   </sheetData>
@@ -26180,7 +26180,7 @@
         <v>90</v>
       </c>
       <c r="M8">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26262,7 +26262,7 @@
         <v>189</v>
       </c>
       <c r="M10">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26303,7 +26303,7 @@
         <v>383</v>
       </c>
       <c r="M11">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -26641,7 +26641,7 @@
         <v>225</v>
       </c>
       <c r="M8">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -26723,7 +26723,7 @@
         <v>544</v>
       </c>
       <c r="M10">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -26764,7 +26764,7 @@
         <v>947</v>
       </c>
       <c r="M11">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -26985,7 +26985,7 @@
         <v>28</v>
       </c>
       <c r="M5">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27213,7 +27213,7 @@
         <v>472</v>
       </c>
       <c r="M11">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -27320,7 +27320,7 @@
         <v>75</v>
       </c>
       <c r="M2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -27443,7 +27443,7 @@
         <v>136</v>
       </c>
       <c r="M5">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27484,7 +27484,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -27645,7 +27645,7 @@
         <v>1423</v>
       </c>
       <c r="M10">
-        <v>1280</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -27686,7 +27686,7 @@
         <v>2031</v>
       </c>
       <c r="M11">
-        <v>1741</v>
+        <v>1748</v>
       </c>
     </row>
   </sheetData>
@@ -28121,7 +28121,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28162,7 +28162,7 @@
         <v>1077</v>
       </c>
       <c r="M11">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
   </sheetData>
@@ -28269,7 +28269,7 @@
         <v>211</v>
       </c>
       <c r="M2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28392,7 +28392,7 @@
         <v>190</v>
       </c>
       <c r="M5">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28515,7 +28515,7 @@
         <v>410</v>
       </c>
       <c r="M8">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -28556,7 +28556,7 @@
         <v>164</v>
       </c>
       <c r="M9">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -28597,7 +28597,7 @@
         <v>1121</v>
       </c>
       <c r="M10">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -28638,7 +28638,7 @@
         <v>2324</v>
       </c>
       <c r="M11">
-        <v>1680</v>
+        <v>1688</v>
       </c>
     </row>
   </sheetData>
@@ -28786,7 +28786,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29073,7 +29073,7 @@
         <v>423</v>
       </c>
       <c r="M10">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29114,7 +29114,7 @@
         <v>808</v>
       </c>
       <c r="M11">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>
@@ -29221,7 +29221,7 @@
         <v>151</v>
       </c>
       <c r="M2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29549,7 +29549,7 @@
         <v>491</v>
       </c>
       <c r="M10">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -29590,7 +29590,7 @@
         <v>1484</v>
       </c>
       <c r="M11">
-        <v>1191</v>
+        <v>1195</v>
       </c>
     </row>
   </sheetData>
@@ -30016,7 +30016,7 @@
         <v>108</v>
       </c>
       <c r="M10">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30057,7 +30057,7 @@
         <v>274</v>
       </c>
       <c r="M11">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -30164,7 +30164,7 @@
         <v>132</v>
       </c>
       <c r="M2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30492,7 +30492,7 @@
         <v>1041</v>
       </c>
       <c r="M10">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30533,7 +30533,7 @@
         <v>1778</v>
       </c>
       <c r="M11">
-        <v>1548</v>
+        <v>1552</v>
       </c>
     </row>
   </sheetData>
@@ -30911,7 +30911,7 @@
         <v>582</v>
       </c>
       <c r="M10">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -30952,7 +30952,7 @@
         <v>619</v>
       </c>
       <c r="M11">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -31059,7 +31059,7 @@
         <v>45</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31381,7 +31381,7 @@
         <v>1104</v>
       </c>
       <c r="M10">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31422,7 +31422,7 @@
         <v>1716</v>
       </c>
       <c r="M11">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
@@ -31529,7 +31529,7 @@
         <v>26</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -31839,7 +31839,7 @@
         <v>306</v>
       </c>
       <c r="M10">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -31880,7 +31880,7 @@
         <v>531</v>
       </c>
       <c r="M11">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -32312,7 +32312,7 @@
         <v>446</v>
       </c>
       <c r="M10">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32353,7 +32353,7 @@
         <v>737</v>
       </c>
       <c r="M11">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -32788,7 +32788,7 @@
         <v>266</v>
       </c>
       <c r="M10">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -32829,7 +32829,7 @@
         <v>643</v>
       </c>
       <c r="M11">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -33059,7 +33059,7 @@
         <v>81</v>
       </c>
       <c r="M5">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -33100,7 +33100,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -33264,7 +33264,7 @@
         <v>478</v>
       </c>
       <c r="M10">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -33305,7 +33305,7 @@
         <v>1084</v>
       </c>
       <c r="M11">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -33646,7 +33646,7 @@
         <v>192</v>
       </c>
       <c r="M8">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -33769,7 +33769,7 @@
         <v>941</v>
       </c>
       <c r="M11">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -34165,7 +34165,7 @@
         <v>152</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34206,7 +34206,7 @@
         <v>329</v>
       </c>
       <c r="M11">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -34354,7 +34354,7 @@
         <v>79</v>
       </c>
       <c r="M3">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -34556,7 +34556,7 @@
         <v>308</v>
       </c>
       <c r="M8">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -34638,7 +34638,7 @@
         <v>813</v>
       </c>
       <c r="M10">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -34679,7 +34679,7 @@
         <v>1444</v>
       </c>
       <c r="M11">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
   </sheetData>
@@ -34786,7 +34786,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -35114,7 +35114,7 @@
         <v>400</v>
       </c>
       <c r="M10">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35155,7 +35155,7 @@
         <v>843</v>
       </c>
       <c r="M11">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -35590,7 +35590,7 @@
         <v>896</v>
       </c>
       <c r="M10">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -35631,7 +35631,7 @@
         <v>1346</v>
       </c>
       <c r="M11">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
   </sheetData>
@@ -35984,7 +35984,7 @@
         <v>250</v>
       </c>
       <c r="M8">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -36066,7 +36066,7 @@
         <v>761</v>
       </c>
       <c r="M10">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36107,7 +36107,7 @@
         <v>1357</v>
       </c>
       <c r="M11">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -36530,7 +36530,7 @@
         <v>812</v>
       </c>
       <c r="M10">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36571,7 +36571,7 @@
         <v>1238</v>
       </c>
       <c r="M11">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -36946,7 +36946,7 @@
         <v>204</v>
       </c>
       <c r="M10">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -36987,7 +36987,7 @@
         <v>267</v>
       </c>
       <c r="M11">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -37368,7 +37368,7 @@
         <v>152</v>
       </c>
       <c r="M10">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37409,7 +37409,7 @@
         <v>231</v>
       </c>
       <c r="M11">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -37720,7 +37720,7 @@
         <v>62</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -37802,7 +37802,7 @@
         <v>585</v>
       </c>
       <c r="M10">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -37843,7 +37843,7 @@
         <v>745</v>
       </c>
       <c r="M11">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -38215,7 +38215,7 @@
         <v>164</v>
       </c>
       <c r="M10">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -38256,7 +38256,7 @@
         <v>234</v>
       </c>
       <c r="M11">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -39155,7 +39155,7 @@
         <v>532</v>
       </c>
       <c r="M10">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39196,7 +39196,7 @@
         <v>924</v>
       </c>
       <c r="M11">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -39604,7 +39604,7 @@
         <v>328</v>
       </c>
       <c r="M10">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -39645,7 +39645,7 @@
         <v>500</v>
       </c>
       <c r="M11">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -40026,7 +40026,7 @@
         <v>166</v>
       </c>
       <c r="M10">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40067,7 +40067,7 @@
         <v>275</v>
       </c>
       <c r="M11">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -40924,7 +40924,7 @@
         <v>2025</v>
       </c>
       <c r="M10">
-        <v>1708</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -40965,7 +40965,7 @@
         <v>2758</v>
       </c>
       <c r="M11">
-        <v>2190</v>
+        <v>2193</v>
       </c>
     </row>
   </sheetData>
@@ -41113,7 +41113,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -41318,7 +41318,7 @@
         <v>203</v>
       </c>
       <c r="M8">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -41359,7 +41359,7 @@
         <v>19</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -41400,7 +41400,7 @@
         <v>216</v>
       </c>
       <c r="M10">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -41441,7 +41441,7 @@
         <v>578</v>
       </c>
       <c r="M11">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -42446,7 +42446,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -42774,7 +42774,7 @@
         <v>133</v>
       </c>
       <c r="M10">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -42815,7 +42815,7 @@
         <v>374</v>
       </c>
       <c r="M11">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -43678,7 +43678,7 @@
         <v>121</v>
       </c>
       <c r="M10">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -43719,7 +43719,7 @@
         <v>266</v>
       </c>
       <c r="M11">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -44009,7 +44009,7 @@
         <v>26</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -44091,7 +44091,7 @@
         <v>265</v>
       </c>
       <c r="M10">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -44132,7 +44132,7 @@
         <v>323</v>
       </c>
       <c r="M11">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -44945,7 +44945,7 @@
         <v>35</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -44986,7 +44986,7 @@
         <v>364</v>
       </c>
       <c r="M10">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45027,7 +45027,7 @@
         <v>468</v>
       </c>
       <c r="M11">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -45368,7 +45368,7 @@
         <v>155</v>
       </c>
       <c r="M8">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45450,7 +45450,7 @@
         <v>485</v>
       </c>
       <c r="M10">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -45491,7 +45491,7 @@
         <v>801</v>
       </c>
       <c r="M11">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -45721,7 +45721,7 @@
         <v>125</v>
       </c>
       <c r="M5">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45762,7 +45762,7 @@
         <v>71</v>
       </c>
       <c r="M6">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -45844,7 +45844,7 @@
         <v>459</v>
       </c>
       <c r="M8">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -45885,7 +45885,7 @@
         <v>271</v>
       </c>
       <c r="M9">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -45967,7 +45967,7 @@
         <v>2438</v>
       </c>
       <c r="M11">
-        <v>2114</v>
+        <v>2119</v>
       </c>
     </row>
   </sheetData>
@@ -47318,7 +47318,7 @@
         <v>14</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -47569,7 +47569,7 @@
         <v>56</v>
       </c>
       <c r="M10">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -47610,7 +47610,7 @@
         <v>129</v>
       </c>
       <c r="M11">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -48775,7 +48775,7 @@
         <v>98</v>
       </c>
       <c r="M10">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -48816,7 +48816,7 @@
         <v>161</v>
       </c>
       <c r="M11">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -49930,7 +49930,7 @@
         <v>28</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -50050,7 +50050,7 @@
         <v>187</v>
       </c>
       <c r="M11">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
